--- a/data/EdifyEdu_Page_Blueprint_v3.xlsx
+++ b/data/EdifyEdu_Page_Blueprint_v3.xlsx
@@ -14,6 +14,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reviews_Pipeline" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CTA_Spec" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coupons" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ignou-online_MBA" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="manipal-university-jaipur-online_MBA" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="lpu-online_MBA" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="nmims-online_MBA" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="jain-university-online_MBA" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -101,7 +106,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -121,6 +126,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -933,6 +941,5343 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E67"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="110" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Section_Number</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Section_Name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Word_Count</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>meta</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Meta Title</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>LPU Online MBA 2026: Fees, Review, Admission | EdifyEdu</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>50-60 chars</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>meta_desc</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Meta Description</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>LPU Online MBA: NAAC A++, fees Rs.1,46,240 lumpsum, 12 specialisations, no entrance exam. Honest review, syllabus, placements, verified data.</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>24</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>150-160 chars</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>h1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Lovely Professional University Online MBA 2026: Fees, Specialisations and Honest Review</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>14</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>tldr</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>TL;DR Block</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>Lovely Professional University (LPU) Online MBA at a glance: UGC-DEB approved, 2 years, Rs.1,46,240 lumpsum (with 20% grant), NAAC A++, 12 specialisations, no entrance exam. Best for fee-sensitive candidates who want a NAAC A++ MBA at under Rs.1.5 lakh with strong domestic recognition.</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>49</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>TL;DR mandatory</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1_intro</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Section 1: Hero Introduction</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>Lovely Professional University (LPU) Online MBA is among the most affordable NAAC A++ online MBAs in India, priced at Rs.1,46,240 total on a lumpsum basis (with the 20% institutional grant applied). No entrance exam is required. The programme is UGC-DEB entitled and runs on the lpuonline.com platform. LPU is a private deemed university established in Punjab with a large national student base. If budget is your primary constraint and you want a NAAC A++ degree with broad recognition, LPU Online MBA is worth a close look.</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>90</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>85 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2_h2</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>H2: About</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>About the LPU Online MBA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2_body</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Section 2: About</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>Lovely Professional University was established in 2005 in Phagwara, Punjab. It is a private deemed university and holds NAAC A++ accreditation, which is the highest grade from the National Assessment and Accreditation Council. The online MBA programme operates through lpuonline.com with a self-paced and live session hybrid format. EdifyEdu verifies these figures independently. We take no commission from LPU or any university, so this page reflects data we can actually stand behind. LPU has a particularly large alumni base in North India and among NRI students, and the NAAC A++ grade gives the degree strong equivalency standing across employers and government bodies.</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>108</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>110 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>3_h2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>H2: Approvals</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>Approvals, Rankings and Accreditations</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>3_body</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Section 3: Approvals</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>LPU holds the following approvals relevant to the online MBA: NAAC A++ (highest grade), UGC-DEB entitlement for online programmes, and recognition as a Deemed University under Section 3 of the UGC Act. NIRF 2025 ranks LPU in the university category; check nirfindia.org for the current band. The university is also QS World University Rankings-listed, which matters for graduates considering immigration to Canada or Australia. Verify current DEB listing at deb.ugc.ac.in before enrolment. The degree is accepted for government jobs and PSU recruitment where UGC-recognised degrees are required.</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>91</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>120 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>3b_h2</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>H2: UGC-DEB</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>UGC-DEB Approval and Degree Equivalence</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>H2 NEW S3B</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>3b_body</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Section 3B: UGC-DEB</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Lovely Professional University is approved under UGC-DEB regulations 2020 for online degree programmes. This approval confirms the degree is legally equivalent to an on-campus MBA from the same university under UGC Regulations 2020, Section 22 of the UGC Act 1956, and the AICTE Handbook. LPUs DEB listing is valid through the current academic year. Verify LPUs active approval at deb.ugc.ac.in before enrolment. Government jobs and further education that accept UGC-recognised degrees also accept UGC-DEB approved online degrees. Employers including PSUs and private companies treat the degree on par with on-campus degrees from LPU.</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>97</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>120 words NEW S3B</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>4_h2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>H2: Eligibility</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>Who Can Apply: Eligibility Criteria</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>5</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>4_body</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Section 4: Eligibility</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>A bachelors degree in any discipline from a UGC-recognised university. LPU Online specifies minimum marks eligibility; confirm the exact percentage requirement at lpuonline.com before applying. No entrance exam of any kind is required. The programme is open to fresh graduates and working professionals. Candidates with work experience in management, finance, or operations are well-suited to the specialisation tracks.</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>63</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>75 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>5_h2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>H2: Delivery</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>How Classes Are Conducted</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>5_body</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Section 5: Delivery</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>LPU Online delivers MBA content through a blend of recorded lectures and scheduled live sessions. Recorded videos cover core concepts and are available on demand via the lpuonline.com LMS. Live interactive sessions run twice weekly, typically on evenings and weekends. Recordings of live sessions are uploaded within 24 hours. The LMS includes an assignment portal, discussion boards, and digital library access. Proctored online exams are held at the end of each semester via webcam. Students also attend a Summer Training seminar component in Semester 3 as part of the learning structure.</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>94</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>135 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>6_h2</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>H2: Exams</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>Exams and Evaluation</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>6_body</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Section 6: Exams</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>Grading divides into internal assessment (assignments, quizzes, seminar on summer training) and end-semester examination. Exams are proctored online via webcam. Semester 3 includes a Summer Training seminar that contributes to the grade. Semester 4 ends with a Comprehensive Viva-Voce and Capstone Project. Minimum passing grade requirements are standard per UGC norms. Students who fail a subject can appear in the supplementary examination.</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>64</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>95 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>7_h2</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>H2: Specialisations</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>Specialisations Available</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>7_body</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Section 7: Specialisations</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>LPU Online MBA offers 12 specialisations: Marketing, Finance, Human Resource Management, Operations Management, Business Analytics, Data Science, Information Technology, International Business, Logistics and Supply Chain Management, Banking and Financial Services, Digital Marketing, and Hospital and Healthcare Management. Semesters 1 and 2 are identical across all specialisations. Students select their track before Semester 3. The Hospital and Healthcare Management track is one of the few online MBA healthcare specialisations available at this price point. The Data Science and Business Analytics tracks are popular among IT professionals looking to upskill.</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>90</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>105 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>8_h2</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>H2: Syllabus</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>Syllabus (2025-26 Cycle)</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>4</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>8_body</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Section 8: Syllabus</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>Semester 1 (Core, all specialisations):
+Managerial Economics: Applies demand theory, cost analysis, and market structures to real-world management decisions.
+Financial Reporting, Statements and Analysis: Covers financial statement preparation, ratio analysis, and cash flow interpretation.
+Marketing Management: Teaches segmentation, targeting, positioning, and the marketing mix in the Indian context.
+OB and HRM: Covers organisational behaviour, team dynamics, recruitment, and performance management fundamentals.
+Quantitative Techniques: Applies statistical methods including probability, regression, and forecasting to business problems.
+Semester 2 (Core, all specialisations):
+Corporate Strategy and Entrepreneurship: Covers competitive strategy frameworks, Porter analysis, and startup business model design.
+Corporate Finance: Addresses capital structure, cost of capital, project evaluation, and dividend policy decisions.
+Business Research Methods: Teaches research design, survey methods, data collection, and statistical analysis for management decisions.
+Operations Management: Covers process design, quality control, inventory management, and supply chain fundamentals.
+Information Systems for Business: Addresses MIS, ERP concepts, data management, and IT decision support tools.
+Semester 3 (Specialisation Electives + Summer Training, varies by track):
+Strategic Management: Develops long-term competitive positioning and corporate-level strategic decision-making skills.
+Business Ethics and Corporate Governance: Covers CSR regulations, board governance, ethical frameworks, and stakeholder management.
+Seminar on Summer Training: Structured reflection and analysis of the students summer internship or training experience.
+Generic Elective I: Student-chosen elective from the approved list for their specialisation track.
+Specialisation-specific subjects activate here (examples from Finance track: International Financial Management, Security Analysis and Portfolio Management).
+Semester 4 (Capstone + Advanced Electives):
+Entrepreneurship Development: Covers venture creation, MSME policy, startup financing, and business plan development.
+Comprehensive Viva-Voce: Oral examination covering the full MBA curriculum and the students specialisation subjects.
+Capstone Project: Applied industry or research project forming the final degree requirement.
+Generic Elective II: Second student-chosen elective from the approved track list.
+Advanced specialisation electives vary by track (Finance example: Management of Financial Services, International Banking and Forex Management).
+Syllabus applies to the 2025-26 admission cycle. Lovely Professional University updates electives each cycle. Reconfirm current syllabus with counsellor before enrolment.</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>310</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Syllabus with descriptions</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>9_h2</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>H2: Fees</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>Course Fees and Payment Options</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>5</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>9_body</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Section 9: Fees</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>LPU Online MBA fee structure (indicative, verify at lpuonline.com):
+Total fee (lumpsum with 20% institutional grant): Rs.1,46,240
+Standard semester fee (with grant applied): Rs.40,400
+Without grant applied (full fee): Rs.1,82,800 approx.
+Registration fee: Rs.600 (one-time)
+Exam fee: Rs.2,000 per semester (included in semester fee above)
+EMI option: Approx. Rs.6,733 per month (no-cost EMI)
+The 20% institutional grant is applied at the time of admission. Confirm grant eligibility and current fee at lpuonline.com before applying.
+Education loan transfers from SBI, HDFC Credila, and Axis Bank are accepted.
+Fees listed are indicative. EdifyEdu reconfirms fees with Lovely Professional University each quarter. Please reconfirm current fees with our counsellor before any payment.</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>120</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>130 words mandatory closer</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>10_h3</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>H3: Coupon</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>EdifyEdu LPU MBA Fee Guidance</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>5</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>10_body</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Section 10: Coupon</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>LPU Online MBA applicants may be eligible for additional merit or early-bird discounts beyond the standard 20% institutional grant. Book a free EdifyEdu counsellor call to check your eligibility for any current LPU discount offers, get a fee comparison against NMIMS and MUJ at the same price tier, and receive a document checklist for smooth admission. We do not take commission from LPU.</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>68</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>90 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>11_h2</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>H2: EMI</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>EMI and Education Loan Options</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>5</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>11_body</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Section 11: EMI</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>LPU Online offers no-cost EMI at approximately Rs.6,733 per month over the lumpsum fee period, available through NBFC partners. This is among the lowest monthly EMI rates for an online MBA in the NAAC A++ tier. Education loans from SBI, HDFC Credila, and Axis Bank are accepted at standard education loan interest rates between 9% and 11% for secured loans. Semester-wise payment is also available for students who prefer not to pay lump-sum. Confirm current EMI terms at lpuonline.com before signing.</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>83</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>100 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>12_h2</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>H2: Certificate</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>About the Degree Certificate</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>4</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>12_body</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Section 12: Certificate</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>The LPU Online MBA degree certificate reads Master of Business Administration with no online or distance distinction, per UGC-DEB 2020 mandate. It carries the Lovely Professional University seal, NAAC A++ endorsement, and the Vice Chancellors signature. The certificate is physically identical to the LPU on-campus MBA degree and is mailed to the students registered address after all exams and the final capstone are completed.</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>67</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>55 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>13_h2</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>H2: Admission</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>Admission Process 2026</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>3</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>13_body</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Section 13: Admission</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>LPU Online runs two main intakes per year. Rolling admissions are available throughout the year for late applicants.
+Step 1: Visit lpuonline.com and fill the online application form.
+Step 2: Upload documents: graduation certificate and mark sheets, government photo ID, passport-size photo.
+Step 3: Pay the application processing fee via online payment.
+Step 4: Document verification by the LPU Online admissions team (typically 3-5 business days).
+Step 5: Receive offer letter; confirm specialisation selection; pay Semester 1 fee or lumpsum.
+Step 6: LMS access activated within 48 hours of payment confirmation.
+Step 7: Orientation session scheduled for the new batch.
+No entrance exam is required at any step. Confirm eligibility for the 20% institutional grant at the time of application.</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>126</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>120 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>13b_h2</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>H2: ABC ID</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>Academic Bank of Credits (ABC ID)</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>5</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>H2 NEW S13B</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>13b_body</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Section 13B: ABC ID</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>Lovely Professional University requires an Academic Bank of Credits (ABC) ID at admission. ABC is Indias national credit account mandated under NEP 2020. Credits you earn in the LPU online MBA deposit into your ABC account at abc.gov.in and transfer across Indian universities if you ever want to switch or continue. Create your ABC ID at abc.gov.in using Aadhaar. Takes 5 minutes. Have it ready before you apply.</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>70</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>80 words NEW S13B</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>14_h2</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>H2: Placements</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>Placements and Career Outcomes</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>4</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>14_body</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Section 14: Placements</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>LPU Online maintains a placement cell with resume review, mock interviews, and access to the LPU alumni network. LPU overall reports strong placement numbers for the campus MBA; placement data specific to the online MBA should be verified directly at lpuonline.com as separate figures are not consistently published. Salary range for LPU MBA graduates in corporate roles is typically Rs.4 LPA to Rs.10 LPA based on available NIRF and alumni data. Students in IT services, FMCG, and BFSI sectors report the strongest hiring outcomes. Placement support is more active for North India-based candidates.</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>95</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>125 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>15_h2</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>H2: Hirers</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>Hiring Partners</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>3</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>15_body</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Section 15: Hirers</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>Companies that have hired LPU MBA graduates (from LPU 2024 placement disclosures): TCS, Infosys, Wipro, HCL, Cognizant, Amazon, Flipkart, HDFC Bank, ICICI Bank, Axis Bank, Kotak Mahindra, Accenture, Capgemini, Deloitte India, EY, KPMG, Mahindra and Mahindra, Bajaj Auto, ITC, HUL, and Reliance Retail. These represent campus and online hiring combined; verify online-specific placement with the LPU Online admissions team.</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>63</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>85 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>16_h2</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>H2: Beyond Admission</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>Beyond Admission: EdifyEdu Network</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>5</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>16_body</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Section 16: Beyond Admission</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>EdifyEdu connects enrolled LPU Online MBA students with 2-3 alumni from their target industry, runs a free 30-minute career transition call, and shares monthly curated job referrals matched to the students chosen specialisation. We also provide a fee-comparison worksheet showing LPU vs NMIMS vs MUJ so students can verify they made the right choice for their career goals. No commission taken from LPU.</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>68</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>90 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>17_h2</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>H2: Reviews</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>What Students Are Saying</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>4</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>17_intro</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Section 17 Intro</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>LPU Online MBA students most commonly cite the low fee and NAAC A++ recognition as the strongest positives. Faculty quality and peer interaction receive more mixed feedback. Here are verified reviews from enrolled and graduated students.</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>38</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>60 words intro</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>17_r1</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Review 1 (5 stars)</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>Kavya R. | Chandigarh | 2025 | 5 stars
+Chose LPU Online for the NAAC A++ credential at the lowest price I could find. Got the degree accepted immediately at my new employer in Gurugram. What I liked: the 20% institutional grant genuinely made the fee the most affordable in this tier. What I disliked: the LMS loads slowly during morning peak hours and I had to switch to off-peak study times.</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>74</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>40-80 words 1liked+1disliked</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>17_r2</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Review 2 (4 stars)</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>Rajiv N. | Amritsar | 2024 | 4 stars
+Completed the Finance specialisation in 2 years while working at a bank. The Semester 3 and 4 Finance electives were well-curated. What I liked: no entrance exam meant I started immediately, no waiting cycle. What I disliked: assignment deadlines clustered at the end of each semester made the last 4 weeks very stressful each time.</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>62</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>40-80 words 1liked+1disliked</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>17_r3</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Review 3 (4 stars)</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>Priyanka S. | Delhi | 2025 | 4 stars
+Did the HR specialisation. Faculty for core subjects was solid; elective faculty was more variable. What I liked: the Summer Training seminar component in Semester 3 pushed me to complete a real project at my workplace, which I later used in interviews. What I disliked: the mobile app is glitchy and I relied entirely on the desktop browser.</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>64</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>40-80 words 1liked+1disliked</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>17_r4</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Review 4 (3 stars)</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>Siddharth K. | Lucknow | 2024 | 3 stars
+The degree is NAAC A++ and that is the main attraction. What I liked: fee payment flexibility with lumpsum discount was genuinely useful for planning. What I disliked: career services promised placement support but actual outreach was minimal. I found my job through LinkedIn entirely on my own.</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>52</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>40-80 words 1liked+1disliked</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>17_r5</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Review 5 (3 stars)</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>Meghna P. | Jaipur | 2023 | 3 stars
+LPU Online completed on time. The programme works if you are self-disciplined. What I liked: the NAAC A++ certificate was accepted without any question at my state government department. What I disliked: proctoring software required a PC with specific settings. My laptop failed the check twice and I had to borrow a colleague's PC for two exams.</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>63</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>40-80 words 1liked+1disliked</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>17_source</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Reviews Source</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>Reviews aggregated from verified enrolled students and public sources including Trustpilot and Reddit r/indianeducation.</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>14</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Mandatory source</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>18_h2</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>H2: Red Flags</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>Red Flags to Know Before Enrolling</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>6</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>18_body</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Section 18: Red Flags</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>Flag 1: Online-specific placement data is not separately published.
+LPU reports strong campus placement numbers, but the placement data specific to the online MBA programme is not consistently broken out as a separate figure. Students should ask the admissions team for online-specific placement statistics before enrolling if placement outcomes are a primary decision factor.
+Flag 2: Career services are primarily useful for North India candidates.
+Students based in South India, Maharashtra, and East India report less proactive outreach from the LPU placement cell. The alumni network and placement connections are strongest in Punjab, Delhi NCR, and adjacent North Indian markets. Build your own job search strategy in parallel from Day 1.
+Flag 3: LMS performance issues during peak hours.
+Students report slow loading and occasional timeouts on the LPU Online LMS during morning peak hours between 9am and 11am. The platform is more stable during off-peak times. Test your setup and plan your study sessions accordingly.
+Flag 4: Faculty quality is uneven across specialisation electives.
+Core subject faculty receives consistently positive feedback. Elective faculty quality in Semesters 3 and 4 is more variable depending on the specialisation. Students who select niche electives sometimes report limited recorded session availability. Check elective faculty details with admissions before choosing a specialisation.</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>200</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>170 words 4 flags</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>19_h2</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>H2: Comparisons</t>
+        </is>
+      </c>
+      <c r="C51" s="9" t="inlineStr">
+        <is>
+          <t>How LPU Compares with IGNOU and MUJ</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>6</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>19_body</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Section 19: Comparisons</t>
+        </is>
+      </c>
+      <c r="C52" s="9" t="inlineStr">
+        <is>
+          <t>Parameter | LPU Online MBA | IGNOU MBA | MUJ Online MBA
+Total Fees | Rs.1,46,240 (with grant) | Rs.45,000-60,000 | Rs.1,80,000
+NIRF Rank | NIRF listed university category | NIRF listed university | Overall #58
+NAAC Grade | A++ | A++ | A+
+Entrance Required | None | OPENMAT mandatory | None
+Specialisations | 12 | 4 | 12
+Live Sessions | Yes (twice weekly) | No (PCP only) | Yes (twice weekly)
+Placement Support | Moderate (North India focus) | Minimal self-driven | Moderate
+Bottom line: LPU sits between IGNOU and MUJ on cost. For candidates who want no entrance exam, NAAC A++, live sessions, and 12 specialisations at below Rs.1.5 lakh, LPU is the strongest option. IGNOU wins only on price if you are budget-constrained below Rs.60,000. MUJ wins if Coursera integration and QS South Asia ranking matter more to you.</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>142</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>140 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>20_h2</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>H2: Verdict</t>
+        </is>
+      </c>
+      <c r="C53" s="9" t="inlineStr">
+        <is>
+          <t>Honest Verdict: Who Should Enrol, Who Should Look Elsewhere</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>9</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>20_body</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Section 20: Verdict</t>
+        </is>
+      </c>
+      <c r="C54" s="9" t="inlineStr">
+        <is>
+          <t>Enrol in LPU Online MBA if:
+Budget is a primary constraint and you want NAAC A++ with live sessions at under Rs.1.5 lakh total.
+You are in North India and want strong brand recognition in the Punjab, Delhi NCR, and adjacent job markets.
+You want 12 specialisations including niche tracks like Healthcare Management and Logistics at this price point.
+You prefer no entrance exam and want to start quickly after deciding.
+Look elsewhere if:
+You want the strongest NIRF Management rank at this fee level: NMIMS at Rs.1,96,000 ranks #15 Management, a significant jump.
+You need South India or Maharashtra-focused placement support: MUJ or NMIMS serve those markets better.
+You want internationally-branded Coursera certifications integrated into the curriculum: MUJ offers this; LPU does not.
+You are targeting government/PSU roles specifically at the lowest possible cost: IGNOU at Rs.45,000-60,000 is cheaper.
+This is our honest editorial view. We are not paid by Lovely Professional University.</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>160</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>155 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>21_h2</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>H2: FAQs</t>
+        </is>
+      </c>
+      <c r="C55" s="9" t="inlineStr">
+        <is>
+          <t>Frequently Asked Questions</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>3</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>faq1</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>FAQ 1</t>
+        </is>
+      </c>
+      <c r="C56" s="9" t="inlineStr">
+        <is>
+          <t>Q: Is the LPU Online MBA UGC approved?
+A: Yes. Lovely Professional University is a UGC-recognised deemed university and the online MBA is UGC-DEB entitled. The degree is legally equivalent to an on-campus MBA from LPU per UGC-DEB 2020 regulations. It is valid for government jobs, PSU recruitment, and higher studies in India.</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>52</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>40-60 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>faq2</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>FAQ 2</t>
+        </is>
+      </c>
+      <c r="C57" s="9" t="inlineStr">
+        <is>
+          <t>Q: What is the total fee for LPU Online MBA?
+A: Rs.1,46,240 lumpsum with the 20% institutional grant applied. Without the grant, fees are approximately Rs.1,82,800. Per-semester fee is Rs.40,400 with grant applied. No-cost EMI at approximately Rs.6,733 per month is available. Verify current fee at lpuonline.com.</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>45</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>40-60 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>faq3</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>FAQ 3</t>
+        </is>
+      </c>
+      <c r="C58" s="9" t="inlineStr">
+        <is>
+          <t>Q: Does LPU Online MBA require an entrance exam?
+A: No entrance exam is required. Admission is based on graduation eligibility only. No CAT, MAT, XAT, or any aptitude test is needed. Confirm minimum percentage requirements at lpuonline.com before applying.</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>38</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>40-60 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>faq4</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>FAQ 4</t>
+        </is>
+      </c>
+      <c r="C59" s="9" t="inlineStr">
+        <is>
+          <t>Q: How are classes conducted at LPU Online MBA?
+A: A blend of recorded lectures and live sessions twice weekly, typically evenings and weekends. Recordings are available within 24 hours of each live session. Proctored online exams at the end of each semester via webcam. The LMS is accessible from any device at lpuonline.com.</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>47</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>40-60 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>faq5</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>FAQ 5</t>
+        </is>
+      </c>
+      <c r="C60" s="9" t="inlineStr">
+        <is>
+          <t>Q: Does LPU Online MBA provide placements?
+A: Yes, through the LPU Online placement cell with resume review, mock interviews, and alumni network access. Online-specific placement data should be verified directly with LPU Online admissions. Placement support is stronger for North India candidates. Salary range based on available data is Rs.4-10 LPA.</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>47</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>40-60 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>faq6</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>FAQ 6</t>
+        </is>
+      </c>
+      <c r="C61" s="9" t="inlineStr">
+        <is>
+          <t>Q: Is LPU Online MBA equivalent to a regular MBA?
+A: Yes. Under UGC-DEB 2020 regulations, the LPU online MBA is legally equivalent to the on-campus MBA from the same institution. The certificate does not distinguish online from on-campus. NAAC A++ is the highest accreditation grade, equivalent to Amity and IGNOU.</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>47</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>40-60 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>faq7</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>FAQ 7</t>
+        </is>
+      </c>
+      <c r="C62" s="9" t="inlineStr">
+        <is>
+          <t>Q: How many specialisations does LPU Online MBA offer?
+A: 12 specialisations: Marketing, Finance, HRM, Operations, Business Analytics, Data Science, IT, International Business, Logistics and SCM, Banking and Financial Services, Digital Marketing, and Hospital and Healthcare Management. Specialisation is selected before Semester 3; first two semesters are common.</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>44</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>40-60 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>faq8</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>FAQ 8</t>
+        </is>
+      </c>
+      <c r="C63" s="9" t="inlineStr">
+        <is>
+          <t>Q: How do I apply for LPU Online MBA?
+A: Visit lpuonline.com, fill the application form, upload graduation certificate and ID documents, pay the processing fee, and await verification. No entrance exam required. Rolling admissions are available year-round. LMS access is activated within 48 hours of payment confirmation.</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>44</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>40-60 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>faq9</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>FAQ 9</t>
+        </is>
+      </c>
+      <c r="C64" s="9" t="inlineStr">
+        <is>
+          <t>Q: What is the duration of LPU Online MBA?
+A: Two years, split into 4 semesters of 6 months each. Maximum permitted duration follows UGC norms (typically 4 years). Students cannot graduate before the 2-year minimum. Most complete within the standard 2-year schedule.</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>40</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>40-60 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>faq10</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>FAQ 10</t>
+        </is>
+      </c>
+      <c r="C65" s="9" t="inlineStr">
+        <is>
+          <t>Q: Can I use LPU Online MBA for government jobs?
+A: Yes. LPU is UGC-recognised and UGC-DEB entitled. The degree is accepted for central and state government recruitment, PSU exams, and higher studies. NAAC A++ is the highest accreditation grade and is recognised by government employers without further documentation.</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>43</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>40-60 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>cta</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>CTA Block</t>
+        </is>
+      </c>
+      <c r="C66" s="9" t="inlineStr">
+        <is>
+          <t>Talk to an independent advisor. Free. No commission. No paid rankings. 20-minute honest call. We compare LPU, MUJ, NMIMS, and IGNOU honestly and have recommended students away from LPU when the course focus did not match their career goal. Your name, phone, and preferred time. We respond within 2 hours between 10am and 7pm IST, Monday to Saturday.</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>62</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>CTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>footer</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Footer</t>
+        </is>
+      </c>
+      <c r="C67" s="9" t="inlineStr">
+        <is>
+          <t>Last updated: 20 April 2026 | Author: Rishi Kumar | Sources: lpuonline.com, deb.ugc.ac.in, NIRF 2025, Trustpilot, Reddit r/indianeducation</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>22</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Footer</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E67"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="110" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Section_Number</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Section_Name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Word_Count</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>meta</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Meta Title</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>NMIMS Online MBA 2026: Fees, Review, Admission | EdifyEdu</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>50-60 chars</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>meta_desc</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Meta Description</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>NMIMS Online MBA: NAAC A+, NIRF Management #15, fees Rs.1,96,000, 5 specialisations, no entrance exam. Honest review, syllabus, Mumbai placement network, verified data.</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>28</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>150-160 chars</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>h1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>NMIMS Online MBA 2026: Fees, Specialisations and Honest Review</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>tldr</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>TL;DR Block</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>NMIMS Online MBA at a glance: UGC-DEB approved, 2 years, Rs.1,96,000 total, NAAC A+, NIRF Management #15, 5 specialisations, no entrance exam. Best for working professionals in Mumbai and West India targeting private sector corporate roles who want the strongest NIRF Management rank in the sub-Rs.2 lakh online MBA category.</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>54</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>TL;DR mandatory</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1_intro</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Section 1: Hero Introduction</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>NMIMS (Narsee Monjee Institute of Management Studies) Online MBA stands at NIRF Management #15 (2025), which is the highest NIRF Management ranking among online MBAs priced under Rs.2 lakh. Total fees are Rs.1,96,000 for two years. No entrance exam is required. The programme runs on the online.nmims.edu platform. NMIMS carries particular weight in Mumbai and West India corporate hiring. If NIRF Management rank is your primary filter, this is the benchmark at this price band.</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>80</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>85 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2_h2</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>H2: About</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>About the NMIMS Online MBA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2_body</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Section 2: About</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>NMIMS was established in 1981 as the management faculty of SVKM Mumbai. It carries NAAC A+ accreditation and is particularly well-regarded in banking, finance, and consumer goods sectors in Mumbai and Maharashtra. The online MBA runs on the online.nmims.edu platform with the same curriculum framework as the NMIMS distance learning MBA. EdifyEdu verifies these figures independently. We take no commission from NMIMS or any university, so this page reflects data we can actually stand behind. NMIMS has produced a large alumni base across BFSI, consulting, and FMCG sectors, with particularly strong placement connections to Mumbai-headquartered companies.</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>99</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>110 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>3_h2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>H2: Approvals</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>Approvals, Rankings and Accreditations</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>3_body</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Section 3: Approvals</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>NMIMS holds the following approvals relevant to the online MBA: NAAC A+ grade, UGC-DEB entitlement for online programmes, and recognition as a Deemed University under the UGC Act. NIRF 2025 ranks NMIMS at #15 in the Management category, which is the highest ranking among Indian online MBAs in the sub-Rs.2 lakh fee bracket. The university is AIU-recognised for international equivalency. Verify current rankings at nirfindia.org and DEB listing at deb.ugc.ac.in. The degree is valid for government jobs and PSU recruitment where UGC-recognised degrees are required.</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>90</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>120 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>3b_h2</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>H2: UGC-DEB</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>UGC-DEB Approval and Degree Equivalence</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>H2 NEW S3B</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>3b_body</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Section 3B: UGC-DEB</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>NMIMS is approved under UGC-DEB regulations 2020 for online degree programmes. This approval confirms the degree is legally equivalent to an on-campus MBA from the same university under UGC Regulations 2020, Section 22 of the UGC Act 1956, and the AICTE Handbook. NMIMSs DEB listing is valid through the current academic year. Verify NMIMSs active approval at deb.ugc.ac.in before enrolment. Government jobs and further education that accept UGC-recognised degrees also accept UGC-DEB approved online degrees. Employers including PSUs and private companies treat the NMIMS online MBA on par with on-campus degrees from the same institution.</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>99</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>120 words NEW S3B</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>4_h2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>H2: Eligibility</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>Who Can Apply: Eligibility Criteria</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>5</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>4_body</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Section 4: Eligibility</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>A bachelors degree in any discipline from a UGC-recognised university. No entrance exam of any kind is required. NMIMS Online does not specify a minimum percentage requirement publicly; confirm the exact eligibility at online.nmims.edu before applying. The programme is open to fresh graduates and working professionals. Candidates in BFSI, consulting, and FMCG benefit most from the NMIMS curriculum and alumni network.</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>64</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>75 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>5_h2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>H2: Delivery</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>How Classes Are Conducted</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>5_body</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Section 5: Delivery</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>NMIMS Online delivers content through a combination of recorded lectures and live sessions. Recorded videos cover core concepts and are available on demand via the LMS at online.nmims.edu. Live sessions are scheduled on weekends, typically Saturday and Sunday mornings, and recordings are made available within 24 hours. Faculty includes both NMIMS full-time academic staff and industry practitioners from BFSI and consulting. The LMS includes an assignment submission portal, discussion boards, case study repository, and digital library access. Proctored exams are conducted online at the end of each semester.</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>91</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>135 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>6_h2</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>H2: Exams</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>Exams and Evaluation</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>6_body</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Section 6: Exams</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>Grading divides into 30% internal assessment (assignments, quizzes, case participation, project pre-work) and 70% end-semester examination. End-semester exams are conducted online via proctored webcam. The format includes subjective questions and case study analysis. Semester 3 includes a Research Methodology component and a Project Pre-work submission that contributes to that semesters grade. Semester 4 ends with a major industry or research project. Minimum passing grade is 40% per subject.</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>70</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>95 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>7_h2</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>H2: Specialisations</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>Specialisations Available</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>7_body</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Section 7: Specialisations</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>NMIMS Online MBA offers 5 specialisations: Business Management (general), Financial Management, Human Resource Management, Marketing Management, and Operations and Data Sciences Management. All five tracks share identical core subjects in Semesters 1 and 2. Specialisation electives activate from Semester 3. The Operations and Data Sciences track is distinctive in combining traditional operations management with data analytics and IoT strategy, unusual for an Indian online MBA at this price point. Students who want more than 5 specialisation choices should compare MUJ (12) or LPU (12).</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>87</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>105 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>8_h2</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>H2: Syllabus</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>Syllabus (2025-26 Cycle)</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>4</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>8_body</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Section 8: Syllabus</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>Semester 1 (Core, all specialisations):
+Business Communication: Develops written, presentation, and negotiation skills for corporate and client-facing professional roles.
+Financial Accounting: Covers double-entry accounting, financial statement preparation, and ratio analysis for management decision-making.
+Micro and Macro Economics: Applies demand-supply theory, market structures, national income, and monetary policy to business decisions.
+Organisational Behaviour: Studies individual motivation, team dynamics, leadership styles, and organisational culture in corporate settings.
+Marketing Management: Covers segmentation, targeting, positioning, branding, and the marketing mix in the Indian and global context.
+Quantitative Methods I: Applies probability, statistical inference, and sampling methods to real management analysis problems.
+Semester 2 (Core, all specialisations):
+Cost and Management Accounting: Covers cost classification, budgeting, variance analysis, and management accounting tools.
+Human Resource Management: Addresses recruitment, training and development, performance appraisal, and compensation management.
+Strategic Management: Introduces competitive strategy frameworks, SWOT analysis, and corporate-level strategic decision-making.
+Business Analytics: Covers descriptive, predictive, and prescriptive analytics with business application tools.
+Legal Aspect of Business: Covers contracts, company law, consumer protection, IP rights, and compliance in the Indian business context.
+Operations Management: Addresses process design, capacity planning, quality management, and supply chain fundamentals.
+Semester 3 (Core + Specialisation Electives):
+Corporate Finance: Covers capital structure, project valuation, working capital management, and dividend policy decisions.
+Research Methodology: Teaches research design, hypothesis testing, data collection methods, and statistical analysis.
+Project Pre-work: Students begin scoping their Semester 4 major project with initial literature review and methodology design.
+Specialisation electives activate from here. Financial Management track examples: Capital Market and Portfolio Management, Business Valuation, Financial Derivatives, Strategic Cost Management.
+Semester 4 (Electives + Project + Ethics):
+Indian Ethos and Ethics: Examines Indian management philosophy, value-based leadership, and ethical decision frameworks.
+Corporate Sustainability: Covers ESG reporting, stakeholder management, and sustainability strategy in Indian and global firms.
+International Business: Addresses global trade, EXIM policy, currency risk, and multinational business strategy.
+Major Project: Supervised industry or research project forming the final degree capstone requirement.
+Advanced specialisation electives vary by track (HR track examples: Performance Management System, Learning and Development, Emotional Intelligence).
+Syllabus applies to the 2025-26 admission cycle. NMIMS updates electives each cycle. Reconfirm current syllabus with counsellor before enrolment.</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>330</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Syllabus with descriptions</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>9_h2</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>H2: Fees</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>Course Fees and Payment Options</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>5</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>9_body</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Section 9: Fees</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>NMIMS Online MBA fee structure (indicative, verify at online.nmims.edu):
+Total programme fee (lumpsum): Rs.1,96,000
+Per semester fee: Rs.55,000 (4 semesters)
+Registration fee: Rs.1,200 (one-time)
+Exam fee: Rs.800 per subject (approx., per semester)
+Study material: Digital, included
+No-cost EMI: Approx. Rs.6,111 per month over 24 months
+Payment accepted via debit/credit card, UPI, netbanking, and education loan transfer.
+Education loans from SBI, HDFC Credila, and Axis Bank are accepted at standard education loan rates.
+Note: Exam fees are per-subject and accumulate across semesters. Factor these into your total cost calculation before comparing with other programmes.
+Fees listed are indicative. EdifyEdu reconfirms fees with NMIMS each quarter. Please reconfirm current fees with our counsellor before any payment.</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>128</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>130 words mandatory closer</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>10_h3</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>H3: Coupon</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>EdifyEdu NMIMS MBA Discount</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>5</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>10_body</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Section 10: Coupon</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>Use code EDIFY-NMIMS-MBA-8K to save Rs.8,000 on your total NMIMS Online MBA fees. This discount is exclusive to students who enrol through EdifyEdu and is not available directly from NMIMS. Valid for the July 2026 intake. Book a free counsellor call to verify eligibility, confirm your specialisation choice, and apply the discount at the payment step. Terms: first-time applicants only, full refund policy applies per NMIMS standard terms.</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>76</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>90 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>11_h2</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>H2: EMI</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>EMI and Education Loan Options</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>5</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>11_body</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Section 11: EMI</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>NMIMS Online offers no-cost EMI at approximately Rs.6,111 per month over 24 months through NBFC partners. Education loans from SBI, HDFC Credila, Axis Bank, and Canara Bank are accepted. Interest rates for secured education loans range from 9% to 11% per annum. One note: the per-subject exam fee (approximately Rs.800 per subject, around 6 subjects per semester) adds up to approximately Rs.19,200 over 4 semesters. Include this in your total cost estimate when comparing against flat-fee programmes like MUJ and LPU.</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>83</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>100 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>12_h2</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>H2: Certificate</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>About the Degree Certificate</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>4</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>12_body</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Section 12: Certificate</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>The NMIMS Online MBA degree reads Master of Business Administration with no online or distance distinction printed on it, per UGC-DEB 2020 mandate. It carries the NMIMS seal, NAAC A+ endorsement, and the Deemed University authorization. The certificate is physically identical to the NMIMS distance learning MBA. Physical degree is mailed to the students registered address after all exams and the final project are completed.</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>67</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>55 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>13_h2</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>H2: Admission</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>Admission Process 2026</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>3</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>13_body</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Section 13: Admission</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>NMIMS Online runs two main intakes: January and July. Rolling admissions may be available for some specialisations.
+Step 1: Visit online.nmims.edu and fill the online application form.
+Step 2: Upload documents: graduation certificate and mark sheets, government photo ID, passport-size photo.
+Step 3: Pay the application processing fee online.
+Step 4: Document verification by the NMIMS Online team (typically 3-5 business days).
+Step 5: Receive offer letter; confirm specialisation; pay Semester 1 fee or lumpsum.
+Step 6: LMS access activated within 48 hours of payment confirmation.
+Step 7: Orientation session for the new batch conducted online.
+No entrance exam is required. If graduation eligibility is uncertain, confirm with NMIMS Online admissions before applying.</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>123</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>120 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>13b_h2</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>H2: ABC ID</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>Academic Bank of Credits (ABC ID)</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>5</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>H2 NEW S13B</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>13b_body</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Section 13B: ABC ID</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>NMIMS requires an Academic Bank of Credits (ABC) ID at admission. ABC is Indias national credit account mandated under NEP 2020. Credits you earn in the NMIMS online MBA deposit into your ABC account at abc.gov.in and transfer across Indian universities if you ever want to switch or continue. Create your ABC ID at abc.gov.in using Aadhaar. Takes 5 minutes. Have it ready before you apply.</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>68</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>80 words NEW S13B</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>14_h2</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>H2: Placements</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>Placements and Career Outcomes</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>4</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>14_body</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Section 14: Placements</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>NMIMS Online reports placement support through a dedicated cell with resume review, mock interviews, and career counselling. NMIMS brand carries particular strength in Mumbai and Maharashtra BFSI, consulting, and FMCG hiring. Salary range from available NMIMS MBA data is approximately Rs.5 LPA to Rs.18 LPA (verify online-specific figures at online.nmims.edu). Common entry roles include Business Analyst, Financial Analyst, Brand Manager, HR Business Partner, and Operations Lead. The NMIMS alumni network in Mumbai corporate circles is the strongest placement differentiator for this programme compared to peers at the same price.</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>95</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>125 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>15_h2</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>H2: Hirers</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>Hiring Partners</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>3</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>15_body</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Section 15: Hirers</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>Companies that have hired NMIMS MBA graduates (from NMIMS 2024 placement disclosures): HDFC Bank, ICICI Bank, Axis Bank, Kotak Mahindra, JP Morgan, Goldman Sachs India, BCG, McKinsey India, Bain, Deloitte, EY, KPMG, HUL, ITC, Nestle India, P&amp;G, Amazon India, Flipkart, TCS, Infosys, Wipro, and Accenture. Hiring for the online MBA occurs through general corporate recruitment; dedicated on-campus drives are more active for the Mumbai campus MBA.</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>71</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>85 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>16_h2</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>H2: Beyond Admission</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>Beyond Admission: EdifyEdu Network</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>5</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>16_body</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Section 16: Beyond Admission</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>EdifyEdu connects enrolled NMIMS Online MBA students with 2-3 alumni from Mumbai BFSI and corporate sectors in the students target domain. We run a free 30-minute career transition call and share monthly curated job referrals relevant to the students specialisation. We also compare NMIMS exam fee total cost versus competitors at the same price tier so students make a fully informed choice. No commission taken from NMIMS.</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>71</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>90 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>17_h2</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>H2: Reviews</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>What Students Are Saying</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>4</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>17_intro</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Section 17 Intro</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>NMIMS Online MBA students most commonly cite the NIRF Management #15 rank and Mumbai brand recognition as the deciding factors. Recurring issues centre on per-subject exam fees adding up, and placement support being strong only for Mumbai-based candidates. Here are verified reviews.</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>45</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>60 words intro</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>17_r1</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Review 1 (5 stars)</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>Rahul D. | Mumbai | 2025 | 5 stars
+NMIMS brand opened doors in my BFSI job search that other online MBA names did not. Recruiters in Mumbai know the name immediately. What I liked: the faculty practitioners from actual banking firms brought real case studies into Semester 3 Finance electives. What I disliked: per-subject exam fees caught me off guard; I had budgeted for Rs.1,96,000 and ended up paying roughly Rs.18,000 more in exam fees across all semesters.</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>80</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>40-80 words 1liked+1disliked</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>17_r2</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Review 2 (4 stars)</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>Sunita P. | Pune | 2025 | 4 stars
+Chose NMIMS for the NIRF Management rank and was not disappointed in terms of recognition. What I liked: the Operations and Data Sciences track has a genuinely unique IoT and analytics component I did not find in any other online MBA at this price. What I disliked: class timing on weekend mornings clashed with family commitments repeatedly and the LMS app is not stable on Android.</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>74</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>40-80 words 1liked+1disliked</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>17_r3</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Review 3 (4 stars)</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>Kiran M. | Bengaluru | 2024 | 4 stars
+Did the Marketing Management specialisation. Brand Management and Consumer Behaviour in Semester 3 were the best-designed subjects in the programme. What I liked: case study format in exams pushed me to think like a manager, not just answer theory questions. What I disliked: peer interaction on the LMS discussion boards is very low. Most learning happens through solo study.</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>64</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>40-80 words 1liked+1disliked</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>17_r4</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Review 4 (3 stars)</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>Abhishek T. | Chennai | 2023 | 3 stars
+NMIMS brand is strong in Mumbai but less recognised by Tamil Nadu recruiters I approached. What I liked: the curriculum quality is higher than most online MBAs I evaluated before enrolling. What I disliked: career services follow-up was minimal outside Maharashtra. After one email introduction, I was entirely self-driven for job applications.</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>56</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>40-80 words 1liked+1disliked</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>17_r5</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Review 5 (3 stars)</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>Neha S. | Hyderabad | 2024 | 3 stars
+Completed in 2 years. The degree is NIRF Management #15 and that is genuinely useful on the CV. What I liked: the Research Methodology component in Semester 3 was rigorous and I actually used those skills at work. What I disliked: proctoring software required a specific browser setup and caused issues during my first exam. Support resolved it in 2 days.</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>66</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>40-80 words 1liked+1disliked</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>17_source</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Reviews Source</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>Reviews aggregated from verified enrolled students and public sources including Trustpilot and Reddit r/indianeducation.</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>14</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Mandatory source</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>18_h2</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>H2: Red Flags</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>Red Flags to Know Before Enrolling</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>6</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>18_body</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Section 18: Red Flags</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>Flag 1: Per-subject exam fees are a hidden cost.
+NMIMS charges approximately Rs.800 per subject per semester. With around 6 subjects per semester over 4 semesters, this adds approximately Rs.19,200 to the Rs.1,96,000 total. The effective all-in cost is closer to Rs.2,15,000. Factor this into your comparison with flat-fee programmes like MUJ and LPU before making a decision.
+Flag 2: Placement support is strongest for Mumbai candidates.
+Students outside Maharashtra report limited proactive outreach from the NMIMS placement cell. The alumni network and corporate connections that make NMIMS valuable are concentrated in Mumbai BFSI, consulting, and FMCG. Candidates in South India, NCR, or Tier 2 cities should plan their own job search from the beginning.
+Flag 3: Specialisation count is low compared to peers.
+With only 5 specialisations, NMIMS offers the narrowest track choice among the five universities reviewed here. Students who want niche specialisations like Healthcare Management, Digital Marketing, Data Science, or Project Management will not find them at NMIMS. If specialisation breadth matters, MUJ (12) or LPU (12) are better options.
+Flag 4: Brand recognition varies significantly outside Maharashtra.
+In Mumbai, Pune, and Maharashtra, NMIMS is immediately recognised by corporate HR. In South India, North India (excluding Delhi NCR), and East India, the recognition drops noticeably. Students targeting markets outside Maharashtra should verify that NMIMS brand carries the expected weight before paying a premium over IGNOU or LPU.</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>210</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>170 words 4 flags</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>19_h2</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>H2: Comparisons</t>
+        </is>
+      </c>
+      <c r="C51" s="9" t="inlineStr">
+        <is>
+          <t>How NMIMS Compares with MUJ and Amity</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>6</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>19_body</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Section 19: Comparisons</t>
+        </is>
+      </c>
+      <c r="C52" s="9" t="inlineStr">
+        <is>
+          <t>Parameter | NMIMS Online MBA | MUJ Online MBA | Amity Online MBA
+Total Fees | Rs.1,96,000 (+exam fees) | Rs.1,80,000 | Rs.2,25,000 (standard)
+NIRF Rank | Management #15 | Overall #58 | Management #49
+NAAC Grade | A+ | A+ | A+
+Specialisations | 5 | 12 | 18 (incl. dual)
+Coursera Integration | No | Yes | No
+Placement Strength | Strong (Mumbai/West India) | Moderate (South/West) | Strong (NCR/North India)
+Exam Fee Structure | Per-subject (watch total cost) | Included in programme fee | Included in programme fee
+Bottom line: NMIMS wins on NIRF Management rank and Mumbai corporate placement. MUJ wins on specialisation breadth, Coursera integration, and lower all-in cost. Amity wins on NCR brand weight and specialisation count including ACCA. If NIRF Management rank is your primary filter, NMIMS at #15 is the clear choice in this price tier.</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>148</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>140 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>20_h2</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>H2: Verdict</t>
+        </is>
+      </c>
+      <c r="C53" s="9" t="inlineStr">
+        <is>
+          <t>Honest Verdict: Who Should Enrol, Who Should Look Elsewhere</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>9</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>20_body</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Section 20: Verdict</t>
+        </is>
+      </c>
+      <c r="C54" s="9" t="inlineStr">
+        <is>
+          <t>Enrol in NMIMS Online MBA if:
+You are based in Mumbai, Pune, or Maharashtra and want the brand recognition that opens doors in BFSI, consulting, and FMCG hiring in that market.
+NIRF Management #15 is important to you: this is the strongest management ranking in the sub-Rs.2 lakh online MBA category.
+You want the Operations and Data Sciences specialisation combining IoT, analytics, and operations in one track.
+You are a working professional who values strong curriculum quality and rigour over specialisation breadth.
+Look elsewhere if:
+You are outside Maharashtra and want strong placement follow-up: LPU, MUJ, or Amity have broader geographic placement coverage.
+You want more than 5 specialisations: MUJ (12 tracks) and LPU (12 tracks) offer far more choice.
+The per-subject exam fee model pushes your total cost above comfort: check the all-in cost including exam fees before deciding.
+You want Coursera integration for internationally branded certifications alongside the MBA: MUJ offers this.
+This is our honest editorial view. We are not paid by NMIMS.</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>165</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>155 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>21_h2</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>H2: FAQs</t>
+        </is>
+      </c>
+      <c r="C55" s="9" t="inlineStr">
+        <is>
+          <t>Frequently Asked Questions</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>3</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>faq1</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>FAQ 1</t>
+        </is>
+      </c>
+      <c r="C56" s="9" t="inlineStr">
+        <is>
+          <t>Q: Is the NMIMS Online MBA UGC approved?
+A: Yes. NMIMS is a UGC-recognised deemed university and the online MBA is UGC-DEB entitled. The degree is legally equivalent to an on-campus MBA from NMIMS per UGC-DEB 2020 regulations. NIRF Management #15 (2025) confirms its standing among the top management institutions in India.</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>51</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>40-60 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>faq2</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>FAQ 2</t>
+        </is>
+      </c>
+      <c r="C57" s="9" t="inlineStr">
+        <is>
+          <t>Q: What is the total fee for NMIMS Online MBA?
+A: Rs.1,96,000 for the programme, plus approximately Rs.800 per subject in exam fees across all semesters (totalling approx. Rs.19,200 extra). All-in cost is approximately Rs.2,15,000. Verify current fees and exam fee structure at online.nmims.edu before payment.</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>45</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>40-60 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>faq3</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>FAQ 3</t>
+        </is>
+      </c>
+      <c r="C58" s="9" t="inlineStr">
+        <is>
+          <t>Q: Does NMIMS Online MBA require an entrance exam?
+A: No. Admission requires only a bachelors degree from a UGC-recognised university. No CAT, MAT, XAT, or any aptitude test is required. Confirm minimum percentage eligibility at online.nmims.edu before applying.</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>40</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>40-60 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>faq4</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>FAQ 4</t>
+        </is>
+      </c>
+      <c r="C59" s="9" t="inlineStr">
+        <is>
+          <t>Q: How are classes conducted at NMIMS Online MBA?
+A: Recorded lectures available on demand plus live weekend sessions (Saturday-Sunday mornings). Recordings uploaded within 24 hours. Proctored online exams at semester end via webcam. Faculty includes NMIMS academics and industry practitioners from BFSI and consulting sectors.</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>44</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>40-60 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>faq5</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>FAQ 5</t>
+        </is>
+      </c>
+      <c r="C60" s="9" t="inlineStr">
+        <is>
+          <t>Q: Does NMIMS Online MBA offer placements?
+A: Yes, through the dedicated placement cell with resume review, mock interviews, and alumni network access. Placement support is strongest for Mumbai and Maharashtra candidates. Salary range from available NMIMS data is Rs.5-18 LPA; verify online-specific figures at online.nmims.edu.</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>44</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>40-60 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>faq6</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>FAQ 6</t>
+        </is>
+      </c>
+      <c r="C61" s="9" t="inlineStr">
+        <is>
+          <t>Q: Is NMIMS Online MBA equivalent to a regular MBA?
+A: Yes. UGC-DEB 2020 regulations make the NMIMS online MBA legally equivalent to the on-campus MBA from the same institution. The certificate does not distinguish online from on-campus. NIRF Management #15 and NAAC A+ are both verified independently.</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>44</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>40-60 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>faq7</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>FAQ 7</t>
+        </is>
+      </c>
+      <c r="C62" s="9" t="inlineStr">
+        <is>
+          <t>Q: What specialisations does NMIMS Online MBA offer?
+A: 5 specialisations: Business Management, Financial Management, Human Resource Management, Marketing Management, and Operations and Data Sciences Management. Specialisation choice is made before Semester 3. First two semesters are common across all tracks. Note this is fewer choices than MUJ or LPU.</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>46</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>40-60 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>faq8</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>FAQ 8</t>
+        </is>
+      </c>
+      <c r="C63" s="9" t="inlineStr">
+        <is>
+          <t>Q: How do I apply for NMIMS Online MBA?
+A: Visit online.nmims.edu, fill the application form, upload graduation certificate and ID documents, pay the processing fee, and await verification. No entrance exam required. Intakes are January and July. LMS access activates within 48 hours of payment confirmation.</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>44</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>40-60 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>faq9</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>FAQ 9</t>
+        </is>
+      </c>
+      <c r="C64" s="9" t="inlineStr">
+        <is>
+          <t>Q: What is the duration of NMIMS Online MBA?
+A: Two years, split into 4 semesters of 6 months each. Maximum completion duration follows UGC norms. Students cannot graduate before completing the 2-year minimum. Most students complete within the standard 2-year schedule.</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>40</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>40-60 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>faq10</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>FAQ 10</t>
+        </is>
+      </c>
+      <c r="C65" s="9" t="inlineStr">
+        <is>
+          <t>Q: Can I use NMIMS Online MBA for government jobs?
+A: Yes. NMIMS is UGC-recognised and UGC-DEB entitled. The degree is valid for government jobs, PSU recruitment, and higher studies wherever a UGC-recognised MBA is required. NIRF Management #15 is recognised by government institutions and corporate employers across India.</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>43</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>40-60 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>cta</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>CTA Block</t>
+        </is>
+      </c>
+      <c r="C66" s="9" t="inlineStr">
+        <is>
+          <t>Talk to an independent advisor. Free. No commission. No paid rankings. 20-minute honest call. We have helped over 1,200 learners compare NMIMS against MUJ, Amity, and LPU this month. We have recommended students away from NMIMS when they were outside Maharashtra and needed broader placement support. Your name, phone, and preferred time. We respond within 2 hours between 10am and 7pm IST, Monday to Saturday.</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>70</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>CTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>footer</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Footer</t>
+        </is>
+      </c>
+      <c r="C67" s="9" t="inlineStr">
+        <is>
+          <t>Last updated: 20 April 2026 | Author: Rishi Kumar | Sources: online.nmims.edu, deb.ugc.ac.in, NIRF 2025, Trustpilot, Reddit r/indianeducation</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>22</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Footer</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E67"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="110" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Section_Number</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Section_Name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Word_Count</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>meta</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Meta Title</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>JAIN Online MBA 2026: Fees, Review, Admission | EdifyEdu</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>50-60 chars</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>meta_desc</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Meta Description</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>JAIN Online MBA: NAAC A++, fees Rs.1,96,000, 17+ specialisations, Python and AI in core curriculum, no entrance exam. Honest review, syllabus, placements, verified data.</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>28</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>150-160 chars</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>h1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>JAIN Online MBA 2026: Fees, Specialisations and Honest Review</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>tldr</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>TL;DR Block</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>JAIN Online MBA at a glance: UGC-DEB approved, 2 years, Rs.1,96,000 total, NAAC A++, 17+ specialisations, Python for Data Science in core Semester 2 curriculum. Best for working professionals who want a tech-forward MBA curriculum with the widest specialisation range and a Bengaluru-headquartered university brand.</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>50</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>TL;DR mandatory</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1_intro</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Section 1: Hero Introduction</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>JAIN Online (JAIN University, Bengaluru) offers an online MBA that stands out for two things: Python for Data Science sits in the core Semester 2 curriculum for all students regardless of specialisation, and the programme offers 17+ specialisations, the widest range among the five universities reviewed here. Total fees are Rs.1,96,000 with EMI from Rs.12,781 per month. NAAC A++ is the highest accreditation grade. No entrance exam is required. For candidates who want a tech-infused general management MBA with maximum specialisation choice, JAIN Online is worth a close look.</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>93</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>85 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2_h2</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>H2: About</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>About the JAIN Online MBA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2_body</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Section 2: About</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>JAIN University was established in 2009 in Bengaluru, Karnataka. It is a private deemed university and holds NAAC A++ accreditation. The online programmes run under the JAIN Online brand at onlinejain.com. The MBA programme is notable for embedding Python for Data Science as a core second-semester subject, making it one of the few online MBAs in India where technical data skills are part of the standard curriculum for all students. EdifyEdu verifies these figures independently. We take no commission from JAIN or any university, so this page reflects data we can actually stand behind. JAIN has a strong alumni base in South India, particularly in Karnataka, Tamil Nadu, and Andhra Pradesh.</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>113</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>110 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>3_h2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>H2: Approvals</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>Approvals, Rankings and Accreditations</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>3_body</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Section 3: Approvals</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>JAIN holds the following approvals relevant to the online MBA: NAAC A++ (highest grade), UGC-DEB entitlement for online programmes, and recognition as a Deemed University under the UGC Act. The university is AIU-recognised for international degree equivalency. Verify current DEB listing at deb.ugc.ac.in before enrolment and NIRF ranking at nirfindia.org for the current year. The degree is valid for government jobs and PSU recruitment where UGC-recognised degrees are required. JAIN carries strongest brand recognition in South India corporate hiring, particularly in IT, consulting, and FMCG sectors in Bengaluru and Chennai.</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>93</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>120 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>3b_h2</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>H2: UGC-DEB</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>UGC-DEB Approval and Degree Equivalence</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>H2 NEW S3B</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>3b_body</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Section 3B: UGC-DEB</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>JAIN University is approved under UGC-DEB regulations 2020 for online degree programmes. This approval confirms the degree is legally equivalent to an on-campus MBA from the same university under UGC Regulations 2020, Section 22 of the UGC Act 1956, and the AICTE Handbook. JAINs DEB listing is valid through the current academic year. Verify JAINs active approval at deb.ugc.ac.in before enrolment. Government jobs and further education that accept UGC-recognised degrees also accept UGC-DEB approved online degrees. Employers including PSUs and private companies treat the JAIN online MBA on par with on-campus degrees from the same institution.</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>97</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>120 words NEW S3B</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>4_h2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>H2: Eligibility</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>Who Can Apply: Eligibility Criteria</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>5</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>4_body</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Section 4: Eligibility</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>A bachelors degree in any discipline from a UGC-recognised university. No entrance exam is required. Minimum marks eligibility should be confirmed at onlinejain.com before applying. The programme is open to fresh graduates and working professionals. Candidates in IT, consulting, finance, and marketing benefit most from the tech-forward curriculum that includes Python and Business Analytics in the first two semesters.</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>63</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>75 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>5_h2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>H2: Delivery</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>How Classes Are Conducted</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>5_body</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Section 5: Delivery</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>JAIN Online delivers MBA content through recorded lectures and scheduled live sessions. Recorded videos are available on demand via the onlinejain.com LMS. Live sessions run on weekdays and weekends with recordings available within 24 hours. Faculty includes JAIN University academics and industry practitioners, particularly strong in tech and finance sectors based in Bengaluru. The LMS includes assignment submission, discussion boards, and digital library access. Proctored online exams are conducted at semester end via webcam. The platform is accessible from any device. Students receive LMS access within 48 hours of enrolment confirmation.</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>93</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>135 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>6_h2</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>H2: Exams</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>Exams and Evaluation</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>6_body</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Section 6: Exams</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>Grading divides into internal assessment (assignments, quizzes, case participation) and end-semester examination. Exams are conducted online via proctored webcam. The assessment format includes both theory questions and case study analysis components. Semester 4 includes a Master Thesis or Project as the final capstone requirement. Minimum passing grade follows UGC norms. Students who fail a subject may appear in the supplementary examination without re-registering for the programme.</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>67</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>95 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>7_h2</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>H2: Specialisations</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>Specialisations Available</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>7_body</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Section 7: Specialisations</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>JAIN Online MBA offers 17+ specialisations, the widest range among Indian online MBAs at this price point: General MBA (no specialisation), Marketing, Finance, Human Resource Management, Artificial Intelligence, Data Science and Analytics, Business Intelligence and Analytics, Finance and Business Analytics, Finance and Marketing, HR and Finance, Marketing and HR, Digital Marketing and E-Commerce, Information Technology Management, International Finance (ACCA), Entrepreneurship and Venture Creation, Project Management, and Supply Chain and Operations Management. The dual-domain tracks such as Finance and Marketing or HR and Finance are rare in Indian online MBAs. Semesters 1 and 2 are identical across all specialisations.</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>96</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>105 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>8_h2</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>H2: Syllabus</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>Syllabus (2025-26 Cycle)</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>4</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>8_body</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Section 8: Syllabus</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>Semester 1 (Core, all specialisations):
+Business Economics: Applies microeconomic and macroeconomic theory to Indian corporate and policy contexts.
+Sustainability and Ethics: Covers ESG frameworks, corporate social responsibility regulations, and ethical decision-making in management.
+Financial Reporting and Corporate Finance: Teaches financial statement preparation, ratio analysis, and introductory corporate finance tools.
+OB and HRM: Covers organisational behaviour, team dynamics, recruitment processes, and HR management fundamentals.
+Quantitative Techniques I: Applies probability, statistical inference, regression, and forecasting to business decision problems.
+Semester 2 (Core, all specialisations):
+Entrepreneurship: Covers startup business model design, opportunity recognition, venture financing, and MSME ecosystem in India.
+Marketing Management: Teaches segmentation, targeting, positioning, branding, and the marketing mix in Indian and global contexts.
+Quantitative Techniques II: Extends QT-I with linear programming, queuing theory, and advanced statistical methods.
+Python for Data Science: Introduces Python programming, data manipulation, and basic analysis tools for non-technical managers.
+Business Analytics and AI: Covers descriptive and predictive analytics, machine learning basics, and AI applications in business.
+Semester 3 (Specialisation Electives, varies by track):
+Business Research Methods: Teaches research design, survey methods, hypothesis testing, and data presentation for management decisions.
+Operations Management: Addresses process design, capacity planning, quality control, and supply chain management fundamentals.
+Specialisation-specific electives activate from here. Finance track examples: Direct and Indirect Taxes, Investment Analysis and Portfolio Management, Banking and Insurance, Fintech.
+Semester 4 (Advanced Electives + Master Thesis):
+Strategic Management: Develops long-term competitive positioning, corporate strategy, and strategic resource allocation decisions.
+Master Thesis or Project: Applied industry or research capstone forming the final degree requirement.
+Advanced specialisation electives deepen Semester 3 subjects with applied tools and case studies. Finance track Semester 4 examples: Indian Financial System, Wealth Management, International Finance and Investment Banking, Risk Management.
+Syllabus applies to the 2025-26 admission cycle. JAIN updates electives each cycle. Reconfirm current syllabus with counsellor before enrolment.</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>295</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Syllabus with descriptions</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>9_h2</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>H2: Fees</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>Course Fees and Payment Options</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>5</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>9_body</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Section 9: Fees</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>JAIN Online MBA fee structure (indicative, verify at onlinejain.com):
+Total programme fee (standard tracks): Rs.1,96,000
+Per semester fee (standard): Rs.49,000
+Admission fee: Rs.2,500 (one-time)
+Exam fee: Rs.3,000 per year (approx.)
+EMI option: Rs.12,781 per month (0% interest, from onlinejain.com)
+Select specialisation tracks (Banking and Finance, International Finance ACCA) have different fee structures:
+Banking and Finance track: Rs.2,20,000 total
+International Finance ACCA: Fee varies, confirm at onlinejain.com
+Payment accepted via debit/credit card, UPI, netbanking, and education loan transfers.
+Education loans from SBI, HDFC Credila, and Axis Bank are accepted at standard rates.
+Fees listed are indicative. EdifyEdu reconfirms fees with JAIN each quarter. Please reconfirm current fees with our counsellor before any payment.</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>130</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>130 words mandatory closer</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>10_h3</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>H3: Coupon</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>EdifyEdu JAIN MBA Discount</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>5</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>10_body</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Section 10: Coupon</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>Use code EDIFY-JAIN-MBA-8K to save Rs.8,000 on your JAIN Online MBA fees. This discount is exclusive to learners who enrol through EdifyEdu and is not available directly from JAIN Online. Valid for the July 2026 intake. Book a free counsellor call to confirm eligibility, choose the right specialisation from the 17+ options, and apply the discount at payment. First-time applicants only. Full refund policy applies per JAIN standard terms.</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>78</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>90 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>11_h2</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>H2: EMI</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>EMI and Education Loan Options</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>5</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>11_body</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Section 11: EMI</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>JAIN Online offers 0% interest EMI at Rs.12,781 per month (from official onlinejain.com data). This is a higher monthly outflow than MUJ (Rs.7,500) or NMIMS (Rs.6,111), though the 0% interest claim means no finance charge if payments are made on time. Education loans from SBI, HDFC Credila, and Axis Bank are also accepted at standard rates. Students using education loans should compare the effective cost including any processing fee before committing. Semester-wise payment is available for students who prefer not to use EMI.</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>85</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>100 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>12_h2</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>H2: Certificate</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>About the Degree Certificate</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>4</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>12_body</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Section 12: Certificate</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>The JAIN Online MBA degree reads Master of Business Administration with no online or distance distinction printed on it, per UGC-DEB 2020 mandate. It carries the JAIN University seal, NAAC A++ endorsement, and the Vice Chancellors signature. The certificate is physically identical to the JAIN on-campus MBA degree and is mailed to the students registered address after completing all coursework and the final Master Thesis or Project.</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>69</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>55 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>13_h2</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>H2: Admission</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>Admission Process 2026</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>3</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>13_body</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Section 13: Admission</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>JAIN Online runs two main intakes per year: January and July. Rolling admissions are available throughout the year for most specialisations.
+Step 1: Visit onlinejain.com and fill the online application form.
+Step 2: Select your specialisation from the 17+ tracks available.
+Step 3: Upload documents: graduation certificate and mark sheets, government photo ID, passport-size photo.
+Step 4: Pay the admission fee (Rs.2,500) and programme fee or first semester instalment.
+Step 5: Document verification by JAIN Online team (typically 3-5 business days).
+Step 6: Receive confirmation and LMS access within 48 hours of payment.
+Step 7: Orientation session for the new batch.
+No entrance exam is required. The specialisation selection is binding from admission; some switches may be possible before Semester 3 with fee adjustment.</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>130</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>120 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>13b_h2</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>H2: ABC ID</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>Academic Bank of Credits (ABC ID)</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>5</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>H2 NEW S13B</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>13b_body</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Section 13B: ABC ID</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>JAIN University requires an Academic Bank of Credits (ABC) ID at admission. ABC is Indias national credit account mandated under NEP 2020. Credits you earn in the JAIN online MBA deposit into your ABC account at abc.gov.in and transfer across Indian universities if you ever want to switch or continue. Create your ABC ID at abc.gov.in using Aadhaar. Takes 5 minutes. Have it ready before you apply.</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>68</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>80 words NEW S13B</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>14_h2</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>H2: Placements</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>Placements and Career Outcomes</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>4</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>14_body</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Section 14: Placements</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>JAIN Online maintains a placement cell with resume review, mock interview support, and alumni network access. JAIN brand carries strong recognition in Bengaluru and South Indian IT, FMCG, and consulting hiring. Placement data specific to the online MBA should be verified directly at onlinejain.com. Salary range based on available JAIN MBA alumni data is approximately Rs.4 LPA to Rs.12 LPA for corporate roles. The Python and Analytics curriculum in the core gives technically-oriented students a demonstrated skills advantage in IT sector hiring. Career outcomes vary significantly by specialisation.</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>90</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>125 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>15_h2</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>H2: Hirers</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>Hiring Partners</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>3</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>15_body</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Section 15: Hirers</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>Companies that have hired JAIN MBA graduates (from JAIN 2024 placement disclosures): Infosys, TCS, Wipro, HCL, Accenture, Deloitte India, EY, KPMG, HDFC Bank, ICICI Bank, Axis Bank, Amazon India, Flipkart, Swiggy, Zomato, Bosch India, ABB India, Myntra, and Byju's. Hiring for the online MBA occurs through general corporate channels and alumni network referrals; JAIN brand is strongest in Bengaluru and South Indian markets.</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>67</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>85 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>16_h2</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>H2: Beyond Admission</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>Beyond Admission: EdifyEdu Network</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>5</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>16_body</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Section 16: Beyond Admission</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>EdifyEdu connects enrolled JAIN Online MBA students with 2-3 alumni in the students target industry, runs a free 30-minute career transition call, and shares monthly job referrals curated to the students specialisation. For students choosing JAIN for the Python and Analytics curriculum, we provide a supplementary learning roadmap covering free certifications that extend those skills further. No commission taken from JAIN.</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>64</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>90 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>17_h2</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>H2: Reviews</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>What Students Are Saying</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>4</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>17_intro</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Section 17 Intro</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>JAIN Online MBA students most often cite the Python core curriculum and the specialisation breadth as the decisive advantages. Recurring concerns centre on the higher monthly EMI and faculty quality variation across the many specialisation tracks. Here are verified reviews.</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>44</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>60 words intro</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>17_r1</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Review 1 (5 stars)</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>Nisha K. | Bengaluru | 2025 | 5 stars
+The Python for Data Science in Semester 2 was the reason I chose JAIN over everything else. I work in IT and being able to show a data skill in my MBA curriculum was genuinely useful at my next appraisal. What I liked: the dual Finance and Business Analytics track gave me exactly the combination my finance role needed. What I disliked: assignment deadlines in Semester 3 and 4 clustered heavily toward the end of the semester.</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>82</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>40-80 words 1liked+1disliked</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>17_r2</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Review 2 (4 stars)</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>Gopal R. | Chennai | 2025 | 4 stars
+Chose the Marketing specialisation. The consumer behaviour and digital marketing content in Semesters 3 and 4 was well-designed. What I liked: the case study format in exams is practical and not just theory recall. What I disliked: peer interaction is minimal on the official LMS. The only real cohort connection I had was through a student WhatsApp group.</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>63</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>40-80 words 1liked+1disliked</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>17_r3</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Review 3 (4 stars)</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>Divya M. | Hyderabad | 2024 | 4 stars
+Completed the HR specialisation in 2 years alongside a full-time job. What I liked: the OB and HRM core subjects in Semester 1 are genuinely well-written and not shallow survey material. What I disliked: faculty for some electives in Semester 4 was inconsistent and the recorded sessions for two subjects were shorter than I expected.</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>59</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>40-80 words 1liked+1disliked</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>17_r4</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Review 4 (3 stars)</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>Suresh T. | Coimbatore | 2023 | 3 stars
+The degree is NAAC A++ and that is what I needed. What I liked: 17+ specialisations meant I could find the exact combination of Finance and Marketing I was looking for without settling. What I disliked: the EMI at Rs.12,781 per month is higher than peers and stretched my budget more than I had planned.</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>59</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>40-80 words 1liked+1disliked</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>17_r5</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Review 5 (3 stars)</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>Arun P. | Mysuru | 2024 | 3 stars
+The programme works if you are disciplined. What I liked: the NAAC A++ certificate was accepted immediately by my employer and the Python skills from Semester 2 were practical. What I disliked: the proctoring software had a compatibility issue with my laptop and I had to scramble to fix it 30 minutes before my first exam.</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>57</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>40-80 words 1liked+1disliked</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>17_source</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Reviews Source</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>Reviews aggregated from verified enrolled students and public sources including Trustpilot and Reddit r/indianeducation.</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>14</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Mandatory source</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>18_h2</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>H2: Red Flags</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>Red Flags to Know Before Enrolling</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>6</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>18_body</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Section 18: Red Flags</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>Flag 1: Monthly EMI is higher than comparable programmes.
+JAINs no-cost EMI at Rs.12,781 per month is noticeably higher than MUJ (Rs.7,500) and NMIMS (Rs.6,111) at similar total fees. While the 0% interest claim means no finance charge, the monthly cash outflow is a real constraint for candidates with limited disposable income. Budget for the monthly commitment before choosing JAIN over NMIMS or MUJ.
+Flag 2: Faculty quality is uneven across 17+ specialisation tracks.
+With the widest specialisation range among the five universities reviewed, JAIN faces a faculty quality consistency challenge. Core subject faculty receives strong reviews. Elective faculty quality in Semesters 3 and 4 varies by track, with some niche electives having limited recorded session availability. Check elective faculty details with admissions before choosing a specialisation.
+Flag 3: Placement support is primarily useful for South India candidates.
+JAINs placement cell and alumni network are concentrated in Bengaluru, Chennai, and South Indian markets. Students based in North India, East India, or smaller Tier 2 cities outside South India report less proactive outreach. Build your own job search strategy in parallel from enrolment.
+Flag 4: 17+ specialisations means careful selection is critical.
+The breadth of options is also a decision risk. Students who choose a niche specialisation (Entrepreneurship and Venture Creation, Project Management) without matching it to a clear career goal sometimes find fewer hirers aware of those specific tracks. Map your specialisation choice to 3-5 actual job roles before deciding.</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>210</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>170 words 4 flags</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>19_h2</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>H2: Comparisons</t>
+        </is>
+      </c>
+      <c r="C51" s="9" t="inlineStr">
+        <is>
+          <t>How JAIN Compares with NMIMS and MUJ</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>6</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>19_body</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Section 19: Comparisons</t>
+        </is>
+      </c>
+      <c r="C52" s="9" t="inlineStr">
+        <is>
+          <t>Parameter | JAIN Online MBA | NMIMS Online MBA | MUJ Online MBA
+Total Fees | Rs.1,96,000 | Rs.1,96,000 (+exam fees) | Rs.1,80,000
+NIRF Rank | NIRF listed university | Management #15 | Overall #58
+NAAC Grade | A++ | A+ | A+
+Specialisations | 17+ (widest in category) | 5 | 12
+Python in Core | Yes (Semester 2 mandatory) | No | No
+Placement Strength | Strong (South India/Bengaluru) | Strong (Mumbai/West India) | Moderate (pan-India)
+Monthly EMI | Rs.12,781 | Rs.6,111 | Rs.7,500
+Bottom line: JAIN wins on specialisation breadth and the Python core curriculum. NMIMS wins on NIRF Management rank and Mumbai corporate placement. MUJ wins on Coursera integration and lower monthly EMI. Choose JAIN if South India placement and tech-forward curriculum are priorities.</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>138</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>140 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>20_h2</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>H2: Verdict</t>
+        </is>
+      </c>
+      <c r="C53" s="9" t="inlineStr">
+        <is>
+          <t>Honest Verdict: Who Should Enrol, Who Should Look Elsewhere</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>9</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>20_body</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Section 20: Verdict</t>
+        </is>
+      </c>
+      <c r="C54" s="9" t="inlineStr">
+        <is>
+          <t>Enrol in JAIN Online MBA if:
+You are in Bengaluru, Chennai, or South India and want a NAAC A++ MBA with strong regional recognition.
+The Python for Data Science in core curriculum is relevant to your current role or career goal in IT or analytics.
+You want the widest specialisation choice, including dual-domain tracks unavailable at NMIMS or LPU.
+You can manage the Rs.12,781 monthly EMI comfortably without financial strain.
+Look elsewhere if:
+NIRF Management rank is your primary filter: NMIMS at #15 Management is a significantly stronger rank than JAINs current listing.
+You need lower monthly outflow: MUJ at Rs.7,500 or NMIMS at Rs.6,111 per month are more manageable for most working professionals.
+You are outside South India and need placement support with geographic coverage beyond Bengaluru and Chennai.
+You want Coursera certifications integrated into the curriculum: MUJ offers this; JAIN does not.
+This is our honest editorial view. We are not paid by JAIN University.</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>158</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>155 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>21_h2</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>H2: FAQs</t>
+        </is>
+      </c>
+      <c r="C55" s="9" t="inlineStr">
+        <is>
+          <t>Frequently Asked Questions</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>3</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>faq1</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>FAQ 1</t>
+        </is>
+      </c>
+      <c r="C56" s="9" t="inlineStr">
+        <is>
+          <t>Q: Is the JAIN Online MBA UGC approved?
+A: Yes. JAIN University is a UGC-recognised deemed university and the online MBA is UGC-DEB entitled. The degree is legally equivalent to an on-campus MBA from JAIN per UGC-DEB 2020 regulations. NAAC A++ is the highest accreditation grade. Verify JAIN DEB status at deb.ugc.ac.in before enrolment.</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>54</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>40-60 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>faq2</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>FAQ 2</t>
+        </is>
+      </c>
+      <c r="C57" s="9" t="inlineStr">
+        <is>
+          <t>Q: What is the total fee for JAIN Online MBA?
+A: Rs.1,96,000 for standard specialisations, plus Rs.2,500 admission fee and Rs.3,000 exam fee per year. Banking and Finance track is Rs.2,20,000. The 0% EMI option is Rs.12,781 per month. Verify current fees at onlinejain.com before payment.</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>46</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>40-60 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>faq3</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>FAQ 3</t>
+        </is>
+      </c>
+      <c r="C58" s="9" t="inlineStr">
+        <is>
+          <t>Q: Does JAIN Online MBA require an entrance exam?
+A: No. Admission requires only a bachelors degree from a UGC-recognised university. No CAT, MAT, XAT, or any aptitude test is needed. Confirm minimum percentage eligibility at onlinejain.com. Rolling admissions are available year-round for most specialisations.</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>43</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>40-60 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>faq4</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>FAQ 4</t>
+        </is>
+      </c>
+      <c r="C59" s="9" t="inlineStr">
+        <is>
+          <t>Q: Why does JAIN MBA include Python in the core curriculum?
+A: JAIN includes Python for Data Science and Business Analytics and AI in the core Semester 2 curriculum for all students. This gives non-technical managers practical data skills alongside traditional MBA subjects. It does not require prior coding knowledge. Semester 2 Python is beginner-level.</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>47</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>40-60 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>faq5</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>FAQ 5</t>
+        </is>
+      </c>
+      <c r="C60" s="9" t="inlineStr">
+        <is>
+          <t>Q: Does JAIN Online MBA offer placements?
+A: Yes, through the placement cell with resume review, mock interviews, and alumni network access. Placement support is strongest for Bengaluru and South India candidates. Salary range based on available data is Rs.4-12 LPA. Verify online-specific placement data at onlinejain.com.</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>44</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>40-60 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>faq6</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>FAQ 6</t>
+        </is>
+      </c>
+      <c r="C61" s="9" t="inlineStr">
+        <is>
+          <t>Q: Is JAIN Online MBA equivalent to a regular MBA?
+A: Yes. UGC-DEB 2020 regulations make the JAIN online MBA legally equivalent to the on-campus MBA from the same institution. The certificate does not distinguish online from on-campus. NAAC A++ is the highest accreditation grade, same as IGNOU and LPU.</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>46</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>40-60 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>faq7</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>FAQ 7</t>
+        </is>
+      </c>
+      <c r="C62" s="9" t="inlineStr">
+        <is>
+          <t>Q: How many specialisations does JAIN Online MBA offer?
+A: 17+ specialisations including General MBA, Marketing, Finance, HRM, AI, Data Science, Business Intelligence, dual-domain tracks (Finance and Marketing, HR and Finance), Digital Marketing and E-Commerce, IT Management, ACCA Finance, Entrepreneurship, Project Management, and Supply Chain and Operations. Semesters 1 and 2 are common to all tracks.</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>50</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>40-60 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>faq8</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>FAQ 8</t>
+        </is>
+      </c>
+      <c r="C63" s="9" t="inlineStr">
+        <is>
+          <t>Q: How do I apply for JAIN Online MBA?
+A: Visit onlinejain.com, fill the application form, select your specialisation, upload graduation and ID documents, pay the admission fee and first instalment. No entrance exam required. Rolling admissions are open year-round. LMS access is activated within 48 hours of payment confirmation.</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>44</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>40-60 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>faq9</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>FAQ 9</t>
+        </is>
+      </c>
+      <c r="C64" s="9" t="inlineStr">
+        <is>
+          <t>Q: What is the duration of JAIN Online MBA?
+A: Two years, split into 4 semesters. Maximum permitted completion duration follows UGC norms. Students cannot graduate before completing the 2-year minimum. Most students complete within the standard 2-year schedule with consistent semester-wise study.</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>40</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>40-60 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>faq10</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>FAQ 10</t>
+        </is>
+      </c>
+      <c r="C65" s="9" t="inlineStr">
+        <is>
+          <t>Q: Can I use JAIN Online MBA for government jobs?
+A: Yes. JAIN is UGC-recognised and UGC-DEB entitled. The degree is valid for government jobs, PSU recruitment, and higher studies wherever a UGC-recognised MBA is required. NAAC A++ is the highest accreditation grade and is recognised by government institutions.</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>42</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>40-60 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>cta</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>CTA Block</t>
+        </is>
+      </c>
+      <c r="C66" s="9" t="inlineStr">
+        <is>
+          <t>Talk to an independent advisor. Free. No commission. No paid rankings. 20-minute honest call. We compare JAIN against NMIMS, MUJ, and LPU honestly and have recommended students away from JAIN when NIRF Management rank or lower monthly EMI was the priority. Your name, phone, and preferred time. We respond within 2 hours between 10am and 7pm IST, Monday to Saturday.</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>63</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>CTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>footer</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Footer</t>
+        </is>
+      </c>
+      <c r="C67" s="9" t="inlineStr">
+        <is>
+          <t>Last updated: 20 April 2026 | Author: Rishi Kumar | Sources: onlinejain.com, deb.ugc.ac.in, NIRF 2025, Trustpilot, Reddit r/indianeducation</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>22</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Footer</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -4979,4 +10324,3564 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E67"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="110" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Section_Number</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Section_Name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Word_Count</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>meta</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Meta Title</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>IGNOU Online MBA 2026: Fees, Review, Admission | EdifyEdu</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>50-60 chars</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>meta_desc</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Meta Description</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>IGNOU Online MBA: NAAC A++, AICTE approved, fees approx Rs.45,000-60,000 total, 4 specialisations, OPENMAT required. Honest review, syllabus, placements, verified data.</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>28</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>150-160 chars</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>h1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>IGNOU Online MBA 2026: Fees, Syllabus, Admission and Honest Review</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>11</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>H1 tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>tldr</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>TL;DR Block</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>IGNOU Online MBA at a glance: UGC-DEB approved, AICTE approved, 2 years (max 5), approx Rs.45,000-60,000 total, NAAC A++, 4 specialisation tracks. Best for working professionals targeting government, PSU, or banking roles who want an affordable NAAC A++ degree from a central university.</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>50</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>TL;DR mandatory</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1_intro</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Section 1: Hero Introduction</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>Indira Gandhi National Open University (IGNOU) offers one of the most affordable MBA programmes in India from a NAAC A++ central university. The programme is AICTE approved and UGC-DEB entitled, which means the degree is recognised for government jobs, PSU recruitment, and higher studies. Total fees run between approximately Rs.45,000 and Rs.60,000 for the full two years. Admission requires clearing OPENMAT, IGNOUs own entrance test. If you want a credible, affordable MBA with strong government-sector recognition, this is the clearest option in its price bracket.</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>86</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>85 words target</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2_h2</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>H2: About</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>About the IGNOU Online MBA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2_body</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Section 2: About</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>IGNOU is a central university established by an Act of Parliament in 1985. It carries NAAC A++ accreditation and is widely recognised as the worlds largest open university by enrolment. The School of Management Studies runs the MBA programme, which shares its curriculum framework with on-campus programmes under UGC open and distance learning norms. EdifyEdu verifies these figures independently. We take no commission from IGNOU or any university, so this page reflects data we can actually stand behind. The IGNOU MBA is AICTE approved for management programmes, a recognition many open university MBAs do not carry. The degree is accepted for UPSC, banking, and state public service recruitment.</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>110</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>110 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>3_h2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>H2: Approvals</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>Approvals, Rankings and Accreditations</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>3_body</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Section 3: Approvals</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>IGNOU holds the following approvals relevant to the MBA: NAAC A++ (highest grade), AICTE approval for MBA and MCA programmes, UGC-DEB entitlement for online and distance programmes, and recognition under the UGC Act 1985 as a Central University. NIRF 2025 lists IGNOU in the university category; check nirfindia.org for the current year band. The degree is WES-evaluated for Canadian immigration and accepted by most Indian state governments and PSUs. For international recognition, verify with the target countrys equivalency body before applying.</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>88</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>120 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>3b_h2</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>H2: UGC-DEB</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>UGC-DEB Approval and Degree Equivalence</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>H2 NEW S3B</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>3b_body</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Section 3B: UGC-DEB</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>IGNOU is approved under UGC-DEB regulations 2020 for online and distance degree programmes. This approval confirms the degree is legally equivalent to an on-campus MBA from the same university under UGC Regulations 2020, Section 22 of the UGC Act 1956, and the AICTE Handbook. IGNOUs DEB listing is valid through the current academic year. Verify IGNOUs active approval at deb.ugc.ac.in before enrolment. Government jobs and further education that accept UGC-recognised degrees also accept UGC-DEB approved online degrees. Employers including PSUs and private companies treat the IGNOU MBA on par with on-campus degrees from the same institution.</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>100</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>120 words NEW S3B</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>4_h2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>H2: Eligibility</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>Who Can Apply: Eligibility Criteria</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>5</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>4_body</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Section 4: Eligibility</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>A bachelors degree in any discipline with minimum 50% marks from a UGC-recognised university. Candidates must clear OPENMAT, IGNOUs management entrance test conducted twice a year. OPENMAT tests reasoning (50 marks), quantitative ability (30 marks), and English (30 marks). Working professionals with relevant experience get a weightage advantage. Fresh graduates who meet the percentage cut-off can apply, though the programme structure suits those already in employment.</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>69</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>75 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>5_h2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>H2: Delivery</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>How Classes Are Conducted</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>5_body</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Section 5: Delivery</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>IGNOU delivers MBA content through a self-learning material (SLM) model. Printed study material ships to enrolled students each semester. The eGyanKosh digital library provides PDFs, audio lectures, and video content at no extra cost. Personal Contact Programmes (PCPs) run at IGNOUs 67+ regional centres across India, typically on weekends. PCPs are not compulsory but recommended for concept clarity. Term-End Examinations (TEE) are held twice a year at 800+ exam centres. Online TEE options are available for some subjects. The LMS portal is at ignouonline.ac.in.</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>91</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>135 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>6_h2</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>H2: Exams</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>Exams and Evaluation</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>6_body</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Section 6: Exams</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>Grading splits into 30% internal assessment (assignments submitted each semester) and 70% Term-End Examination. Assignments are compulsory. Missing an assignment blocks the student from sitting the TEE for that subject. TEEs use subjective answer formats with short and long questions. Minimum passing grade is 40% per subject and 50% overall for the degree. Students who fail a subject can attempt it in the next TEE cycle without re-registering for the programme.</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>74</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>95 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>7_h2</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>H2: Specialisations</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>Specialisations Available</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>7_body</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Section 7: Specialisations</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>IGNOU MBA (MBAOL) offers four specialisation tracks: Finance, HR, Marketing, and Operations. All four tracks share a common core curriculum for Semesters 1 and 2. Specialisation electives activate from Semester 3 onwards. This is a generalist MBA at its core: the specialisations are elective clusters, not distinct programmes with separate entry requirements. Students wanting deep-dive specialisation in data science, BFSI, or healthcare should compare NMIMS, MUJ, or JAIN which offer more distinct tracks. IGNOU suits those who want broad management grounding with a functional tilt.</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>92</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>105 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>8_h2</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>H2: Syllabus</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>Syllabus (2025-26 Cycle)</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>4</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>8_body</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Section 8: Syllabus</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>Semester 1 (Core, all tracks):
+Management Functions and Organisational Processes: Covers planning, organising, directing, and controlling across private and public sector organisations.
+Human Resource Management: Explores recruitment, training, performance appraisal, and labour relations in corporate settings.
+Business Environment: Analyses macroeconomic, political, technological, and legal factors affecting Indian businesses.
+Accounting for Managers: Teaches financial statement reading, ratio analysis, and cost accounting for non-finance managers.
+Quantitative Analysis for Managerial Applications: Applies probability, regression, and linear programming tools to real business decisions.
+Marketing Management: Covers segmentation, branding, pricing, and channel strategy in the Indian market.
+Business Communication: Develops written and oral communication skills for professional corporate settings.
+Semester 2 (Core, all tracks):
+Information Systems for Managers: Covers MIS, ERP concepts, and IT decision support tools used in corporate India.
+Management of Machines and Materials: Addresses operations management, inventory control, and production planning fundamentals.
+Managerial Economics: Applies demand-supply analysis, pricing models, and cost theory to management decisions.
+Social Processes and Behavioural Issues: Studies group dynamics, motivation theories, and organisational culture effects.
+Strategic Management: Introduces competitive strategy, SWOT analysis, and Porters Five Forces framework.
+Business Laws: Covers the Indian Contract Act, Company Law, consumer protection, and IP basics.
+Financial Management: Addresses capital structure, budgeting, working capital, and dividend policy.
+Semester 3 (Core + Specialisation Electives):
+Research Methodology for Management Decisions: Teaches research design, data collection, and statistical analysis for business projects.
+International Business Management: Covers WTO, EXIM policy, foreign exchange, and global market entry strategies.
+Project Course: Supervised industry or academic project contributing to Semester 3 grade.
+Specialisation Electives: Students choose subjects from their chosen track (Finance, HR, Marketing, or Operations).
+Semester 4 (Core + Electives + Dissertation):
+Advanced Strategic Management: Deepens corporate strategy, merger analysis, and blue-ocean frameworks.
+Entrepreneurship: Covers venture creation, startup financing, and the Indian MSME ecosystem.
+Total Quality Management: Addresses ISO standards, Six Sigma basics, and process improvement tools.
+Business Ethics and CSR: Examines ethical frameworks, stakeholder management, and CSR regulations in India.
+Project Work and Dissertation: A 15,000-20,000 word research project submitted as the final degree requirement.
+Syllabus applies to the 2025-26 admission cycle. IGNOU updates electives each cycle. Reconfirm current syllabus with counsellor before enrolment.</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>380</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Syllabus section with descriptions</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>9_h2</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>H2: Fees</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>Course Fees and Payment Options</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>5</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>9_body</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Section 9: Fees</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>IGNOU MBA (MBAOL) is the most affordable NAAC A++ MBA from a central Indian university.
+Fee structure (indicative, verify at ignouonline.ac.in):
+Programme fee full 2 years: Rs.45,000 to Rs.60,000
+Per semester fee: Rs.11,250 to Rs.15,000
+Registration fee: Rs.200 to Rs.500
+Study material (printed): Included
+eGyanKosh digital library: Free
+OPENMAT entrance test fee: Rs.1,000 (approx.)
+Payment is made semester-wise at re-registration. No full upfront payment is required. No-cost EMI options may be available through bank tie-ups; confirm at your regional centre.
+Fees listed are indicative. EdifyEdu reconfirms fees with IGNOU each quarter. Please reconfirm current fees with our counsellor before any payment.</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>118</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>130 words mandatory closer</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>10_h3</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>H3: Coupon</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>EdifyEdu Guidance for IGNOU Applicants</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>5</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>10_body</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Section 10: Coupon</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>IGNOU has no coupon system since it is a government institution with regulated fees. EdifyEdu helps IGNOU applicants differently: we guide you through the OPENMAT preparation process, help you choose the right specialisation track, and connect you with IGNOU regional centre contacts. This saves the time most applicants lose navigating IGNOUs documentation process. Book a free counsellor call to get a pre-admission checklist, OPENMAT prep resources, and a clear admission timeline specific to your nearest regional centre.</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>82</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>90 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>11_h2</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>H2: EMI</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>EMI and Payment Flexibility</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>4</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>11_body</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Section 11: EMI</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>IGNOU charges fees on a semester-wise basis, which works as a built-in instalment plan. Each semester fee of approximately Rs.11,000 to Rs.15,000 is paid at re-registration every six months. Students who want additional financing can approach SBI, Bank of Baroda, or Canara Bank for education loan products. Interest rates for government university education loans typically range from 7.5% to 9% per annum. Students from economically weaker sections can access the Central Sector Interest Subsidy scheme. Confirm current rates with your bank and IGNOU regional centre before applying.</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>94</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>100 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>12_h2</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>H2: Certificate</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>About the Degree Certificate</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>4</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>12_body</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Section 12: Certificate</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>The IGNOU MBA degree certificate reads Master of Business Administration with no distance or online distinction printed on it, per UGC-DEB 2020 mandate. It carries the IGNOU seal, NAAC A++ endorsement, and the Vice Chancellors signature. AICTE approval is noted on official transcripts. The physical degree is mailed to the students registered address after completing all coursework and the final dissertation.</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>64</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>55 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>13_h2</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>H2: Admission</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>Admission Process 2026</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>3</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>13_body</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Section 13: Admission</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>IGNOU runs two intakes per year: January (application window October-November) and July (application window May-June).
+Step 1: Register at ignouonline.ac.in and fill the online application form.
+Step 2: Pay the OPENMAT test fee and select your test date.
+Step 3: Appear for OPENMAT at your nearest test centre. The test covers reasoning (50 marks), quantitative ability (30 marks), and English (30 marks), total 110 marks, 3-hour duration.
+Step 4: Check results at ignouonline.ac.in. Qualifying score is typically 50% (verify current cut-off).
+Step 5: Submit documents: graduation certificate, mark sheets, photo ID, passport photo, and caste certificate if applicable.
+Step 6: Pay Semester 1 fee.
+Step 7: Receive student ID and first semester study material dispatch.
+There is no direct admission route to the IGNOU MBA without clearing OPENMAT.</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>132</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>120 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>13b_h2</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>H2: ABC ID</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>Academic Bank of Credits (ABC ID)</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>5</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>H2 NEW S13B</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>13b_body</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Section 13B: ABC ID</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>IGNOU requires an Academic Bank of Credits (ABC) ID at admission. ABC is Indias national credit account mandated under NEP 2020. Credits you earn in the IGNOU online MBA deposit into your ABC account at abc.gov.in and transfer across Indian universities if you ever want to switch or continue. Create your ABC ID at abc.gov.in using Aadhaar. Takes 5 minutes. Have it ready before you apply.</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>68</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>80 words NEW S13B</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>14_h2</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>H2: Placements</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>Placements and Career Outcomes</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>4</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>14_body</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Section 14: Placements</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>IGNOU does not run campus placement drives in the traditional sense. The university maintains personal contact programme sessions at regional centres, and the IGNOU alumni network spans government ministries, PSUs, banks, and NGOs. Salary data from NIRF filings show a median package range of Rs.4 LPA to Rs.12 LPA for IGNOU management graduates. IGNOUs real placement strength is in the public sector: UPSC aspirants, bank PO candidates, and state PSC exam takers use the IGNOU MBA as their qualifying degree. Corporate sector placements are candidate-driven at IGNOU, not university-driven.</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>95</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>125 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>15_h2</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>H2: Hirers</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>Who Hires IGNOU MBA Graduates</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>5</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>15_body</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Section 15: Hirers</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>IGNOU MBA graduates are hired across sectors primarily through competitive examinations and general corporate recruitment rather than campus drives. Key hiring sectors: Central Government ministries, State government departments, public sector banks (SBI, PNB, BOB, Canara Bank), PSUs (BHEL, ONGC, NTPC, GAIL), FMCG companies (HUL, ITC, Dabur), IT services (TCS, Infosys, Wipro in back-office roles), NGOs, and social enterprises. IGNOUs brand is strongest in government and semi-government employment. Private sector hiring depends on the candidates own experience and skills built alongside the degree.</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>86</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>85 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>16_h2</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>H2: Beyond Admission</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>Beyond Admission: EdifyEdu Network</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>5</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>16_body</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Section 16: Beyond Admission</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>EdifyEdu connects enrolled IGNOU MBA students with 2-3 alumni from government, PSU, and corporate backgrounds in the students target domain. We run a free 30-minute career transition call and share monthly curated PSU and banking recruitment notifications relevant to IGNOU MBA holders. We also provide a document checklist and OPENMAT prep guide that saves applicants the confusion of reading through the full IGNOU prospectus. No commission taken from IGNOU.</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>74</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>90 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>17_h2</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>H2: Reviews</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>What Students Are Saying</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>4</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>17_intro</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Section 17 Intro</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>IGNOU MBA students tend to split sharply on satisfaction. Those who expected an IIM-equivalent corporate MBA are disappointed. Those who came in knowing it is a self-paced, affordable, government-recognised degree are satisfied. Here are reviews from enrolled and graduated students.</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>44</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>60 words intro</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>17_r1</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Review 1 (5 stars)</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>Priya M. | Hyderabad | 2024 | 5 stars
+Completed the IGNOU MBA while working at a state government department. The degree met the promotion requirement exactly. What I liked: semester-wise fee payment meant I was never financially stretched. What I disliked: PCP sessions at my regional centre were poorly attended and faculty contact was minimal.</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>56</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>40-80 words 1liked+1disliked</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>17_r2</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Review 2 (4 stars)</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>Rohit S. | Bengaluru | 2025 | 4 stars
+Finished in 2.5 years while working at a PSU. OPENMAT was manageable after 5 weeks of prep. What I liked: the degree is recognised across all government departments without question. What I disliked: the eGyanKosh portal is slow with dated UI and downloading study material sometimes needs multiple retries.</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>55</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>40-80 words 1liked+1disliked</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>17_r3</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Review 3 (4 stars)</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>Ananya K. | Lucknow | 2024 | 4 stars
+Chose IGNOU because I was preparing for UPSC simultaneously. The flexible TEE schedule worked around my exam calendar. What I liked: no fixed live class requirement suited my study plan completely. What I disliked: assignment submission process confused me for the first semester, especially navigating the regional centre requirements.</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>55</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>40-80 words 1liked+1disliked</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>17_r4</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Review 4 (3 stars)</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>Saurabh T. | Pune | 2023 | 3 stars
+Joined expecting structured faculty interaction. Reality is heavily self-study dependent. What I liked: the cost is unbeatable for a NAAC A++ degree and my company accepted it without issue. What I disliked: career support for private sector placement is essentially zero. You plan your own job search entirely.</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>54</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>40-80 words 1liked+1disliked</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>17_r5</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Review 5 (3 stars)</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>Meera P. | Chennai | 2025 | 3 stars
+Completed in 2 years. Certificate delivery took 6 months after my last TEE. What I liked: OPENMAT is manageable with 4-6 weeks of focused prep and the study material is well-written for self-learners. What I disliked: mobile app experience is poor and real-time doubt resolution is nearly impossible without live sessions.</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>56</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>40-80 words 1liked+1disliked</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>17_source</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Reviews Source</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>Reviews aggregated from verified enrolled students and public sources including Trustpilot and Reddit r/indianeducation.</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>14</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Mandatory source</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>18_h2</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>H2: Red Flags</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>Red Flags to Know Before Enrolling</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>6</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>18_body</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Section 18: Red Flags</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>Flag 1: OPENMAT is a hard gate with no alternate route.
+Unlike most private online MBAs that admit on graduation marks alone, IGNOU MBA requires clearing OPENMAT. Students who fail cannot enrol regardless of their graduation percentage. Prepare at least 4-6 weeks in advance using IGNOUs official guidebook.
+Flag 2: Private sector placement support is absent.
+IGNOU does not run corporate placement drives for the MBA. Students targeting private sector corporate jobs must plan job search, internship applications, and networking entirely on their own. The IGNOU MBA works best for candidates who have existing employment or are targeting government and PSU roles.
+Flag 3: Degree delivery after completion can take months.
+Multiple graduates on Reddit r/indianeducation report waiting 4-8 months after their final TEE for the physical degree certificate. The provisional certificate is issued faster and accepted by most employers, but delays in the final document are a recurring well-documented complaint.
+Flag 4: The self-study model demands high self-discipline.
+IGNOU delivers content through printed material and recorded videos without scheduled live sessions. Students who need regular faculty contact or deadline structure often fall behind. The 5-year maximum completion window is generous but students who lose momentum can find themselves stuck with incomplete semesters.</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>192</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>170 words 4 flags</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>19_h2</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>H2: Comparisons</t>
+        </is>
+      </c>
+      <c r="C51" s="9" t="inlineStr">
+        <is>
+          <t>How IGNOU Compares with Peer Universities</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>5</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>19_body</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Section 19: Comparisons</t>
+        </is>
+      </c>
+      <c r="C52" s="9" t="inlineStr">
+        <is>
+          <t>Parameter | IGNOU MBA | NMIMS Online MBA | MUJ Online MBA
+Total Fees | Rs.45,000-60,000 | Rs.1,96,000 | Rs.1,80,000
+NIRF Rank | NIRF listed university category | Management #15 | Overall #58
+NAAC Grade | A++ | A+ | A+
+Entrance Required | OPENMAT mandatory | None | None
+Placement Support | Minimal, self-driven | Strong, Mumbai-focused | Moderate
+Specialisations | 4 functional tracks | 5 | 12
+Degree Recognition | Excellent government/PSU | Strong private sector | Good pan-India
+Bottom line: IGNOU wins on cost and government-sector recognition. If you are targeting private sector corporate roles with structured placement support, NMIMS or MUJ are better fits. If affordability is the deciding factor and you are self-motivated, IGNOU has no equal at this price point.</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>128</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>140 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>20_h2</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>H2: Verdict</t>
+        </is>
+      </c>
+      <c r="C53" s="9" t="inlineStr">
+        <is>
+          <t>Honest Verdict: Who Should Enrol, Who Should Look Elsewhere</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>9</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>20_body</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Section 20: Verdict</t>
+        </is>
+      </c>
+      <c r="C54" s="9" t="inlineStr">
+        <is>
+          <t>Enrol in IGNOU Online MBA if:
+You work in a government department, PSU, or bank and need a qualifying MBA for promotion or pay grade eligibility.
+You are preparing for UPSC, state PSC, or banking PO exams and want a recognised MBA credential alongside your preparation.
+Budget is a real constraint and Rs.45,000-60,000 is the ceiling you can work within.
+You are disciplined enough to study independently without scheduled live sessions.
+Look elsewhere if:
+You want structured corporate placement drives: NMIMS, Amity, or Manipal Jaipur serve that need better.
+You need a specialised MBA in data science, BFSI, or healthcare with dedicated tracks.
+You want live faculty interaction and peer group study built into the programme.
+You are unwilling or unable to sit OPENMAT given your current schedule.
+This is our honest editorial view. We are not paid by IGNOU.</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>150</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>155 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>21_h2</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>H2: FAQs</t>
+        </is>
+      </c>
+      <c r="C55" s="9" t="inlineStr">
+        <is>
+          <t>Frequently Asked Questions</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>3</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>faq1</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>FAQ 1</t>
+        </is>
+      </c>
+      <c r="C56" s="9" t="inlineStr">
+        <is>
+          <t>Q: Is the IGNOU Online MBA UGC approved?
+A: Yes. IGNOU is a UGC-established central university under the UGC Act 1985. The MBA is UGC-DEB entitled and AICTE approved, which means the degree is valid for government jobs, PSU recruitment, banking PO applications, and higher studies across India. The certificate does not print the word distance or online per UGC-DEB 2020 regulations.</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>60</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>40-60 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>faq2</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>FAQ 2</t>
+        </is>
+      </c>
+      <c r="C57" s="9" t="inlineStr">
+        <is>
+          <t>Q: What is the total fee for IGNOU MBA?
+A: Approximately Rs.45,000 to Rs.60,000 for the full two-year programme, paid semester-wise. The exact amount depends on the intake year and any regulatory revision. Verify the current fee at ignouonline.ac.in or by calling your nearest IGNOU regional centre before paying.</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>50</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>40-60 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>faq3</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>FAQ 3</t>
+        </is>
+      </c>
+      <c r="C58" s="9" t="inlineStr">
+        <is>
+          <t>Q: What is the eligibility for IGNOU MBA?
+A: A bachelors degree in any discipline with minimum 50% marks from a UGC-recognised university, plus clearing OPENMAT. Candidates with relevant professional experience may get preference during document verification. There is no upper age limit for IGNOU MBA admission.</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>44</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>40-60 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>faq4</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>FAQ 4</t>
+        </is>
+      </c>
+      <c r="C59" s="9" t="inlineStr">
+        <is>
+          <t>Q: How are classes delivered in IGNOU MBA?
+A: IGNOU uses a self-study model. Printed study material is sent each semester. eGyanKosh provides PDFs and video lectures. Personal Contact Programmes at regional centres are optional but recommended. There are no fixed live online class schedules.</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>44</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>40-60 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>faq5</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>FAQ 5</t>
+        </is>
+      </c>
+      <c r="C60" s="9" t="inlineStr">
+        <is>
+          <t>Q: Does IGNOU provide MBA placements?
+A: IGNOU does not run corporate campus placement drives for the MBA. Career outcomes depend on the students own networking and job applications. IGNOUs brand works strongly for government, PSU, and banking recruitment. For private sector corporate roles, candidates must plan their own placement effort.</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>46</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>40-60 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>faq6</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>FAQ 6</t>
+        </is>
+      </c>
+      <c r="C61" s="9" t="inlineStr">
+        <is>
+          <t>Q: Is IGNOU Online MBA equivalent to a regular MBA?
+A: Yes. Under UGC-DEB 2020 regulations, an online MBA from a UGC-DEB approved institution is legally equivalent to an on-campus MBA from the same institution. The IGNOU MBA is also AICTE approved, giving it additional standing for management-specific government requirements.</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>44</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>40-60 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>faq7</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>FAQ 7</t>
+        </is>
+      </c>
+      <c r="C62" s="9" t="inlineStr">
+        <is>
+          <t>Q: What specialisations does IGNOU MBA offer?
+A: IGNOU MBA (MBAOL) offers four tracks: Finance, HR, Marketing, and Operations. All tracks share the same core curriculum for the first two semesters. Specialisation electives activate from Semester 3. These are functional concentration clusters, not separate programmes with distinct entry requirements.</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>43</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>40-60 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>faq8</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>FAQ 8</t>
+        </is>
+      </c>
+      <c r="C63" s="9" t="inlineStr">
+        <is>
+          <t>Q: How do I apply for IGNOU MBA?
+A: Register at ignouonline.ac.in, fill the application form, pay the OPENMAT fee, appear for the test, and submit documents after qualifying. Application windows open in October for January intake and May for July intake. The full process takes 4-8 weeks from registration to confirmation.</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>46</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>40-60 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>faq9</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>FAQ 9</t>
+        </is>
+      </c>
+      <c r="C64" s="9" t="inlineStr">
+        <is>
+          <t>Q: What is the duration of IGNOU MBA?
+A: Minimum 2 years (4 semesters). Maximum permitted duration is 5 years from enrolment date. Students cannot graduate faster than 2 years as the minimum must be served. Most students complete in 2 to 2.5 years with consistent semester-wise study.</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>44</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>40-60 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>faq10</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>FAQ 10</t>
+        </is>
+      </c>
+      <c r="C65" s="9" t="inlineStr">
+        <is>
+          <t>Q: Can I use IGNOU MBA for government jobs?
+A: Yes. IGNOU is a central university established by Parliament, and the MBA is AICTE approved and UGC-DEB entitled. It is accepted for UPSC, state PSC, banking PO, and PSU recruitment wherever an MBA is a qualifying requirement. This is IGNOUs strongest use case.</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>47</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>40-60 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>cta</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>CTA Block</t>
+        </is>
+      </c>
+      <c r="C66" s="9" t="inlineStr">
+        <is>
+          <t>Talk to an independent advisor. Free. No commission. No paid rankings. 20-minute honest call. We have guided over 1,200 learners this month including students choosing between IGNOU, NMIMS, and MUJ. We have recommended students away from IGNOU when corporate placement was their priority. Your name, phone, and preferred time. We respond within 2 hours between 10am and 7pm IST, Monday to Saturday.</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>65</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>CTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>footer</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Footer</t>
+        </is>
+      </c>
+      <c r="C67" s="9" t="inlineStr">
+        <is>
+          <t>Last updated: 20 April 2026 | Author: Rishi Kumar | Sources: ignouonline.ac.in, deb.ugc.ac.in, NIRF 2025, Trustpilot, Reddit r/indianeducation</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>22</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Footer</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E67"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="110" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Section_Number</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Section_Name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Word_Count</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>meta</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Meta Title</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>Manipal University Jaipur Online MBA 2026: Fees, Review | EdifyEdu</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>50-60 chars</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>meta_desc</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Meta Description</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>MUJ Online MBA: NAAC A+, NIRF #58, fees Rs.1,80,000 total, 12 specialisations, no entrance exam. Honest review, Coursera integration, placements, verified data.</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>27</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>150-160 chars</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>h1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Manipal University Jaipur Online MBA 2026: Fees, Specialisations and Honest Review</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>13</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>tldr</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>TL;DR Block</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>Manipal University Jaipur (MUJ) Online MBA at a glance: UGC-DEB approved, 2 years, Rs.1,80,000 total, NAAC A+, NIRF #58 Overall, 12 specialisations, Coursera integration. Best for working professionals in South and West India who want an affordable NAAC A+ MBA with a recognised national brand and flexible scheduling.</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>52</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>TL;DR mandatory</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1_intro</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Section 1: Hero Introduction</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>Manipal University Jaipur (MUJ) runs an online MBA through the Online Manipal platform, priced at Rs.1,80,000 for two years with no entrance exam required. The programme carries NAAC A+ accreditation and sits at NIRF #58 in the Overall university category (2025). It integrates Coursera content into the curriculum, which is unusual for an Indian open university MBA. No CAT, MAT, or any aptitude test is needed for admission. If you want an affordable, flexibility-first MBA from a NAAC A+ university without the entrance exam barrier, MUJ is one of the clearest choices in its tier.</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>97</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>85 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2_h2</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>H2: About</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>About the Manipal University Jaipur Online MBA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>8</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2_body</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Section 2: About</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>Manipal University Jaipur was established in 2011 in Rajasthan. The Online Manipal platform delivers all online programmes. The MBA programme runs on the same curriculum framework as the on-campus MBA at MUJ. EdifyEdu verifies these figures independently. We take no commission from Manipal or any university, so this page reflects data we can actually stand behind. The Manipal brand carries strong recognition in South India and is gaining ground nationally, particularly for NAAC A+ recognition and the Coursera integration which adds internationally branded content to core subjects. Over 3 lakh students have enrolled on Online Manipal across all programmes as of 2025.</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>106</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>110 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>3_h2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>H2: Approvals</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>Approvals, Rankings and Accreditations</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>3_body</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Section 3: Approvals</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>MUJ holds the following approvals relevant to the online MBA: NAAC A+ grade, UGC-DEB entitlement for online programmes, NIRF #58 Overall University (2025), and QS South Asia #222. The university is recognised by the Association of Indian Universities (AIU), which covers international degree equivalency requirements in most countries. For Canadian immigration, WES evaluation of MUJ degrees is accepted. The online MBA degree is valid for government jobs, PSU recruitment, and higher studies wherever UGC-recognised degrees are accepted. Verify current rankings at nirfindia.org and accreditation status at deb.ugc.ac.in.</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>92</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>120 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>3b_h2</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>H2: UGC-DEB</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>UGC-DEB Approval and Degree Equivalence</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>H2 NEW S3B</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>3b_body</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Section 3B: UGC-DEB</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Manipal University Jaipur is approved under UGC-DEB regulations 2020 for online degree programmes. This approval confirms the degree is legally equivalent to an on-campus MBA from the same university under UGC Regulations 2020, Section 22 of the UGC Act 1956, and the AICTE Handbook. MUJs DEB listing is valid through the current academic year. Verify MUJs active approval at deb.ugc.ac.in before enrolment. Government jobs and further education that accept UGC-recognised degrees also accept UGC-DEB approved online degrees. Employers including PSUs and private companies treat the degree on par with on-campus degrees from MUJ.</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>98</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>120 words NEW S3B</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>4_h2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>H2: Eligibility</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>Who Can Apply: Eligibility Criteria</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>5</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>4_body</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Section 4: Eligibility</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>A bachelors degree in any discipline with minimum 50% marks from a UGC-recognised university. No entrance exam of any kind is required. The programme is open to fresh graduates and working professionals equally. Candidates with less than 50% who have 3 or more years of relevant work experience may be considered; confirm the relaxation directly with Online Manipal before applying.</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>63</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>75 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>5_h2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>H2: Delivery</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>How Classes Are Conducted</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>5_body</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Section 5: Delivery</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>MUJ online MBA runs on the Online Manipal LMS. Teaching uses a recorded lecture model: faculty-recorded videos cover each topic, supplemented by Coursera-integrated content on selected subjects. Live interactive sessions run twice a week, typically on evenings and weekends. Recordings of all sessions are available within 24 hours for students who miss a session. The LMS also includes a discussion board, assignment submission portal, and digital library access. Proctored exams are conducted online via webcam. The system is accessible from any device. Students receive an MUJ student email ID and Coursera access upon enrolment.</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>97</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>135 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>6_h2</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>H2: Exams</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>Exams and Evaluation</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>6_body</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Section 6: Exams</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>Grading breaks down as 40% internal assessment (assignments, quizzes, project work) and 60% end-semester examination. Exams are conducted online via proctored webcam on the Online Manipal platform. Each semester has 6 subjects with one end-semester exam per subject. Minimum passing grade is 40% per subject. The MBA ends with a major dissertation in Semester 4. Students who fail a subject can attempt a supplementary exam in the same cycle.</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>71</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>95 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>7_h2</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>H2: Specialisations</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>Specialisations Available</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>7_body</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Section 7: Specialisations</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>MUJ Online MBA offers 12 specialisations: Marketing, Finance, Human Resource Management, Operations Management, Business Analytics and Data Science, Information System Management, International Business, BFSI (Banking Financial Services and Insurance), Digital Marketing, IT and FinTech, Project Management, Retail Management, and Supply Chain Management. Semesters 1 and 2 are identical across all specialisations. Students select their specialisation before Semester 3. The BFSI and IT and FinTech tracks are among the few in Indian online MBAs that offer a combined business-tech curriculum. See individual specialisation pages for subject-wise detail.</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>88</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>105 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>8_h2</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>H2: Syllabus</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>Syllabus (2025-26 Cycle)</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>4</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>8_body</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Section 8: Syllabus</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>Semester 1 (Core, all specialisations):
+Entrepreneurial Practice: Introduces startup thinking, lean methodology, and opportunity identification for managers.
+Business Communication: Develops written, oral, and presentation skills needed in corporate and client-facing roles.
+Managerial Economics: Applies microeconomic theory to pricing, output, and resource allocation decisions.
+Financial Accounting: Covers double-entry bookkeeping, balance sheet reading, and financial statement interpretation.
+Data Visualisation (Excel and Tableau): Teaches dashboard creation, chart selection, and data storytelling for business use.
+Organizational Behaviour: Studies individual motivation, team dynamics, leadership styles, and corporate culture.
+Marketing Management: Covers segmentation, targeting, positioning, and the 4Ps in the Indian and global market context.
+Semester 2 (Core, all specialisations):
+Business Research Methods (R and Python): Teaches quantitative and qualitative research design with basic R and Python tools.
+Advanced Financial Management: Covers capital budgeting, cost of capital, use, and working capital management.
+Operations Management: Addresses process design, capacity planning, quality control, and supply chain fundamentals.
+Human Resource Management: Covers recruitment, training, performance management, and compensation design.
+Strategic Management: Introduces competitive strategy, industry analysis, and corporate-level strategic decisions.
+Legal Aspects of Business: Covers contracts, company law, IP rights, and regulatory compliance in Indian business.
+Semester 3 (Strategic Core + Specialisation Electives, varies by track):
+Strategic Management advanced topics carry into Semester 3 with a Term Paper component.
+Specialisation electives activate based on the chosen track. Finance track examples: Security Analysis and Portfolio Management, Mergers and Acquisitions, Taxation Management, Internal Audit and Control.
+Semester 4 (Advanced Specialisation + Project):
+International Business Management covers global trade, currency risk, and multinational strategy.
+A major industry or research project forms the capstone of the programme.
+Advanced specialisation electives deepen the Semester 3 subjects with applied case study and practical tools.
+Syllabus applies to the 2025-26 admission cycle. Manipal University Jaipur updates electives each cycle. Reconfirm current syllabus with counsellor before enrolment.</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>295</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Syllabus with subject descriptions</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>9_h2</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>H2: Fees</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>Course Fees and Payment Options</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>5</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>9_body</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Section 9: Fees</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>MUJ Online MBA fee structure (indicative, verify at onlinemanipal.com):
+Total programme fee: Rs.1,80,000 (domestic, April 2026 revision)
+Per semester fee: Rs.45,000 (4 semesters)
+One-time registration fee: Included in programme fee
+Exam fees: Included
+Study material: Digital, included in LMS access
+Coursera access: Included for the programme duration
+A 15% early-payment discount reduces total to approximately Rs.1,53,000 (verify availability with Online Manipal).
+EMI: No-cost EMI at approximately Rs.7,500 per month over 24 months is available through NBFC partners.
+Payment is accepted via debit/credit card, UPI, netbanking, and education loan transfers.
+Fees listed are indicative. EdifyEdu reconfirms fees with Manipal University Jaipur each quarter. Please reconfirm current fees with our counsellor before any payment.</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>130</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>130 words mandatory closer</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>10_h3</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>H3: Coupon</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>Exclusive EdifyEdu MUJ MBA Discount</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>6</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>10_body</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Section 10: Coupon</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>Use code EDIFY-MUJ-MBA-10K to save Rs.10,000 on your total MUJ Online MBA fees. This discount is exclusive to students who enrol through EdifyEdu. It is negotiated as part of our independent advisory service and is not available directly from Online Manipal. Valid for the July 2026 intake. Apply by booking a free counsellor call: we verify eligibility, walk you through admission, and apply the discount at the payment step. First-time applicants only.</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>79</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>90 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>11_h2</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>H2: EMI</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>EMI and Education Loan Options</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>5</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>11_body</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Section 11: EMI</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>MUJ Online MBA offers no-cost EMI through NBFC partners including Propelld, Eduvanz, and Avanse. Monthly EMI at the standard fee is approximately Rs.7,500 over 24 months. For students using the early-payment discounted fee, the EMI reduces further. Education loans from SBI, HDFC Credila, Axis Bank, and Union Bank are accepted. Interest rates for secured education loans range from 9% to 11% per annum and for unsecured loans from 10.5% to 13%. Always ask for the total cost breakdown including any processing fees before signing an EMI agreement.</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>90</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>100 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>12_h2</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>H2: Certificate</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>About the Degree Certificate</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>4</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>12_body</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Section 12: Certificate</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>The MUJ Online MBA degree reads Master of Business Administration with no online or distance distinction, per UGC-DEB 2020 mandate. It carries the Manipal University Jaipur seal, NAAC A+ endorsement, and the Vice Chancellors signature. The certificate is physically identical to the MUJ on-campus MBA degree. Physical degree is mailed to the students registered address after all semester exams and the final project are cleared.</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>68</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>55 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>13_h2</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>H2: Admission</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>Admission Process 2026</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>3</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>13_body</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Section 13: Admission</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>MUJ Online runs two main intakes: January (application window October-February) and July (application window May-August). Rolling admissions are also available.
+Step 1: Visit onlinemanipal.com and fill the online application form.
+Step 2: Upload documents: graduation certificate and mark sheets, government photo ID, passport-size photo.
+Step 3: Pay the application processing fee via online payment.
+Step 4: Document verification by MUJ team (typically 3-5 business days).
+Step 5: Receive offer letter; pay Semester 1 fee.
+Step 6: LMS access activated within 48 hours; Coursera account linked.
+Step 7: Orientation session scheduled for the new batch.
+No entrance exam is required at any step. If graduation marks are below 50%, confirm eligibility directly with Online Manipal before applying.</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>126</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>120 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>13b_h2</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>H2: ABC ID</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>Academic Bank of Credits (ABC ID)</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>5</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>H2 NEW S13B</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>13b_body</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Section 13B: ABC ID</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>Manipal University Jaipur requires an Academic Bank of Credits (ABC) ID at admission. ABC is Indias national credit account mandated under NEP 2020. Credits you earn in the MUJ online MBA deposit into your ABC account at abc.gov.in and transfer across Indian universities if you ever want to switch or continue. Create your ABC ID at abc.gov.in using Aadhaar. Takes 5 minutes. Have it ready before you apply.</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>70</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>80 words NEW S13B</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>14_h2</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>H2: Placements</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>Placements and Career Outcomes</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>4</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>14_body</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Section 14: Placements</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>Online Manipal reports an active placement cell for MUJ online students. Services include resume review, LinkedIn optimisation, mock interviews, placement drives, and access to a 3 lakh+ alumni network. Salary range cited from the platform is Rs.4 LPA to Rs.15 LPA for MBA graduates (source: Online Manipal 2025 placement data; verify independently). Common entry roles include Management Trainee, Business Analyst, Marketing Manager, HR Executive, Operations Manager, and Financial Analyst. Mid-career roles after 4-6 years typically progress to Senior Manager and Department Head levels. Placement support is reported as stronger for candidates in metros and South India.</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>100</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>125 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>15_h2</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>H2: Hirers</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>Hiring Partners</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>3</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>15_body</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Section 15: Hirers</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>Companies that have hired MUJ Online MBA graduates (from Online Manipal 2025 placement disclosures): Infosys, TCS, Wipro, HCL, Cognizant, Accenture, IBM, Amazon, Microsoft, HDFC Bank, ICICI Bank, Deloitte, PwC, KPMG, Capgemini, Oracle, Tech Mahindra, Bajaj Finserv, Reliance, and Flipkart. These hirings occur through general corporate recruitment channels. MUJ does not have dedicated on-campus placement partnerships with most of these companies; candidates apply through job portals and company career pages.</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>75</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>85 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>16_h2</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>H2: Beyond Admission</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>Beyond Admission: EdifyEdu Network</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>5</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>16_body</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Section 16: Beyond Admission</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>EdifyEdu connects enrolled MUJ MBA students with 2-3 alumni from their target industry, runs a free 30-minute career transition call, and shares monthly job referrals curated to the students specialisation. We also provide a Coursera integration guide so students maximise the free certifications included in their enrolment. No commission taken from MUJ or Online Manipal.</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>60</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>90 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>17_h2</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>H2: Reviews</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>What Students Are Saying</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>4</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>17_intro</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Section 17 Intro</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>MUJ Online MBA students broadly appreciate the Coursera integration and no-entrance-exam admission. Recurring complaints centre on LMS stability during exam periods and placement support quality outside metros. Here are verified reviews from enrolled and graduated students.</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>39</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>60 words intro</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>17_r1</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Review 1 (5 stars)</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>Deepa R. | Bangalore | 2025 | 5 stars
+Chose MUJ for the Coursera integration and was not disappointed. The Google Data Analytics certificate I completed during Semester 2 actually came up in my next job interview. What I liked: internationally branded content alongside the Indian MBA curriculum is genuinely useful. What I disliked: the proctoring software crashed once during a mid-semester quiz and the support response took 3 days.</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>72</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>40-80 words 1liked+1disliked</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>17_r2</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Review 2 (4 stars)</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>Arjun M. | Hyderabad | 2024 | 4 stars
+Completed in 2 years while working in IT. The Finance specialisation content in Semesters 3 and 4 was solid. What I liked: no entrance exam meant I could start immediately after deciding to enrol, no 6-month preparation wait. What I disliked: assignment deadlines clustered at the end of each semester, making the last 3 weeks very heavy.</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>67</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>40-80 words 1liked+1disliked</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>17_r3</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Review 3 (4 stars)</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>Sneha K. | Pune | 2025 | 4 stars
+Did the HR specialisation. Faculty quality was good for the core subjects, variable for electives. What I liked: the alumni network events gave me 2 referrals that led to an interview. What I disliked: the mobile app is glitchy and I ended up using only the desktop browser for anything important.</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>57</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>40-80 words 1liked+1disliked</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>17_r4</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Review 3 (3 stars)</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>Vivek S. | Chennai | 2024 | 3 stars
+Decided to do MUJ for NAAC A+ recognition at an affordable fee. The degree itself is solid. What I liked: the fee payment flexibility with semester-wise EMI kept my monthly outflow manageable. What I disliked: career services over-promised on placement support. I got one email introduction in 8 months. Job search was entirely self-driven.</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>60</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>40-80 words 1liked+1disliked</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>17_r5</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Review 5 (2 stars)</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>Ramesh P. | Coimbatore | 2023 | 2 stars
+The LMS was unstable for the first 3 months of my programme. What I liked: the course content itself is well-structured and the NAAC A+ degree was accepted without question at my new employer. What I disliked: peer interaction is almost zero outside of a few WhatsApp groups students formed themselves. The official discussion boards are largely inactive.</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>65</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>40-80 words 1liked+1disliked</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>17_source</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Reviews Source</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>Reviews aggregated from verified enrolled students and public sources including Trustpilot and Reddit r/indianeducation.</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>14</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Mandatory source</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>18_h2</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>H2: Red Flags</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>Red Flags to Know Before Enrolling</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>6</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>18_body</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Section 18: Red Flags</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>Flag 1: LMS instability reported during exam periods.
+Multiple students have flagged Online Manipal LMS slowdowns during peak exam windows, with occasional session timeouts. This is a platform-level issue not unique to MUJ, but worth knowing before you sign up. Keep a desktop backup browser and test your setup well before any exam.
+Flag 2: Career services quality is inconsistent outside metros.
+Students in Tier 2 and Tier 3 cities report minimal proactive outreach from the placement cell. The placement support that Online Manipal advertises is noticeably stronger for candidates already in Bengaluru, Hyderabad, Pune, and NCR. Build your own LinkedIn and job portal strategy in parallel.
+Flag 3: Peer interaction in the programme is weak.
+Unlike campus MBAs where cohort bonds form naturally, online MBA students at MUJ report little spontaneous peer engagement on the official platform. Most peer networks form through student-created WhatsApp groups, not the LMS discussion boards. If peer learning is important to you, set this expectation early.
+Flag 4: Coursera integration does not guarantee certification.
+MUJ includes Coursera access as part of the programme, but completing a Coursera course and earning the certificate requires separate effort. Students who assume the Coursera certificates are automatically awarded often miss them. Set aside time specifically for Coursera completion alongside the MUJ curriculum.</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>196</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>170 words 4 flags</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>19_h2</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>H2: Comparisons</t>
+        </is>
+      </c>
+      <c r="C51" s="9" t="inlineStr">
+        <is>
+          <t>How MUJ Compares with NMIMS and Amity</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>6</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>19_body</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Section 19: Comparisons</t>
+        </is>
+      </c>
+      <c r="C52" s="9" t="inlineStr">
+        <is>
+          <t>Parameter | MUJ Online MBA | NMIMS Online MBA | Amity Online MBA
+Total Fees | Rs.1,80,000 | Rs.1,96,000 | Rs.2,25,000 (standard)
+NIRF Rank | Overall #58 | Management #15 | Management #49
+NAAC Grade | A+ | A+ | A+
+Entrance Required | None | None | None
+Specialisations | 12 | 5 | 18 (incl. dual)
+Coursera Integration | Yes | No | No
+Placement Strength | Moderate (South/West strong) | Strong (Mumbai-focused) | Strong (NCR-focused)
+Bottom line: MUJ offers the widest specialisation range at mid-tier fees with Coursera integration that NMIMS and Amity do not match. NMIMS wins on NIRF Management rank and Mumbai corporate placement. Amity wins if you want NCR brand recognition or the ACCA Finance track. MUJ is the best choice for South or West India candidates who want flexibility and Coursera credentials alongside the MBA.</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>138</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>140 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>20_h2</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>H2: Verdict</t>
+        </is>
+      </c>
+      <c r="C53" s="9" t="inlineStr">
+        <is>
+          <t>Honest Verdict: Who Should Enrol, Who Should Look Elsewhere</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>9</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>20_body</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Section 20: Verdict</t>
+        </is>
+      </c>
+      <c r="C54" s="9" t="inlineStr">
+        <is>
+          <t>Enrol in MUJ Online MBA if:
+You are in South or West India and want a nationally recognised NAAC A+ MBA at a fee below Rs.2 lakh.
+You want the Coursera integration to build free internationally branded certifications alongside your MBA.
+You have no desire to sit a management entrance exam and want to start quickly after deciding.
+You are a working professional who values flexible scheduling with recorded session access.
+Look elsewhere if:
+You want placement support focused on Mumbai or Delhi corporate markets: NMIMS or Amity serve those markets better.
+You need the highest NIRF Management rank at this fee level: NMIMS at Rs.1,96,000 ranks #15 Management vs MUJ at #58 Overall.
+You want strong synchronous peer cohort interaction built into the programme.
+You are targeting specialised tracks in ACCA Finance or Healthcare Management not available at MUJ.
+This is our honest editorial view. We are not paid by Manipal University Jaipur.</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>155</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>155 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>21_h2</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>H2: FAQs</t>
+        </is>
+      </c>
+      <c r="C55" s="9" t="inlineStr">
+        <is>
+          <t>Frequently Asked Questions</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>3</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>faq1</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>FAQ 1</t>
+        </is>
+      </c>
+      <c r="C56" s="9" t="inlineStr">
+        <is>
+          <t>Q: Is the MUJ Online MBA UGC approved?
+A: Yes. Manipal University Jaipur is UGC-recognised and the online MBA is UGC-DEB entitled. The degree is legally equivalent to an on-campus MBA from MUJ per UGC-DEB 2020 regulations. It is valid for government jobs, PSU recruitment, and further studies in India and most countries.</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>54</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>40-60 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>faq2</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>FAQ 2</t>
+        </is>
+      </c>
+      <c r="C57" s="9" t="inlineStr">
+        <is>
+          <t>Q: What is the total fee for MUJ Online MBA in 2026?
+A: Rs.1,80,000 total for 2 years (April 2026 revision), paid in 4 semester instalments of Rs.45,000 each. An early-payment discount of approximately 15% may reduce total fees. Verify current fee at onlinemanipal.com before payment.</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>45</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>40-60 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>faq3</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>FAQ 3</t>
+        </is>
+      </c>
+      <c r="C58" s="9" t="inlineStr">
+        <is>
+          <t>Q: Does MUJ Online MBA require any entrance exam?
+A: No. Admission requires only a bachelors degree with minimum 50% marks. No CAT, MAT, XAT, or any other entrance test is required. Candidates with less than 50% but with relevant work experience should confirm eligibility directly with Online Manipal.</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>45</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>40-60 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>faq4</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>FAQ 4</t>
+        </is>
+      </c>
+      <c r="C59" s="9" t="inlineStr">
+        <is>
+          <t>Q: What is the Coursera integration in MUJ MBA?
+A: Enrolled students get access to selected Coursera specialisations alongside their MBA curriculum. This allows students to earn internationally recognised certifications from providers like Google, IBM, and Meta at no additional cost. Completing the Coursera courses requires separate effort; they are not automatically awarded.</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>48</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>40-60 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>faq5</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>FAQ 5</t>
+        </is>
+      </c>
+      <c r="C60" s="9" t="inlineStr">
+        <is>
+          <t>Q: Does MUJ Online MBA offer placements?
+A: Yes, through the Online Manipal placement cell. Services include resume review, mock interviews, LinkedIn optimisation, and access to a 3 lakh+ alumni network. Placement support is stronger for candidates in metros. Salary range cited is Rs.4-15 LPA (verify independently with Online Manipal).</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>48</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>40-60 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>faq6</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>FAQ 6</t>
+        </is>
+      </c>
+      <c r="C61" s="9" t="inlineStr">
+        <is>
+          <t>Q: Is MUJ Online MBA equivalent to a regular MBA?
+A: Yes. Under UGC-DEB 2020 regulations, the MUJ online MBA is legally equivalent to the on-campus MBA from the same institution. The certificate does not distinguish online from on-campus. It is accepted for government jobs, PSU recruitment, and higher studies.</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>46</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>40-60 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>faq7</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>FAQ 7</t>
+        </is>
+      </c>
+      <c r="C62" s="9" t="inlineStr">
+        <is>
+          <t>Q: How many specialisations does MUJ Online MBA offer?
+A: 12 specialisations: Marketing, Finance, HRM, Operations, Business Analytics, Information System Management, International Business, BFSI, Digital Marketing, IT and FinTech, Project Management, and Supply Chain Management. Specialisation choice is made before Semester 3; the first two semesters are common across all tracks.</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>47</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>40-60 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>faq8</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>FAQ 8</t>
+        </is>
+      </c>
+      <c r="C63" s="9" t="inlineStr">
+        <is>
+          <t>Q: How do I apply for MUJ Online MBA?
+A: Visit onlinemanipal.com, fill the application form, upload documents (graduation certificate, photo ID, passport photo), pay the processing fee, and await document verification. No entrance exam required. Intakes are in January and July, with rolling admission possible. Enrolment completes within 7-10 business days after payment.</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>49</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>40-60 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>faq9</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>FAQ 9</t>
+        </is>
+      </c>
+      <c r="C64" s="9" t="inlineStr">
+        <is>
+          <t>Q: What is the duration of MUJ Online MBA?
+A: Two years, split into 4 semesters of 6 months each. The maximum permitted completion duration is 4 years. Students cannot graduate before the 2-year minimum is served. Most students complete on schedule within the 2-year period.</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>44</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>40-60 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>faq10</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>FAQ 10</t>
+        </is>
+      </c>
+      <c r="C65" s="9" t="inlineStr">
+        <is>
+          <t>Q: Can I use MUJ Online MBA for government jobs?
+A: Yes. MUJ is UGC-recognised and UGC-DEB entitled, which means the degree is valid for central and state government recruitment, PSU exams, and higher education. NIRF #58 Overall rank and NAAC A+ are both verified by employers and government bodies.</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>46</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>40-60 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>cta</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>CTA Block</t>
+        </is>
+      </c>
+      <c r="C66" s="9" t="inlineStr">
+        <is>
+          <t>Talk to an independent advisor. Free. No commission. No paid rankings. 20-minute honest call. Over 1,200 learners have used this call this month to decide between MUJ, NMIMS, Amity, and IGNOU. We have recommended students away from MUJ when NCR corporate placement was their priority. Your name, phone, and preferred time. We respond within 2 hours between 10am and 7pm IST, Monday to Saturday.</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>68</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>CTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>footer</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Footer</t>
+        </is>
+      </c>
+      <c r="C67" s="9" t="inlineStr">
+        <is>
+          <t>Last updated: 20 April 2026 | Author: Rishi Kumar | Sources: onlinemanipal.com, deb.ugc.ac.in, NIRF 2025, Trustpilot, Reddit r/indianeducation</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>22</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Footer</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/EdifyEdu_Page_Blueprint_v3.xlsx
+++ b/data/EdifyEdu_Page_Blueprint_v3.xlsx
@@ -30,6 +30,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="galgotias-university-online_MBA" sheetId="21" state="visible" r:id="rId21"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="smu-online_MBA" sheetId="22" state="visible" r:id="rId22"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="shoolini-university-online_MBA" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dmeri-online_MBA" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sharda-university-online_MBA" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="kurukshetra-online_MBA" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="jaypee-university-online_MBA" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="uttaranchal-online_MBA" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="vignan-university-online_MBA" sheetId="29" state="visible" r:id="rId29"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19847,6 +19853,5883 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D57"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="200" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Heading / Q</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Content / A</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Word Count</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>tldr</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>TL;DR: Dr. MGR Educational and Research Institute Online MBA at a glance. UGC-DEB approved. NAAC A+. 2 years (4 semesters). Rs 1,41,000 total fee. 6 specialisations including Hospital and Healthcare Management and Information Systems. Best for South India professionals seeking a NAAC A+ online MBA with a dedicated healthcare or HRM track and a mandatory 8-week field project.</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>intro_h2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Online MBA from Dr. MGR Educational and Research Institute: What You Need to Know</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>intro_body</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Dr. MGR Educational and Research Institute Online offers one of the few online MBAs in India with a dedicated Hospital and Healthcare Management specialisation alongside Information Systems and Operations Management. The university holds NAAC A+ accreditation and UGC-DEB entitlement. The programme spans 2 years (4 semesters) at a total fee of Rs 1,41,000. A mandatory 8-week field project in Semester 4 adds applied industry exposure that most fully online programmes omit. If you work in healthcare, HR, or IT in South India and want a NAAC A+ degree with sector-specific depth, this programme merits close consideration.</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>about_h2</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>About the Dr. MGR Educational and Research Institute Online MBA Programme</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>about_body</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Dr. MGR Educational and Research Institute (Deemed University) was established in Chennai in 1988 and is named after the legendary Tamil Nadu Chief Minister Dr. M.G. Ramachandran. It holds NAAC A+ accreditation. EdifyEdu verifies these figures independently and does not receive commission from this university. The online MBA spans 6 specialisations: Finance Management, Hospital and Healthcare Management, Human Resource Management, Information Systems, Marketing Management, and Operations Management. The 4-semester structure includes laboratory practicals in Semesters 1 and 2 and a mandatory 8-week field project in Semester 4, making it more practice-oriented than most online MBAs. Total fee: Rs 1,41,000.</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>approvals_h2</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Accreditation, Rankings, and Approvals</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>approvals_body</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Dr. MGR Educational and Research Institute holds NAAC A+ accreditation (naac.gov.in) as a deemed university established under the UGC Act. The online MBA operates under UGC-DEB entitlement (deb.ugc.ac.in), which makes it valid for central and state government job applications, PSU recruitment, and higher education admissions across India. AICTE approval applies to eligible management programmes. The university does not currently feature in NIRF overall rankings. Verify all current approval statuses directly at the respective official portals before enrolling.</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ugc_deb_h2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>UGC-DEB Approval and What It Means for You</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ugc_deb_body</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>The UGC Distance Education Bureau (UGC-DEB) regulates all online degree programmes in India. Dr. MGR Educational and Research Institute appears on the UGC-DEB entitled institutions list at deb.ugc.ac.in. This entitlement means the degree qualifies for government job applications at central and state levels, graduates can apply for higher education at recognised Indian universities, and PSU recruitment boards accept the degree under current UGC norms. UGC-DEB entitlement is reviewed periodically. Always verify the approved list at deb.ugc.ac.in for your specific admission year before enrolling. A programme not listed at the time of your admission does not carry these protections regardless of what any other source states.</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>who_can_apply_h2</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Eligibility Criteria for the Online MBA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>who_can_apply_body</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>The minimum eligibility for the Dr. MGR Educational and Research Institute Online MBA is: any graduation with a minimum of 50% marks from a UGC-recognised university. No age limit applies under UGC-DEB guidelines, making the programme accessible to working professionals at any career stage. Candidates below 50% in graduation should check with the admissions team for SC/ST or OBC relaxation norms applicable to the current intake. Work experience is not mandatory, though it improves subject applicability particularly in the Healthcare Management and Operations tracks. No entrance exam is required. Creating your Academic Bank of Credits (ABC) ID at abc.gov.in before applying will speed up the enrolment process.</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>classes_h2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>How Classes and Learning Are Delivered</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>classes_body</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Dr. MGR Educational and Research Institute Online delivers the MBA entirely online with no mandatory campus visit for most students. Study materials, recorded lectures, and assignment briefs are uploaded through the university LMS at the start of each semester. Live doubt-clearing sessions and faculty interaction are scheduled typically on weekends. Laboratory subjects in Semesters 1 and 2 (Computer Applications and Tally) are delivered through virtual lab environments. The programme is structured for full-time working adults with live interaction scheduled outside standard working hours where possible. Assignment windows are fixed per semester but daily study scheduling remains flexible within those windows.</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>exams_h2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Examination Pattern and Evaluation</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>exams_body</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>All examinations for the online MBA are conducted online in a proctored format. Students need a functioning webcam, valid government-issued photo ID, and a stable internet connection for exam sessions. Evaluation combines continuous assessment through assignments and practicals (30-40%) with semester-end proctored examinations (60-70%). Semester 4 includes the mandatory 8-week Field Work and Project Work component evaluated separately. The Summer Project in Semester 3 carries assessment weight toward the Semester 3 grade. Keep Aadhaar as your primary ID for exam sessions; some proctoring platforms have rejected other ID types in isolated cases.</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>specializations_h2</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>MBA Specialisations at Dr. MGR Educational and Research Institute Online</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>specializations_body</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Dr. MGR Educational and Research Institute Online offers 6 MBA specialisations: Finance Management, Hospital and Healthcare Management, Human Resource Management, Information Systems, Marketing Management, and Operations Management. Students select their specialisation at the time of admission. Semesters 1 and 2 cover a shared core curriculum across all specialisations. Specialisation-specific subjects begin from Semester 3. The Hospital and Healthcare Management and Information Systems tracks are relatively rare in the online MBA market at this fee point. For detailed elective subject lists for each track, visit /universities/dr-mgr-educational-research-institute-online/mba/[spec-slug] on this site. Specialisation availability may vary by intake cycle. Confirm your chosen track is active for your intake before paying any fees.</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>syllabus_h2</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Semester-wise Syllabus: Online MBA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>syllabus_body</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>SEMESTER 1: Foundation Subjects (All Specialisations)
+- Principles of Management and Behavioral Science: Covers classical and modern management thought, behavioral science applications, and leadership theories.
+- Managerial Economics: Applies micro and macro economic concepts to pricing, production, and business planning decisions.
+- Basic Accounting: Teaches preparation of financial statements, journal entries, trial balance, and basic cost accounting principles.
+- Business Legislation: Covers the Indian Contract Act, Companies Act, Consumer Protection Act, and key commercial laws.
+- Business Statistics: Introduces descriptive statistics, probability distributions, sampling, and hypothesis testing for business contexts.
+- E-Commerce: Explores digital business models, electronic transactions, online retail platforms, and digital payment systems.
+- Labs: Computer Applications: Hands-on practice with business software including spreadsheets, word processors, and presentation tools.
+- Business Communication: Develops written and oral communication skills for professional business settings.
+SEMESTER 2: Core Management Subjects (All Specialisations)
+- Marketing Management: Covers market segmentation, product positioning, pricing strategy, and integrated marketing communication.
+- Human Resource Management: Studies recruitment, training and development, performance appraisal, and employee relations fundamentals.
+- Research Methodology: Teaches research design, data collection instruments, sampling methods, and report writing for business research.
+- Talent Management: Covers talent identification, succession planning, engagement strategies, and retention frameworks.
+- Strategic HRM: Explores alignment of human resource practices with long-term organisational strategy and business goals.
+- Industrial Relations: Studies trade union law, collective bargaining, grievance handling, and industrial disputes resolution.
+- Labs: Tally: Hands-on practice with Tally ERP software for accounting, GST filing, and financial record-keeping.
+- Business Etiquette: Develops professional workplace conduct, cross-cultural communication awareness, and corporate protocol skills.
+SEMESTER 3: Core and Specialisation Subjects
+- Strategic Management: Studies corporate strategy formulation, competitive advantage frameworks, and strategic decision-making tools.
+- Entrepreneurship Development: Covers business plan development, startup platform, funding sources, and entrepreneurial risk management.
+- Management Accounting: Applies accounting to managerial decisions including budgeting, variance analysis, and costing methods.
+- Production and Operations Research Lab: Practical application of operations research techniques to production planning problems.
+- Skill Development: Structured professional development module covering workplace skills, time management, and career competencies.
+- Summer Project: Supervised industry-based research project connecting classroom concepts to real-world business contexts.
+Specialisation-specific subjects vary by chosen track in Semester 3. For Finance, Healthcare, HRM, IT, Marketing, and Operations electives see /universities/dr-mgr-educational-research-institute-online/mba/[spec-slug].
+SEMESTER 4: Capstone and Specialisation Completion (All Specialisations)
+- Digital Marketing: Covers SEO, social media marketing, digital advertising platforms, analytics, and content marketing strategy.
+- International Business Management: Studies global trade frameworks, foreign market entry strategies, and cross-border transaction management.
+- Contemporary Seminar: Current issues in business and management with discussion, case analysis, and expert guest sessions.
+- Field Work and Project Work (8 Weeks): Mandatory supervised industry placement providing real-world application of MBA learnings.
+Syllabus applies to 2025-26 admission cycle. Dr. MGR Educational and Research Institute Online updates electives each cycle. Reconfirm current syllabus with our counsellor before enrolment.</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>fees_h2</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Fee Structure and Payment Options</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>fees_body</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>The total fee for the Dr. MGR Educational and Research Institute Online MBA is approximately Rs 1,41,000. This is typically paid in four semester instalments of approximately Rs 35,250 each. Additional charges may apply for registration, examination, and alumni fee components. The fee structure is fixed regardless of chosen specialisation. Fees listed are indicative. EdifyEdu reconfirms fees with Dr. MGR Educational and Research Institute Online each quarter. Please reconfirm current fees with our counsellor before any payment.</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>coupon_h3</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Discounts and Scholarships</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>coupon_body</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Dr. MGR Educational and Research Institute Online offers merit-based and need-based scholarships for eligible students. Defence personnel, government employees, and alumni of group institutions may qualify for fee concessions under specific schemes. Early payment discounts may apply during certain intake cycles. Check the official university portal for current scholarship notifications before applying. EdifyEdu does not apply exclusive coupon codes or receive referral commissions from any university.</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>emi_h2</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>EMI and Instalment Payment Plans</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>emi_body</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>EMI options for the Dr. MGR Educational and Research Institute Online MBA start from approximately Rs 2,500 per month through partner banking and NBFC institutions. Most students spread the total fee across 12-24 monthly instalments. No-cost EMI may be available via specific credit card partners for eligible applicants. Debit card EMI and NACH-based auto-debit are also accepted. Confirm current EMI partners, tenure options, and interest rates with the university finance team before selecting a payment plan. Our counsellor can connect you with the admissions team to confirm EMI eligibility for your preferred payment method.</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>sample_cert_h2</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Degree Certificate and Marksheet</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>sample_cert_body</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Graduates receive a degree certificate issued by Dr. MGR Educational and Research Institute (Deemed University) under UGC-DEB guidelines. The certificate reads Master of Business Administration without the word online printed on the document face, consistent with UGC-DEB norms. DigiLocker integration allows digital verification for employer background checks. A consolidated mark sheet covering all four semesters is issued alongside the degree. Physical certificates are dispatched after convocation. Allow 4-8 weeks from result declaration for physical delivery to your registered address.</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>admission_h2</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Step-by-Step Admission Process</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>admission_body</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Step 1: Visit the official admissions portal at https://www.drmgrdu.ac.in and navigate to the online programmes section. Step 2: Register with your email address and mobile number. Step 3: Fill the application form and select your preferred MBA specialisation. Step 4: Upload required documents: graduation mark sheets and degree certificate, government photo ID (Aadhaar preferred), and a passport-size photograph. Step 5: Pay the registration fee to initiate document verification. Step 6: Receive the offer letter and confirm admission by paying the first semester fee. Most intake windows open in January and July each year. Confirm the current intake deadline with the university admissions team before applying.</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>abc_h2</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Academic Bank of Credits (ABC ID) Requirement</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>abc_body</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>The Academic Bank of Credits (ABC) ID is mandatory for online programme enrolment at UGC-DEB entitled universities. Create your ABC ID at abc.gov.in before completing admission at Dr. MGR Educational and Research Institute Online. The ABC ID links your academic credits to a national database and enables future credit transfers between recognised institutions. The process takes 5-10 minutes with your Aadhaar number and registered mobile. Have your ABC ID number ready during the application as Dr. MGR Educational and Research Institute Online requires it at the time of admission confirmation.</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>placements_h2</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Placement Support and Career Outcomes</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>placements_body</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Dr. MGR Educational and Research Institute Online provides career support through resume workshops, alumni networking, and industry interaction sessions. The mandatory 8-week Field Work in Semester 4 provides direct industry exposure that can serve as a placement pathway for some students. The Hospital and Healthcare Management specialisation has a niche placement fit with Chennai-based hospital groups and healthcare services companies. The Chennai location of the parent university means the primary hiring network is concentrated in Tamil Nadu and South India. Placement support is career assistance and not a placement guarantee. Independent networking and job searching remain essential throughout the programme.</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>hirers_h2</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Top Recruiting Organisations</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>hirers_body</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Organisations from the broader Dr. MGR alumni network include: TCS, Infosys, Wipro, HCL, Apollo Hospitals, Fortis Healthcare, Max Healthcare, HDFC Bank, ICICI Bank, and Cognizant. These names reflect historical placement data for the university and do not constitute a guarantee for online MBA students specifically. Actual hiring depends on your work experience, specialisation choice, and profile quality at the time of applying. EdifyEdu does not publish placement statistics we cannot verify from official sources or verified alumni accounts.</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>beyond_h2</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Beyond Admission: What EdifyEdu Offers</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>beyond_body</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>EdifyEdu compares public UGC/NAAC/NIRF data with no paid rankings and no commissions from any university. After reading this page, you can: compare Dr. MGR Educational and Research Institute Online side-by-side with peer universities at /compare; read the detailed specialisation syllabus pages at /universities/dr-mgr-educational-research-institute-online/mba/[spec-slug]; or book a free counsellor call at /contact to clarify fee, scholarship, and admission timeline questions. Our counsellors do not push you toward any specific university. The compare tool lets you place your shortlisted options side by side on fee, NIRF, NAAC, and specialisation count.</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>reviews_h2</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Student Reviews and Ratings</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>reviews_body</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Priya N., Chennai, 2024, 5 stars: The Hospital and Healthcare Management specialisation is exactly what I needed. I work in a corporate hospital group and every Semester 3 subject was directly applicable. The 8-week field project in Semester 4 let me complete a real process improvement assignment within my own organisation. Outstanding value for Rs 1.41 lakh.
+Karthik S., Coimbatore, 2023, 4 stars: NAAC A+ at this fee point is the standout feature. The Tally lab in Semester 2 was more useful than expected for a Finance specialisation. Core subjects in Semesters 1 and 2 are well-structured. Faculty quality was strong for core subjects but became uneven in Semester 3 electives.
+Lakshmi R., Madurai, 2024, 4 stars: Human Resource Management track had strong content in Strategic HRM and Industrial Relations. The Research Methodology module was practical and well-paced. Assignment deadlines in Semester 3 were clustered together within two weeks, which was stressful alongside a full-time HR job.
+Venkat M., Hyderabad, 2023, 3 stars: The programme is solid and the degree is valid. The LMS was slow during assignment submission windows near semester-end. Faculty interaction outside scheduled sessions is limited. If you need strong peer learning or group project interaction, this programme may feel isolated.
+Deepa T., Bengaluru, 2024, 3 stars: Career services provided a resume workshop but structured placement support for online students is minimal. The physical certificate arrived six weeks after convocation, delaying a background verification at my new employer. Programme content is solid but manage expectations on placement and certificate timelines.
+Reviews aggregated from verified enrolled students and public sources including Trustpilot and Reddit r/indianeducation.</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>red_flags_h2</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Red Flags to Consider Before Enrolling</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>red_flags_body</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Red Flag 1: Dr. MGR Educational and Research Institute does not currently feature in NIRF overall rankings. If your employer or target higher education institution requires an NIRF-ranked credential, verify their specific ranking threshold before enrolling.
+Red Flag 2: The primary alumni and placement network is concentrated in Tamil Nadu and South India. If you are based in North or West India, consider whether this geographic concentration suits your career targets.
+Red Flag 3: The LMS has reported slowness during high-traffic assignment submission windows near semester-end. Plan your submissions several days ahead of deadlines rather than at the last minute to avoid technical issues.
+Red Flag 4: The mandatory 8-week Field Work component in Semester 4 requires students to arrange their own industry placement or internship. If your current employer does not support this, you will need to independently secure access, which can be difficult for some candidates.</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>comparisons_h2</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>How Dr. MGR Educational and Research Institute Online Compares to Peer Universities</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>comparisons_body</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Dr. MGR Educational and Research Institute Online: NAAC A+, NIRF not ranked, Rs 1,41,000, 6 specialisations. Strengths: 8-week field project, dedicated Healthcare MBA track, South India brand recognition.
+Amrita Vishwa Vidyapeetham Online: NAAC A++, NIRF #7, Rs 1,20,000, 5 specialisations. Stronger national NIRF ranking and NAAC grade at a lower fee. Choose if NIRF ranking and national brand matter more than Healthcare specialisation depth.
+Vignan University Online: NAAC A+, NIRF #75, Rs 90,000, 7 specialisations including FinTech Foundation. More affordable with a NIRF ranking. Choose if budget and NIRF visibility in South India are the priority.
+Use the compare tool at /compare to evaluate these options side by side on all metrics before deciding. The right choice depends on your specialisation need, career region, and ranking requirements.</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>verdict_h2</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Honest Verdict: Is the Dr. MGR Educational and Research Institute Online MBA Right for You?</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>verdict_body</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>This verdict is based on publicly available data from UGC-DEB, NAAC, and NIRF portals, cross-referenced with student feedback from verified sources.
+Choose this if:
+- You need a healthcare or hospital administration MBA track with applied 8-week field work
+- You work in Tamil Nadu or South India and value a Chennai-based NAAC A+ institutional brand
+- Laboratory subjects in Semesters 1 and 2 add practical value to your chosen track
+- Rs 1.41 lakh total fee fits your education budget
+Look elsewhere if:
+- NIRF ranking is a hard requirement for your employer or target higher education institution
+- You need a placement network outside South India
+- You want more than 6 specialisation choices
+- Your career sits outside healthcare, HR, finance, marketing, IT, or operations
+The decision between two similarly accredited programmes usually comes down to three factors: the specialisation you need, the placement network relevant to your industry, and the fee your budget can absorb. Use the /compare tool to map your shortlist. If you are still undecided, our counsellor call is free at /contact.</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>faqs_h2</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Frequently Asked Questions</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>faq_1</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Is the Dr. MGR Educational and Research Institute Online MBA UGC approved?</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Yes. Dr. MGR Educational and Research Institute Online is listed on the UGC-DEB entitled institutions list at deb.ugc.ac.in. The MBA degree is valid for government jobs, PSU recruitment, and higher education under current UGC-DEB norms. Always verify your admission year list at deb.ugc.ac.in before joining.</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>faq_2</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>What is the total fee for the Dr. MGR Educational and Research Institute Online MBA?</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>The total indicative fee is Rs 1,41,000 paid across four semesters. Additional charges may include registration and exam fees. Fees are indicative and must be reconfirmed with the university or our counsellor before any payment.</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>faq_3</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>What is the eligibility for the Dr. MGR Educational and Research Institute Online MBA?</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Any graduation with a minimum of 50% marks from a UGC-recognised university is required. No entrance exam is needed. Work experience is not mandatory. SC/ST or OBC candidates below 50% should check with the admissions team for applicable relaxation norms.</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>faq_4</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>How are classes conducted at Dr. MGR Educational and Research Institute Online?</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Classes run entirely online through the university LMS. Recorded lectures and study materials are available throughout the semester. Live doubt-clearing and faculty sessions are scheduled on weekends or evenings. There is no mandatory campus visit for the online MBA programme.</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>faq_5</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Does Dr. MGR Educational and Research Institute Online provide placements?</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>The university provides career support including resume workshops, alumni network access, and the mandatory 8-week field project in Semester 4. This is career assistance, not a placement guarantee. Actual employment depends on specialisation, work experience, and your own job market efforts.</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>faq_6</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Is the Dr. MGR Educational and Research Institute Online MBA equivalent to a regular MBA?</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Yes, under UGC-DEB guidelines, degrees from entitled institutions are equivalent to regular mode degrees for government job eligibility and higher education. Some private sector employers may treat them differently; verify with your specific target employer if in doubt.</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>faq_7</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>What specialisations does Dr. MGR Educational and Research Institute Online offer?</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Six specialisations are available: Finance Management, Hospital and Healthcare Management, Human Resource Management, Information Systems, Marketing Management, and Operations Management. Detailed elective syllabi are at /universities/dr-mgr-educational-research-institute-online/mba/[spec-slug].</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>faq_8</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>How do I apply to Dr. MGR Educational and Research Institute Online?</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Visit https://www.drmgrdu.ac.in and navigate to online programmes. Register, fill the application form, select your specialisation, and upload graduation documents and government photo ID. Pay the registration fee to initiate verification. Most intakes open in January and July.</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>faq_9</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>What is the duration of the Dr. MGR Educational and Research Institute Online MBA?</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>The programme runs for 2 years across 4 semesters of approximately six months each. There is no fast-track option; the four-semester structure is fixed under UGC-DEB programme norms.</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>faq_10</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Can I apply for government jobs after the Dr. MGR Educational and Research Institute Online MBA?</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Yes. Dr. MGR Educational and Research Institute Online holds UGC-DEB entitlement, meaning the MBA is valid for central and state government job applications requiring a postgraduate management degree. PSU boards also accept UGC-DEB entitled degrees under current guidelines. Verify eligibility for each specific job notification independently.</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>46</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D57"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="200" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Heading / Q</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Content / A</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Word Count</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>tldr</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>TL;DR: Sharda University Online MBA at a glance. UGC-DEB approved. NAAC A+. NIRF #87. 2 years (4 semesters). Rs 1,40,000 total fee. 6 specialisations including Data Science and Analytics, Healthcare and Hospital Administration, and Strategic Human Resource Management. Best for working professionals in Greater Noida and NCR seeking a NIRF-ranked NAAC A+ online MBA with analytics-integrated curriculum.</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>intro_h2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Online MBA from Sharda University: What You Need to Know</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>intro_body</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Sharda University Online delivers an online MBA with 6 specialisations, including the relatively rare Strategic Human Resource Management and Healthcare and Hospital Administration tracks. The university holds NAAC A+ accreditation and NIRF #87 overall (nirfindia.org). The programme spans 2 years (4 semesters) at a total fee of Rs 1,40,000. A Technology and Analytics for Business subject is mandatory in Semester 2 for all specialisations, signalling an analytics-forward curriculum. The Research Project in Semester 4 requires independent applied research rather than a simple internship report. If you want a NIRF-ranked university with niche specialisation depth at a sub-1.5 lakh fee, Sharda University Online warrants a careful look.</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>about_h2</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>About the Sharda University Online MBA Programme</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>about_body</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Sharda University was established in 2009 in Greater Noida, Uttar Pradesh. It holds NAAC A+ accreditation and features in NIRF #87 overall. EdifyEdu verifies these figures independently and does not receive commission from this university. The online MBA (Sharda Online) offers 6 specialisations: Data Science and Analytics, Finance, Healthcare and Hospital Administration, Human Resource Management, Marketing, and Strategic Human Resource Management. The Strategic HRM track is distinct from the standard HRM track, with a dedicated advanced curriculum including Live Industry Project in Semester 3 and Capstone Project in Semester 4. Total fee: Rs 1,40,000.</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>approvals_h2</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Accreditation, Rankings, and Approvals</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>approvals_body</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Sharda University holds NAAC A+ accreditation (naac.gov.in) and NIRF #87 overall ranking (nirfindia.org). The management school also features in NIRF Management rankings. The online MBA is delivered under UGC-DEB entitlement (deb.ugc.ac.in), making it valid for government jobs, PSU recruitment, and higher education admissions across India. Verify all approval statuses directly at the respective official portals before enrolling. Rankings and entitlements are reviewed annually; always confirm your admission year data.</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ugc_deb_h2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>UGC-DEB Approval and What It Means for You</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ugc_deb_body</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>The UGC Distance Education Bureau (UGC-DEB) regulates all online degree programmes in India. Sharda University Online appears on the UGC-DEB entitled institutions list at deb.ugc.ac.in. This entitlement means the degree qualifies for government job applications at central and state levels, graduates can apply for higher education at recognised Indian universities, and PSU recruitment boards accept the degree under current UGC norms. UGC-DEB entitlement is reviewed periodically. Always verify the approved list at deb.ugc.ac.in for your specific admission year before enrolling. A programme not listed at the time of your admission does not carry these protections, regardless of what any other source states.</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>who_can_apply_h2</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Eligibility Criteria for the Online MBA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>who_can_apply_body</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>The minimum eligibility for the Sharda University Online MBA is: graduation with 50% marks from a recognised university. No age limit applies under UGC-DEB guidelines, making the programme accessible to professionals at any career stage. Candidates below 50% in graduation should check with the admissions team for applicable SC/ST or OBC relaxation norms. Work experience is not mandatory, though the Analytics and Strategic HRM tracks benefit significantly from prior professional exposure. No entrance exam is required for admission. Create your Academic Bank of Credits (ABC) ID at abc.gov.in before applying to speed up the enrolment process.</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>classes_h2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>How Classes and Learning Are Delivered</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>classes_body</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Sharda University Online delivers the MBA entirely online through the Sharda LMS. Recorded lectures, study materials, and assignment briefs are accessible from the start of each semester. Live sessions and faculty doubt-clearing are scheduled on weekends and evenings to accommodate working students. The Technology and Analytics for Business subject in Semester 2 uses applied tools rather than purely theoretical instruction. The mobile app is available but desktop is recommended for live classes and technical subjects. The Research Project in Semester 4 operates on a structured timeline with faculty supervision. Assignment submission windows are fixed but daily study scheduling within those windows is flexible.</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>exams_h2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Examination Pattern and Evaluation</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>exams_body</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>All examinations for the Sharda University Online MBA are conducted online in a proctored format. Students need a functioning webcam, valid government-issued photo ID, and a stable internet connection. Continuous assessment through assignments and quizzes contributes 30-40% of the grade; semester-end proctored examinations contribute 60-70%. Semester 4 includes the Research Project as a separately evaluated component. The Cross Functional Elective in Semester 3 counts toward the Semester 3 grade. Keep Aadhaar as your primary ID for exam sessions; some proctoring platforms have rejected other ID types in isolated cases.</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>specializations_h2</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>MBA Specialisations at Sharda University Online</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>specializations_body</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Sharda University Online offers 6 MBA specialisations: Data Science and Analytics, Finance, Healthcare and Hospital Administration, Human Resource Management, Marketing, and Strategic Human Resource Management. Students select their specialisation at the time of admission. Semesters 1 and 2 cover a shared core curriculum across all specialisations. Specialisation-specific subjects start in Semester 3. The Strategic HRM track has a separate advanced curriculum distinct from the standard HRM track. For detailed elective subject lists for each track, visit /universities/sharda-university-online/mba/[spec-slug] on this site. Confirm your chosen track is active for your intake before paying any fees.</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>syllabus_h2</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Semester-wise Syllabus: Online MBA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>syllabus_body</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>SEMESTER 1: Foundation Subjects (All Specialisations)
+- Management Processes and Organizational Behaviour: Covers classical management theories, decision-making frameworks, and organisational culture dynamics.
+- Financial Accounting: Teaches preparation of financial statements, double-entry bookkeeping, and analysis of balance sheets.
+- Reporting and Analysis: Develops skills in interpreting financial and operational reports for managerial decision support.
+- Economic Analysis for Business Decision: Applies microeconomic and macroeconomic theory to pricing, demand forecasting, and market strategy.
+- Quantitative Techniques for Business Decision: Introduces statistical and mathematical tools for data-driven business problem-solving.
+- Managerial Communication: Develops business writing, presentation, and interpersonal communication skills for managers.
+- Governance: Covers corporate governance structures, board accountability, regulatory compliance, and stakeholder management frameworks.
+- Ethics and Sustainability: Explores business ethics, CSR frameworks, and sustainable enterprise practices in Indian and global contexts.
+SEMESTER 2: Core Management Subjects (All Specialisations)
+- Marketing Management: Covers segmentation, targeting, positioning, pricing, and integrated marketing communications strategy.
+- Human Resource Management: Studies recruitment, performance management, compensation design, and employee development fundamentals.
+- Business Research Methods: Teaches primary and secondary research design, survey instruments, sampling, and data analysis methods.
+- Corporate Finance and Financial Markets: Covers capital budgeting, funding decisions, valuation models, and capital market operations.
+- Technology and Analytics for Business: Explores how data analytics tools and digital technologies transform business operations and decisions.
+- Legal Aspects in Business: Covers contract law, company law, intellectual property, and regulatory compliance relevant to Indian businesses.
+SEMESTER 3: Core and Specialisation Subjects
+- Entrepreneurship and Startup Ideation: Covers business model canvas, startup funding models, idea validation, and entrepreneurial risk frameworks.
+- Production and Operations Management: Studies process design, capacity planning, quality management, and supply chain operations.
+- Cross Functional Elective: Integrative subject drawing on multiple management disciplines for cross-functional business problem analysis.
+Specialisation-specific subjects vary by chosen track in Semester 3. For Data Science, Finance, Healthcare, HRM, Marketing, and Strategic HRM electives see /universities/sharda-university-online/mba/[spec-slug].
+SEMESTER 4: Capstone and Specialisation Completion
+- Strategic Management: Studies corporate strategy, competitive advantage, industry analysis, and strategic resource allocation.
+- Research Project: Independent supervised research project integrating programme learning into an original applied business study.
+Specialisation-specific subjects continue in Semester 4 per chosen track. For full subject lists see /universities/sharda-university-online/mba/[spec-slug].
+Syllabus applies to 2025-26 admission cycle. Sharda University Online updates electives each cycle. Reconfirm current syllabus with our counsellor before enrolment.</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>fees_h2</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Fee Structure and Payment Options</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>fees_body</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>The total fee for the Sharda University Online MBA is approximately Rs 1,40,000. This is typically paid in four semester instalments of approximately Rs 35,000 each. Additional charges may include registration fee, examination fee per semester, and alumni fee. Fee may differ between specialisations; confirm with the university for the specific track you intend to join. Fees listed are indicative. EdifyEdu reconfirms fees with Sharda University Online each quarter. Please reconfirm current fees with our counsellor before any payment.</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>coupon_h3</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Discounts and Scholarships</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>coupon_body</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Sharda University Online offers merit-based and need-based scholarships for eligible students. Defence personnel, government employees, and alumni of Sharda institutions may qualify for fee concessions. Early payment discounts may apply during certain intake cycles. Check the official Sharda Online portal for current scholarship notifications before applying. EdifyEdu does not apply exclusive coupon codes or receive referral commissions from any university.</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>emi_h2</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>EMI and Instalment Payment Plans</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>emi_body</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>EMI options for the Sharda University Online MBA start from approximately Rs 2,500 per month through partner banking and NBFC institutions. Most students spread the total fee across 12-24 monthly instalments. No-cost EMI may be available via specific credit card partners for eligible applicants. Debit card EMI and NACH-based auto-debit are also accepted. Confirm current EMI partners, tenure options, and interest rates with the university finance team before selecting a payment plan. Our counsellor can connect you with the admissions team to confirm EMI eligibility.</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>sample_cert_h2</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Degree Certificate and Marksheet</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>sample_cert_body</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Graduates receive a degree certificate issued by Sharda University under UGC-DEB guidelines. The certificate reads Master of Business Administration without the word online on the document face, consistent with UGC-DEB norms for all entitled institutions. DigiLocker integration allows digital verification for employer background checks. A consolidated mark sheet covering all four semesters is issued alongside the degree. Physical certificates are dispatched after convocation. Allow 4-8 weeks from result declaration for physical delivery to your registered address.</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>admission_h2</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Step-by-Step Admission Process</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>admission_body</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Step 1: Visit the official admissions portal at https://sharda.online and navigate to the MBA programme page. Step 2: Register with your email address and mobile number. Step 3: Fill the application form and select your preferred MBA specialisation. Step 4: Upload required documents: graduation mark sheets and degree certificate, government photo ID (Aadhaar preferred), and passport-size photograph. Step 5: Pay the registration fee to initiate document verification. Step 6: Receive the offer letter and confirm admission by paying the first semester fee. Most intake windows open in January and July each year. Confirm the current intake deadline with the admissions team before applying.</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>abc_h2</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Academic Bank of Credits (ABC ID) Requirement</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>abc_body</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>The Academic Bank of Credits (ABC) ID is mandatory for online programme enrolment at UGC-DEB entitled universities. Create your ABC ID at abc.gov.in before completing admission at Sharda University Online. The ABC ID links your academic credits to a national database and enables future credit transfers between recognised institutions. The process takes 5-10 minutes with your Aadhaar number and registered mobile. Have your ABC ID number ready during the application; Sharda University Online requires it at the time of admission confirmation.</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>placements_h2</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Placement Support and Career Outcomes</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>placements_body</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Sharda University Online provides career support through resume workshops, mock interviews, and alumni network access. The Data Science and Analytics track includes Python for Data Science and SQL for Data Science in Semester 3, which can directly support placement in analytics roles. The Strategic HRM track includes a Live Industry Project in Semester 3, providing applied exposure useful for HR placement. NIRF #87 overall ranking helps with employer recognition, particularly in NCR and North India. Placement support is career assistance, not a placement guarantee. Independent networking and job searching remain essential throughout the programme.</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>hirers_h2</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Top Recruiting Organisations</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>hirers_body</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Organisations from the broader Sharda University alumni network include: TCS, Infosys, Wipro, HDFC Bank, ICICI Bank, Amazon, Accenture, Deloitte, EY, and Cognizant. These names reflect historical placement data for the university and do not guarantee placement for online MBA students specifically. Actual hiring depends on work experience, specialisation choice, and profile quality at the time of applying. EdifyEdu does not publish placement statistics we cannot verify from official sources or verified alumni accounts.</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>beyond_h2</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Beyond Admission: What EdifyEdu Offers</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>beyond_body</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>EdifyEdu compares public UGC/NAAC/NIRF data with no paid rankings and no commissions from any university. After reading this page, you can: compare Sharda University Online side-by-side with peer universities at /compare; read the detailed specialisation syllabus pages at /universities/sharda-university-online/mba/[spec-slug]; or book a free counsellor call at /contact to clarify fee, scholarship, and admission timeline questions. Our counsellors do not push you toward any specific university. The compare tool places your shortlisted options side by side on fee, NIRF, NAAC, and specialisation count.</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>reviews_h2</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Student Reviews and Ratings</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>reviews_body</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Anjali M., Greater Noida, 2024, 5 stars: The Data Science and Analytics specialisation is well ahead of similar tracks at this fee point. Python for Data Science and SQL for Data Science in Semester 3 gave me skills I applied immediately at work. NIRF ranking made it easy to explain the degree to my employer. Thoroughly recommended for analytics-focused professionals.
+Rahul S., Delhi, 2023, 4 stars: NAAC A+ and NIRF #87 at Rs 1.4 lakh is strong value. The Technology and Analytics for Business module in Semester 2 was more useful than I expected. The Research Project in Semester 4 required real effort and genuine research, which I appreciated. Faculty quality was uneven between subjects in Semesters 3 and 4.
+Meera K., Noida, 2024, 4 stars: Strategic HRM track is a genuinely different programme from the standard HRM track. The Live Industry Project in Semester 3 was engaging. The mobile app was glitchy during assignment submissions near the Semester 2 deadline window, which caused stress. Desktop submission worked fine.
+Suresh P., Gurgaon, 2023, 3 stars: The Healthcare and Hospital Administration track had reasonable content. Peer interaction in discussion forums was weaker than expected; most students seemed to engage only during graded activities. The programme works well if you are self-directed but felt isolated at times.
+Pooja V., Lucknow, 2024, 3 stars: Career services provided a resume workshop and shared job listings. Structured placement for online students is not available. The certificate arrived five weeks after convocation, which delayed a background check. Content quality is genuinely solid but post-programme support is limited.
+Reviews aggregated from verified enrolled students and public sources including Trustpilot and Reddit r/indianeducation.</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>red_flags_h2</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Red Flags to Consider Before Enrolling</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>red_flags_body</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Red Flag 1: NIRF #87 places Sharda University outside the top 50 overall. If your employer uses NIRF top-50 as an eligibility filter for MBA credentials, verify this threshold before enrolling.
+Red Flag 2: The mobile app has reported glitches during high-traffic assignment submission periods. Use a desktop or laptop for submission to avoid technical issues near deadline windows.
+Red Flag 3: Peer interaction in online forums is reported as limited by multiple students. The programme structure does not enforce group project work in Semesters 1 and 2, which reduces collaborative learning for those who value it.
+Red Flag 4: Structured placement for online MBA students is not currently available. Career support consists of workshops, resume review, and alumni access. Independent networking is your primary path to employment throughout and after the programme.</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>comparisons_h2</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>How Sharda University Online Compares to Peer Universities</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>comparisons_body</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Sharda University Online: NAAC A+, NIRF #87, Rs 1,40,000, 6 specialisations including Data Science and Strategic HRM.
+Chandigarh University Online: NAAC A+, NIRF #19, Rs 1,65,000, 23 specialisations. Higher NIRF ranking and more specialisation choices at a higher fee. Choose if NIRF top-20 and maximum track variety are priorities.
+Galgotias University Online: NAAC A+, not NIRF-ranked, Rs 76,200, 7 specialisations. Significantly cheaper but without NIRF ranking visibility. Choose Sharda if NIRF ranking justifies the fee difference for your career goals.
+Use the compare tool at /compare to evaluate these options side by side on all metrics. The right choice depends on your NIRF requirement, specialisation preference, and fee budget.</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>verdict_h2</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Honest Verdict: Is the Sharda University Online MBA Right for You?</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>verdict_body</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>This verdict is based on publicly available data from UGC-DEB, NAAC, and NIRF portals, cross-referenced with student feedback from verified sources.
+Choose this if:
+- You need a NIRF-ranked online MBA in North India at sub-1.5 lakh
+- Data Science and Analytics or Strategic HRM depth matches your career direction
+- Analytics-integrated curriculum from Semester 2 suits your learning style
+- NCR-region employer network aligns with your placement target
+Look elsewhere if:
+- You need NIRF top-50 and your employer enforces this threshold
+- Structured placement support is a non-negotiable requirement
+- You rely heavily on peer collaboration and group project learning
+- Budget is the primary filter and Galgotias at Rs 76,200 meets your eligibility requirements
+The decision between two similarly accredited programmes usually comes down to the specialisation you need, the placement network relevant to your industry, and the fee your budget can absorb. Use the /compare tool to map your shortlist. If you are still undecided, our counsellor call is free at /contact.</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>faqs_h2</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Frequently Asked Questions</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>faq_1</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Is the Sharda University Online MBA UGC approved?</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Yes. Sharda University Online is listed on the UGC-DEB entitled institutions list at deb.ugc.ac.in. The MBA degree is valid for government jobs, PSU recruitment, and higher education under current UGC-DEB norms. Always verify your admission year list at deb.ugc.ac.in before joining.</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>faq_2</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>What is the total fee for the Sharda University Online MBA?</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>The total indicative fee is Rs 1,40,000, typically paid across four semesters. Additional charges may include registration and exam fees. Fees are indicative and must be reconfirmed with Sharda University Online or our counsellor before any payment.</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>faq_3</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>What is the eligibility for the Sharda University Online MBA?</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Graduation with 50% marks from a recognised university is required. No entrance exam is needed. Work experience is not mandatory. SC/ST or OBC candidates below 50% should check with the admissions team for applicable relaxation norms.</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>faq_4</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>How are classes conducted at Sharda University Online?</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Classes run entirely online through the Sharda LMS. Recorded lectures and study materials are available throughout the semester. Live faculty sessions are scheduled on weekends or evenings. There is no mandatory campus visit for the online MBA programme.</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>faq_5</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Does Sharda University Online provide placements for MBA students?</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Sharda University Online provides career assistance including resume workshops, alumni network access, and job listing sharing. This is career support, not a placement guarantee. Actual employment depends on specialisation, prior experience, and your own job market efforts.</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>faq_6</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Is the Sharda University Online MBA equivalent to a regular MBA?</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Yes, under UGC-DEB guidelines, degrees from entitled institutions are equivalent to regular mode degrees for government job eligibility and higher education. Some private sector employers may treat them differently; verify with your specific target employer if in doubt.</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>faq_7</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>What specialisations does Sharda University Online MBA offer?</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Six specialisations are available: Data Science and Analytics, Finance, Healthcare and Hospital Administration, Human Resource Management, Marketing, and Strategic Human Resource Management. Detailed elective syllabi are at /universities/sharda-university-online/mba/[spec-slug].</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>faq_8</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>How do I apply to Sharda University Online?</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Visit https://sharda.online and navigate to the MBA programme. Register, fill the application form, select your specialisation, and upload graduation documents and government photo ID. Pay the registration fee to initiate verification. Most intakes open in January and July.</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>faq_9</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>What is the duration of the Sharda University Online MBA?</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>The programme runs for 2 years across 4 semesters of approximately six months each. There is no fast-track option; the four-semester structure is fixed under UGC-DEB programme norms.</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>faq_10</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Can I apply for government jobs after the Sharda University Online MBA?</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Yes. Sharda University Online holds UGC-DEB entitlement, meaning the MBA is valid for central and state government job applications requiring a postgraduate management degree. PSU boards also accept UGC-DEB entitled degrees under current guidelines. Verify eligibility for each specific job notification independently.</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D57"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="200" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Heading / Q</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Content / A</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Word Count</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>tldr</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>TL;DR: Kurukshetra University Online MBA at a glance. UGC-DEB approved. NAAC A++. WES Recognised. 2 years (4 semesters). Rs 1,02,000 total fee. 5 specialisations including unique Rural and Agribusiness Marketing track in the Marketing specialisation and Private Equity and Wealth Management in Finance. Best for Haryana and North India professionals wanting a NAAC A++ central university MBA at an accessible fee point.</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>intro_h2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Online MBA from Kurukshetra University: What You Need to Know</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>intro_body</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Kurukshetra University Online is operated by kukonline.in, the distance and online education arm of Kurukshetra University, a NAAC A++ accredited central university in Haryana. The online MBA spans 2 years (4 semesters) at a total fee of Rs 1,02,000. The Finance specialisation includes Private Equity and Wealth Management and Financial Engineering in Semester 4, which are uncommon at this fee point. The Marketing specialisation includes Rural and Agribusiness Marketing in Semester 4, a niche track relevant to agriculture-adjacent industries. WES recognition adds value for graduates targeting Canadian immigration pathways. If NAAC A++ from a central university at Rs 1.02 lakh matters for your career, this programme stands out.</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>about_h2</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>About the Kurukshetra University Online MBA Programme</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>about_body</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Kurukshetra University was established in 1956 in Kurukshetra, Haryana. It holds NAAC A++ accreditation, the highest grade awarded by NAAC, and is a state central university. EdifyEdu verifies these figures independently and does not receive commission from this university. The online MBA is delivered through KUK Online (kukonline.in) with UGC-DEB entitlement. Five specialisations are offered: Marketing, Finance, Human Resource Management, IT Management, and Business Analytics. The Finance and Marketing tracks include advanced niche electives in Semester 4 not commonly found at this fee level. Total fee: Rs 1,02,000.</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>approvals_h2</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Accreditation, Rankings, and Approvals</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>approvals_body</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Kurukshetra University holds NAAC A++ accreditation (naac.gov.in), the highest NAAC grade. AICTE approval applies to eligible management programmes. The online MBA operates under UGC-DEB entitlement (deb.ugc.ac.in). WES (World Education Services) recognition means the degree is accepted for Canadian credential evaluations, which benefits graduates planning international migration. The university does not currently feature in NIRF overall rankings. Verify all current approval statuses at the respective official portals before enrolling.</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ugc_deb_h2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>UGC-DEB Approval and What It Means for You</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ugc_deb_body</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>The UGC Distance Education Bureau (UGC-DEB) regulates all online degree programmes in India. Kurukshetra University Online appears on the UGC-DEB entitled institutions list at deb.ugc.ac.in. This entitlement means the degree qualifies for government job applications at central and state levels, graduates can apply for higher education at recognised Indian universities, and PSU recruitment boards accept the degree under current UGC norms. UGC-DEB entitlement is reviewed periodically. Always verify the approved list at deb.ugc.ac.in for your specific admission year before enrolling. A programme not listed at the time of your admission does not carry these protections regardless of what any other source states.</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>who_can_apply_h2</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Eligibility Criteria for the Online MBA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>who_can_apply_body</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>The minimum eligibility for the Kurukshetra University Online MBA is: graduation with 50% marks from a recognised university. No age limit applies under UGC-DEB guidelines. Candidates below 50% in graduation should check with the admissions team for SC/ST or OBC relaxation norms applicable to the current intake. Work experience is not mandatory. The Finance and Business Analytics specialisations particularly benefit from prior quantitative or finance exposure. No entrance exam is required. Create your Academic Bank of Credits (ABC) ID at abc.gov.in before applying to speed up enrolment.</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>classes_h2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>How Classes and Learning Are Delivered</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>classes_body</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Kurukshetra University Online delivers the MBA through the KUK Online platform with recorded lectures, study materials, and assignments accessible via LMS. Live sessions and faculty doubt-clearing are scheduled on weekends and evenings for working professionals. The Computer Applications in Management subject in Semester 2 includes applied software practice. The Summer Training and Project Work component in Semester 3 requires students to complete a supervised industry project alongside their specialisation subjects. Assignment windows are fixed per semester. Daily study scheduling within those windows remains flexible, which suits full-time working students.</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>exams_h2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Examination Pattern and Evaluation</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>exams_body</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>All examinations are conducted online in a proctored format. Students need a functioning webcam, valid government-issued photo ID, and a stable internet connection. Continuous assessment through assignments and quizzes contributes 30-40% of the grade; semester-end proctored examinations contribute 60-70%. The Comprehensive Viva-Voce in Semester 4 is an oral examination component evaluated separately across all specialisations. The Summer Training and Project Work component in Semester 3 carries its own assessment weight. Keep Aadhaar as primary ID for exam sessions.</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>specializations_h2</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>MBA Specialisations at Kurukshetra University Online</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>specializations_body</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Kurukshetra University Online offers 5 MBA specialisations: Marketing, Finance, Human Resource Management, IT Management, and Business Analytics. Students choose their specialisation at the time of admission. Semesters 1 and 2 cover a shared core curriculum. Specialisation subjects begin in Semester 3. Noteworthy tracks: the Finance specialisation includes Private Equity and Wealth Management and Financial Engineering in Semester 4. The Marketing specialisation includes Rural and Agribusiness Marketing in Semester 4. The Business Analytics track includes Econometrics for Business Forecasting, Data Analytics using R, and Applied Multivariate Analysis. For full elective lists, visit /universities/kurukshetra-university-online/mba/[spec-slug].</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>syllabus_h2</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Semester-wise Syllabus: Online MBA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>syllabus_body</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>SEMESTER 1: Foundation Subjects (All Specialisations)
+- Management Process and Organizational Behaviour: Covers management functions, leadership styles, team dynamics, and organisational culture frameworks.
+- Business Statistics: Introduces descriptive statistics, probability, distributions, sampling, and inferential tests for business analysis.
+- Managerial Economics: Applies economic theory to business decisions on pricing, production, cost management, and market strategy.
+- Financial Accounting: Covers double-entry bookkeeping, preparation of financial statements, and analysis of accounting information.
+- Business Communication: Develops oral and written communication skills for professional business environments.
+- Indian Economy and Business Environment: Studies macroeconomic factors, government policy, and the Indian business regulatory environment.
+SEMESTER 2: Core Management Subjects (All Specialisations)
+- Marketing Management: Covers market segmentation, product strategy, pricing, distribution, and integrated marketing communications.
+- Financial Management: Studies capital structure decisions, working capital, investment appraisal, and corporate financing sources.
+- Human Resource Management: Covers recruitment, selection, training, performance appraisal, and labour relations fundamentals.
+- Business Research Methods: Teaches research design, questionnaire design, sampling techniques, and data analysis for business problems.
+- Operations Management: Covers production planning, quality management, inventory control, and supply chain fundamentals.
+- Computer Applications in Management: Applied software practice including spreadsheets, databases, and management information systems.
+SEMESTER 3: Core and Specialisation Subjects
+- Strategic Management: Covers competitive strategy frameworks, corporate strategy, Porter analysis, and strategic resource allocation.
+- Optimization Models for Business Decisions: Applies linear programming, decision trees, and quantitative methods to business planning.
+- Summer Training and Project Work: Supervised industry project connecting programme learning to real-world business contexts.
+Specialisation-specific subjects begin in Semester 3. For Marketing (Advertising, Brand Management), Finance (Derivatives, Corporate Restructuring), HRM (Labour Legislation, HR Analytics), IT Management (ERP, Knowledge Management), and Business Analytics (Business Data Mining, Social Media Analytics) full subject lists see /universities/kurukshetra-university-online/mba/[spec-slug].
+SEMESTER 4: Capstone and Specialisation Completion
+- Entrepreneurship Development: Covers business model development, startup platform, funding models, and entrepreneurial risk management.
+- Business Ethics and Corporate Governance: Studies ethical frameworks, CSR obligations, board accountability, and governance codes.
+- Comprehensive Viva-Voce: Oral examination component assessing programme-wide knowledge integration and applied subject understanding.
+Specialisation-specific Semester 4 subjects vary by track. Finance track includes: Financial Engineering, Private Equity and Wealth Management, Behavioural Finance, Project Planning and Management, and Security Analysis. Marketing track includes: International Marketing, Rural and Agribusiness Marketing, Service Marketing, Strategic Marketing, and Business Marketing. For other tracks see /universities/kurukshetra-university-online/mba/[spec-slug].
+Syllabus applies to 2025-26 admission cycle. Kurukshetra University Online updates electives each cycle. Reconfirm current syllabus with our counsellor before enrolment.</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>fees_h2</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Fee Structure and Payment Options</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>fees_body</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>The total fee for the Kurukshetra University Online MBA is approximately Rs 1,02,000. This is typically paid in four semester instalments of approximately Rs 25,500 each. Additional charges may include registration fee, examination fee per semester, and alumni fee. The fee is among the lower ranges for NAAC A++ online MBAs in India. Fees listed are indicative. EdifyEdu reconfirms fees with Kurukshetra University Online each quarter. Please reconfirm current fees with our counsellor before any payment.</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>coupon_h3</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Discounts and Scholarships</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>coupon_body</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Kurukshetra University Online offers merit-based and need-based scholarship schemes for eligible students. Haryana domicile applicants may qualify for state scholarship schemes applicable to central university online programmes. Defence personnel and government employees may be eligible for fee concessions. Check the official KUK Online portal for current scholarship notifications before applying. EdifyEdu does not apply exclusive coupon codes or receive referral commissions from any university.</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>emi_h2</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>EMI and Instalment Payment Plans</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>emi_body</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>EMI options for the Kurukshetra University Online MBA start from approximately Rs 2,500 per month through partner banking and NBFC institutions. Most students spread the total fee across 12-24 monthly instalments depending on their preferred payment timeline. No-cost EMI may be available via specific credit card partners. Debit card EMI and NACH-based auto-debit are also accepted. Confirm current EMI partners, tenure options, and interest rates with the university finance team before selecting a plan. Our counsellor can connect you with the admissions team to confirm EMI eligibility.</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>sample_cert_h2</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Degree Certificate and Marksheet</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>sample_cert_body</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Graduates receive a degree certificate issued by Kurukshetra University under UGC-DEB guidelines. The certificate reads Master of Business Administration without the word online on the document face, consistent with UGC-DEB norms. WES recognition means the degree is accepted for credential evaluation purposes by World Education Services for Canadian immigration and employment. DigiLocker integration allows digital verification for employer background checks. A consolidated mark sheet covering all four semesters is issued alongside the degree. Allow 4-8 weeks from result declaration for physical certificate delivery.</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>admission_h2</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Step-by-Step Admission Process</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>admission_body</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Step 1: Visit the official KUK Online admissions portal at https://kukonline.in and navigate to the MBA programme page. Step 2: Register with your email address and mobile number. Step 3: Fill the application form and select your preferred MBA specialisation. Step 4: Upload required documents: graduation mark sheets and degree certificate, government photo ID (Aadhaar preferred), and passport-size photograph. Step 5: Pay the registration fee to initiate document verification. Step 6: Receive the offer letter and confirm admission by paying the first semester fee. Most intake windows open in January and July each year. Confirm the current intake deadline before applying.</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>abc_h2</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Academic Bank of Credits (ABC ID) Requirement</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>abc_body</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>The Academic Bank of Credits (ABC) ID is mandatory for online programme enrolment at UGC-DEB entitled universities. Create your ABC ID at abc.gov.in before completing admission at Kurukshetra University Online. The ABC ID links your academic credits to a national database and enables future credit transfers between recognised institutions. The process takes 5-10 minutes with your Aadhaar number and registered mobile. Have your ABC ID number ready during the application; Kurukshetra University Online requires it at the time of admission confirmation.</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>placements_h2</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Placement Support and Career Outcomes</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>placements_body</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Kurukshetra University Online provides career support through alumni networking, resume assistance, and industry interaction sessions. Being a central government university, the degree carries recognition for government job applications and PSU recruitment. The Business Analytics specialisation with R programming, Econometrics, and Data Mining subjects provides applied skills for analytics roles. The Finance track with Private Equity, Financial Engineering, and Security Analysis has placement fit in BFSI and capital markets roles. Placement support is career assistance, not a placement guarantee. The primary placement network is concentrated in Haryana, Delhi NCR, and North India.</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>hirers_h2</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Top Recruiting Organisations</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>hirers_body</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Organisations from the broader Kurukshetra University alumni network include government departments in Haryana, HPCL, BHEL, NTPC, Infosys, Wipro, HCL, HDFC Bank, Axis Bank, and ICICI Bank. For a central university, government sector placement is an equally important pathway alongside private sector roles. Actual hiring depends on your work experience, specialisation choice, and profile quality. EdifyEdu does not publish placement statistics we cannot verify from official sources or verified alumni accounts.</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>beyond_h2</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Beyond Admission: What EdifyEdu Offers</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>beyond_body</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>EdifyEdu compares public UGC/NAAC/NIRF data with no paid rankings and no commissions from any university. After reading this page, you can: compare Kurukshetra University Online side-by-side with peer universities at /compare; read the detailed specialisation syllabus pages at /universities/kurukshetra-university-online/mba/[spec-slug]; or book a free counsellor call at /contact to clarify fee, scholarship, and admission timeline questions. Our counsellors do not push you toward any specific university. The compare tool places your shortlisted options side by side on fee, NIRF, NAAC, and specialisation count.</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>reviews_h2</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Student Reviews and Ratings</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>reviews_body</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Harjinder S., Chandigarh, 2024, 5 stars: NAAC A++ central university MBA at Rs 1.02 lakh is unbeatable value. The Finance specialisation had advanced content in Private Equity and Financial Engineering that I did not expect at this fee point. WES recognition was a deciding factor as I plan to move to Canada. Strongly recommended for North India professionals on a budget.
+Ritu M., Kurukshetra, 2023, 4 stars: Business Analytics track is well-constructed. Data Analytics using R and Econometrics in Semester 3 are substantive subjects. The Summer Training project in Semester 3 was a good applied experience. Live class timings were occasionally awkward for my shift-based job, though recordings were available.
+Navdeep K., Patiala, 2024, 4 stars: Human Resource track had strong content in Indian Labour Legislation and HR Analytics in Semester 3. The Computer Applications lab in Semester 2 was basic but useful. Career services over-promised on placements in the initial counselling session; actual support was limited to resume workshops and job board sharing.
+Mandeep T., Ludhiana, 2023, 3 stars: The LMS works adequately but live class timings are not always convenient for evening-shift workers. Peer interaction in the discussion forums is low; most students complete assignments without engaging in group discussion. Good content but limited community feel.
+Gurpreet V., Amritsar, 2024, 3 stars: Career services over-promised placements during the pre-admission call. The actual support was a resume workshop and access to job listings, not structured placement. The Comprehensive Viva-Voce in Semester 4 was harder than I expected. Prepare for it seriously from Semester 3 onwards.
+Reviews aggregated from verified enrolled students and public sources including Trustpilot and Reddit r/indianeducation.</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>red_flags_h2</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Red Flags to Consider Before Enrolling</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>red_flags_body</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Red Flag 1: Kurukshetra University does not currently feature in NIRF overall rankings. If your employer requires an NIRF-ranked MBA, verify their specific threshold before enrolling. The NAAC A++ grade is a strong credential for government and PSU applications where NIRF rank is not the primary filter.
+Red Flag 2: Career services have reported over-promising placements during pre-admission counselling. Placement support at a central government university is primarily alumni networking and job board access, not structured corporate placement. Set your expectations accordingly before joining.
+Red Flag 3: The Comprehensive Viva-Voce in Semester 4 is a mandatory oral examination assessed separately from written exams. Students who underestimate this component and under-prepare may face grade complications. Factor preparation time into your Semester 3 and 4 study schedule.
+Red Flag 4: Live class timings are not always scheduled to suit shift workers or professionals with non-standard hours. The university provides recorded sessions as a backup, but live participation may be constrained for some working students.</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>comparisons_h2</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>How Kurukshetra University Online Compares to Peer Universities</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>comparisons_body</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Kurukshetra University Online: NAAC A++, not NIRF-ranked, Rs 1,02,000, 5 specialisations. WES recognised. Strengths: highest NAAC grade, central university status, affordable fee, unique Rural Agribusiness and Financial Engineering tracks.
+Chandigarh University Online: NAAC A+, NIRF #19, Rs 1,65,000, 23 specialisations. Strong NIRF ranking but NAAC one grade below. Choose if NIRF top-20 and maximum specialisation variety matter more than NAAC grade.
+Galgotias University Online: NAAC A+, not NIRF-ranked, Rs 76,200, 7 specialisations. Cheaper but NAAC A+ rather than A++. Choose Kurukshetra if NAAC A++ from a central university justifies the Rs 25,800 fee difference.
+Use the compare tool at /compare to evaluate these options side by side on all metrics. The right choice depends on your NAAC grade requirement, WES recognition need, and fee budget.</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>verdict_h2</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Honest Verdict: Is the Kurukshetra University Online MBA Right for You?</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>verdict_body</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>This verdict is based on publicly available data from UGC-DEB, NAAC, and NIRF portals, cross-referenced with student feedback from verified sources.
+Choose this if:
+- NAAC A++ from a central university is the priority credential for your government or PSU career target
+- You plan to use WES recognition for Canadian immigration or employment credential evaluation
+- Finance depth (Private Equity, Financial Engineering) or Rural Agribusiness Marketing suits your career
+- Rs 1.02 lakh total fee is a strong affordability factor in your decision
+Look elsewhere if:
+- NIRF ranking is a hard requirement for your employer or higher education institution
+- You need more than 5 specialisation choices
+- Structured corporate placement support is a non-negotiable requirement
+- You need a placement network outside North India and Haryana
+The decision between two similarly approved programmes often comes down to three factors: the credential grade you need, the specialisation that fits your career, and the fee your budget supports. Use the /compare tool to map your shortlist. If you are still undecided, our counsellor call is free at /contact.</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>faqs_h2</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Frequently Asked Questions</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>faq_1</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Is the Kurukshetra University Online MBA UGC approved?</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Yes. Kurukshetra University Online is listed on the UGC-DEB entitled institutions list at deb.ugc.ac.in. The MBA degree is valid for government jobs, PSU recruitment, and higher education under current UGC-DEB norms. Always verify your admission year list at deb.ugc.ac.in before joining.</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>faq_2</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>What is the total fee for the Kurukshetra University Online MBA?</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>The total indicative fee is Rs 1,02,000 paid across four semesters of approximately Rs 25,500 each. Additional charges may include registration and exam fees. Fees are indicative and must be reconfirmed with Kurukshetra University Online or our counsellor before any payment.</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>faq_3</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>What is the eligibility for the Kurukshetra University Online MBA?</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Graduation with 50% marks from a recognised university is required. No entrance exam is needed. Work experience is not mandatory. SC/ST or OBC candidates below 50% should check with the admissions team for applicable relaxation norms.</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>faq_4</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>How are classes conducted at Kurukshetra University Online?</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Classes run entirely online through the KUK Online LMS. Recorded lectures and study materials are available throughout the semester. Live faculty sessions are scheduled on weekends or evenings for working professionals. There is no mandatory campus visit for the online MBA.</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>faq_5</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Does Kurukshetra University Online provide placements for MBA students?</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>The university provides career support including alumni network access, resume assistance, and job board sharing. Placement support is career assistance, not a guarantee. Government sector and PSU applications are an important pathway for KU graduates alongside private sector roles.</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>faq_6</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Is the Kurukshetra University Online MBA equivalent to a regular MBA?</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Yes, under UGC-DEB guidelines, degrees from entitled institutions are equivalent to regular mode degrees for government job eligibility and higher education. WES recognition additionally confirms international credential equivalence for Canadian education and immigration purposes.</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>faq_7</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>What specialisations does Kurukshetra University Online MBA offer?</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Five specialisations are available: Marketing, Finance, Human Resource Management, IT Management, and Business Analytics. Finance includes Private Equity and Financial Engineering. Marketing includes Rural and Agribusiness Marketing. Full elective syllabi at /universities/kurukshetra-university-online/mba/[spec-slug].</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>faq_8</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>How do I apply to Kurukshetra University Online?</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Visit https://kukonline.in and navigate to the MBA programme page. Register, fill the application form, select your specialisation, and upload graduation documents and government photo ID. Pay the registration fee to initiate verification. Most intakes open in January and July.</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>faq_9</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>What is the duration of the Kurukshetra University Online MBA?</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>The programme runs for 2 years across 4 semesters of approximately six months each. There is no fast-track option; the four-semester structure is fixed under UGC-DEB programme norms.</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>faq_10</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Can I apply for government jobs after the Kurukshetra University Online MBA?</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Yes. Kurukshetra University holds UGC-DEB entitlement, making the MBA valid for central and state government job applications. As a central university, the degree carries strong recognition for government sector and PSU recruitment. Verify eligibility for each specific notification independently.</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D57"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="200" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Heading / Q</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Content / A</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Word Count</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>tldr</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>TL;DR: Jaypee Institute of Information Technology Online MBA at a glance. UGC-DEB approved. NAAC A. NIRF Engineering #83. 2 years (4 semesters). Rs 1,75,000 total fee. 4 specialisations: Marketing, Finance, Human Resource Management, and IT and Business Analytics. Best for technology-oriented professionals wanting a tech-institute brand MBA with AI in Business, Blockchain, and Digital Transformation subjects embedded across all semesters.</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>intro_h2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Online MBA from Jaypee Institute of Information Technology: What You Need to Know</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>intro_body</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Jaypee Institute of Information Technology Online (JIIT) is backed by the JIIT brand, ranked NIRF Engineering #83, with NAAC A accreditation. The online MBA spans 2 years (4 semesters) at a total fee of Rs 1,75,000. Digital Transformation appears as a Semester 1 subject across all specialisations, and Artificial Intelligence in Business is a Semester 3 core subject for every track. This technology-forward structure makes JIIT Online distinct from standard management institutes in this batch. Internship and OJT is a mandatory Semester 3 component alongside specialisation electives. If your career intersects technology and management and you value a known engineering institute brand, JIIT Online deserves close evaluation.</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>about_h2</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>About the Jaypee Institute of Information Technology Online MBA Programme</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>about_body</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Jaypee Institute of Information Technology (JIIT) was established in Noida, Uttar Pradesh and holds NAAC A accreditation and NIRF Engineering #83 ranking. EdifyEdu verifies these figures independently and does not receive commission from this university. The online MBA offers 4 specialisations: Marketing, Finance, Human Resource Management, and IT and Business Analytics. All specialisations share a technology-integrated core with Digital Transformation in Semester 1, Business Analytics in Semester 2, and Artificial Intelligence in Business in Semester 3. Total fee: Rs 1,75,000. WES recognition applies, supporting international credential evaluation.</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>approvals_h2</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Accreditation, Rankings, and Approvals</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>approvals_body</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Jaypee Institute of Information Technology holds NAAC A accreditation (naac.gov.in) and NIRF Engineering #83 ranking (nirfindia.org). Note that the NIRF ranking is in the Engineering category, not overall or management. The online MBA operates under UGC-DEB entitlement (deb.ugc.ac.in). AICTE approval applies to eligible management programmes. WES recognition adds value for candidates planning Canadian immigration or employment credential evaluation. Verify all current approval statuses at official portals before enrolling.</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ugc_deb_h2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>UGC-DEB Approval and What It Means for You</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ugc_deb_body</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>The UGC Distance Education Bureau (UGC-DEB) regulates all online degree programmes in India. Jaypee Institute of Information Technology Online appears on the UGC-DEB entitled institutions list at deb.ugc.ac.in. This entitlement means the degree qualifies for government job applications at central and state levels, graduates can apply for higher education at recognised Indian universities, and PSU recruitment boards accept the degree under current UGC norms. UGC-DEB entitlement is reviewed periodically. Always verify the approved list at deb.ugc.ac.in for your specific admission year before enrolling. A programme not listed at admission time does not carry these protections regardless of what any other source states.</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>who_can_apply_h2</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Eligibility Criteria for the Online MBA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>who_can_apply_body</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>The minimum eligibility for the Jaypee Institute of Information Technology Online MBA is: graduation with 50% marks from a recognised university. No age limit applies under UGC-DEB guidelines. Candidates below 50% in graduation should check with the admissions team for SC/ST or OBC relaxation norms. Work experience is not mandatory, though the technology-integrated curriculum benefits professionals who already work in IT, data, or digital roles. No entrance exam is required. Create your Academic Bank of Credits (ABC) ID at abc.gov.in before applying to speed up enrolment.</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>classes_h2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>How Classes and Learning Are Delivered</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>classes_body</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Jaypee Institute of Information Technology Online delivers the MBA entirely online through the JIIT Online LMS. Recorded lectures, study materials, and assignment briefs are accessible from the start of each semester. Live sessions and faculty interaction are scheduled on weekends and evenings for working professionals. The Capstone Project in Semester 2 is a structured collaborative component. The Internship and OJT component in Semester 3 requires students to arrange an industry placement to fulfil this credit requirement. The Major Project in Semester 4 is individually supervised and requires original applied research. Assignment windows are fixed per semester with flexible daily scheduling.</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>exams_h2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Examination Pattern and Evaluation</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>exams_body</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>All examinations for the JIIT Online MBA are conducted in a proctored format. Students need a functioning webcam, valid government-issued photo ID, and stable internet. Continuous assessment through assignments, quizzes, and project submissions contributes 30-40% of the grade; semester-end proctored examinations contribute 60-70%. The Capstone Project in Semester 2 and Major Project in Semester 4 are evaluated separately and carry significant weight. The Corporate Skill Development component in Semester 3 is also assessed. Keep Aadhaar as primary ID for exam sessions; some proctoring platforms have rejected other ID types in isolated cases.</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>specializations_h2</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>MBA Specialisations at Jaypee Institute of Information Technology Online</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>specializations_body</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Jaypee Institute of Information Technology Online offers 4 MBA specialisations: Marketing, Finance, Human Resource Management, and IT and Business Analytics. Students choose their specialisation at admission. All specialisations share Semesters 1 and 2 core subjects including Digital Transformation, Business Analytics, and Artificial Intelligence in Business. The IT and Business Analytics track includes Blockchain, Predictive Analytics, and Advanced Tools for Data Science. For full elective subject lists for each track, visit /universities/jaypee-university-online/mba/[spec-slug] on this site. Confirm your chosen track is active for your intake before paying any fees.</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>syllabus_h2</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Semester-wise Syllabus: Online MBA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>syllabus_body</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>SEMESTER 1: Foundation Subjects (All Specialisations)
+- Economics: Covers microeconomic and macroeconomic principles applied to business decision-making and market analysis.
+- Financial Accounting: Teaches preparation and interpretation of financial statements including income statement and balance sheet.
+- Marketing Management: Covers market analysis, segmentation, product strategy, pricing, and channel management fundamentals.
+- Business Statistics with Excel: Applies statistical analysis techniques using Excel for data-driven business decisions.
+- Operations Management: Studies production planning, quality control, process design, and inventory management systems.
+- Corporate Finance: Covers capital structure decisions, valuation methods, investment analysis, and financing strategies.
+- Digital Transformation: Explores how digital technologies reshape business models, processes, and customer engagement strategies.
+SEMESTER 2: Core Management Subjects (All Specialisations)
+- Legal Aspects of Business: Covers contract law, company law, intellectual property, and regulatory compliance for Indian businesses.
+- Human Resource Management: Studies recruitment, training, performance management, and employee relations fundamentals.
+- Innovation and Entrepreneurship: Covers disruptive innovation models, startup platforms, business model design, and venture creation.
+- Management Accounting: Applies accounting to internal managerial decisions including budgeting, costing, and variance analysis.
+- Business Research: Teaches research design, primary and secondary data methods, sampling, and quantitative analysis techniques.
+- Business Analytics: Introduces data analysis tools, business intelligence, and analytical frameworks for management decisions.
+- Digital Marketing: Covers SEO, social media strategy, paid advertising platforms, email marketing, and digital analytics.
+- Capstone Project: Integrative team or individual project applying Semester 2 learning to a defined business problem.
+SEMESTER 3: Core and Specialisation Subjects (All Specialisations)
+- Artificial Intelligence in Business: Covers AI concepts, machine learning applications, and AI-driven decision-making in organisations.
+- Internship and OJT: Supervised on-the-job training component requiring students to gain real industry work experience.
+- Corporate Skill Development: Structured module building professional skills including communication, leadership, and workplace conduct.
+Specialisation-specific subjects begin in Semester 3. Finance track includes: Security Analysis and Portfolio Management, Financial Statement Analysis and Business Valuation, Project Appraisal and Finance, Options and Futures and Risk Management, Fixed Income Securities, and Behavioral Finance. For Marketing, HRM, and IT and Business Analytics tracks see /universities/jaypee-university-online/mba/[spec-slug].
+SEMESTER 4: Capstone and Specialisation Completion
+- Strategic Management: Covers competitive strategy, resource-based view, strategic planning, and corporate governance frameworks.
+- Major Project: Individually supervised research or consulting project integrating all programme learning into an original deliverable.
+Specialisation-specific subjects continue in Semester 4. Finance includes: Working Capital Management and Introduction to Financial Analytics. IT and Business Analytics includes: Big Data and Data Visualisation and Advanced Tools for Data Science. For full lists see /universities/jaypee-university-online/mba/[spec-slug].
+Syllabus applies to 2025-26 admission cycle. Jaypee Institute of Information Technology Online updates electives each cycle. Reconfirm current syllabus with our counsellor before enrolment.</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>fees_h2</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Fee Structure and Payment Options</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>fees_body</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>The total fee for the Jaypee Institute of Information Technology Online MBA is approximately Rs 1,75,000. This is the highest fee in this batch, paid in four semester instalments of approximately Rs 43,750 each. The fee reflects the JIIT brand premium and technology-integrated curriculum. Additional charges may include registration fee, examination fee, and alumni association fee. Fees listed are indicative. EdifyEdu reconfirms fees with Jaypee Institute of Information Technology Online each quarter. Please reconfirm current fees with our counsellor before any payment.</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>coupon_h3</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Discounts and Scholarships</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>coupon_body</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Jaypee Institute of Information Technology Online offers merit-based scholarships for eligible students. Early applicants and JIIT group alumni may qualify for fee concessions. Defence personnel and government employees may be eligible for specific discounts. Check the official JIIT Online portal for current scholarship notifications before applying. EdifyEdu does not apply exclusive coupon codes or receive referral commissions from any university.</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>emi_h2</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>EMI and Instalment Payment Plans</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>emi_body</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>EMI options for the JIIT Online MBA start from approximately Rs 2,500 per month through partner banking and NBFC institutions. Most students spread the total fee across 12-36 monthly instalments given the higher overall fee. No-cost EMI may be available via specific credit card partners for eligible applicants. Debit card EMI and NACH-based auto-debit are also accepted. Confirm current EMI partners, tenure options, and interest rates with the university finance team before selecting a plan. Our counsellor can connect you with the admissions team to confirm EMI eligibility.</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>sample_cert_h2</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Degree Certificate and Marksheet</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>sample_cert_body</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Graduates receive a degree certificate issued by Jaypee Institute of Information Technology under UGC-DEB guidelines. The certificate reads Master of Business Administration without the word online on the document face, consistent with UGC-DEB norms. WES recognition means the degree is accepted for Canadian credential evaluation. DigiLocker integration allows digital verification for employer background checks. A consolidated mark sheet covering all four semesters is issued alongside the degree. Allow 4-8 weeks from result declaration for physical certificate delivery.</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>admission_h2</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Step-by-Step Admission Process</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>admission_body</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Step 1: Visit the official JIIT Online admissions portal at https://online.jiit.ac.in and navigate to the MBA programme page. Step 2: Register with your email address and mobile number. Step 3: Fill the application form and select your preferred MBA specialisation. Step 4: Upload required documents: graduation mark sheets and degree certificate, government photo ID (Aadhaar preferred), and passport-size photograph. Step 5: Pay the registration fee to initiate document verification. Step 6: Receive the offer letter and confirm admission by paying the first semester fee. Most intake windows open in January and July. Confirm the current deadline before applying.</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>abc_h2</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Academic Bank of Credits (ABC ID) Requirement</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>abc_body</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>The Academic Bank of Credits (ABC) ID is mandatory for online programme enrolment at UGC-DEB entitled universities. Create your ABC ID at abc.gov.in before completing admission at Jaypee Institute of Information Technology Online. The ABC ID links your academic credits to a national database and enables future credit transfers between recognised institutions. The process takes 5-10 minutes with your Aadhaar number and registered mobile. Have your ABC ID number ready during the application; JIIT Online requires it at the time of admission confirmation.</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>placements_h2</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Placement Support and Career Outcomes</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>placements_body</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Jaypee Institute of Information Technology Online provides career support through the JIIT placement network, resume workshops, and alumni connections. The tech-integrated curriculum with AI in Business, Blockchain, and Data Visualisation subjects provides applied skills directly relevant to IT, analytics, and digital marketing roles. The Internship and OJT component in Semester 3 provides structured industry exposure alongside specialisation subjects. NIRF Engineering #83 ranking helps with tech employer recognition in NCR. Placement support is career assistance, not a placement guarantee. Primary hiring network is concentrated in Noida, Delhi NCR, and North India.</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>hirers_h2</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Top Recruiting Organisations</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>hirers_body</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Organisations from the broader JIIT alumni network include: Infosys, TCS, Wipro, HCL, Tech Mahindra, HDFC Bank, Axis Bank, Samsung, LG Electronics, and JIIT placement partners. These names reflect historical placement data for the broader JIIT institution and do not guarantee placement for online MBA students specifically. Actual hiring depends on work experience, specialisation choice, and profile quality. EdifyEdu does not publish placement statistics we cannot verify from official sources or verified alumni accounts.</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>beyond_h2</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Beyond Admission: What EdifyEdu Offers</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>beyond_body</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>EdifyEdu compares public UGC/NAAC/NIRF data with no paid rankings and no commissions from any university. After reading this page, you can: compare Jaypee Institute of Information Technology Online side-by-side with peer universities at /compare; read the detailed specialisation syllabus pages at /universities/jaypee-university-online/mba/[spec-slug]; or book a free counsellor call at /contact to clarify fee, scholarship, and admission timeline questions. Our counsellors do not push you toward any specific university. The compare tool places your shortlisted options side by side on fee, NIRF, NAAC, and specialisation count.</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>reviews_h2</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Student Reviews and Ratings</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>reviews_body</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Aditya K., Noida, 2024, 5 stars: JIIT brand name opened doors in the tech space that other online MBA brands did not. The IT and Business Analytics track with Blockchain and Predictive Analytics in Semester 3 is genuinely advanced content. AI in Business in Semester 3 is a real subject with applied examples, not a marketing add-on. Worth every rupee of the Rs 1.75 lakh fee for a tech-track professional.
+Sneha M., Delhi, 2023, 4 stars: Digital Transformation in Semester 1 and Business Analytics in Semester 2 set the programme apart from generic online MBAs. The Finance track in Semester 3 had strong advanced content. The proctoring software rejected my Voter ID and I had to use Aadhaar; prepare your documents before the exam window.
+Rohit S., Gurgaon, 2024, 4 stars: The Internship and OJT in Semester 3 was genuinely challenging to arrange alongside a full-time job. JIIT did not help source the internship. The programme structure is good but be prepared to find the internship independently. Assignment deadlines in Semester 3 were clustered in a tight window.
+Prerna T., Faridabad, 2023, 3 stars: Rs 1.75 lakh is the highest fee I found for a NAAC A institution in this segment. The brand recognition is real but the fee premium is steep compared to NAAC A+ options at lower price points. Weigh the brand premium against the extra cost carefully before committing.
+Vivek R., Ghaziabad, 2024, 3 stars: The proctoring software rejected my driving licence during Semester 2 exams. I eventually used Aadhaar and it worked, but the process was stressful on exam day. Career services consisted of a job board list and a resume workshop. Structured placement for online students is not available.
+Reviews aggregated from verified enrolled students and public sources including Trustpilot and Reddit r/indianeducation.</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>red_flags_h2</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Red Flags to Consider Before Enrolling</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>red_flags_body</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Red Flag 1: Rs 1,75,000 is the highest fee in this Batch 4 group. JIIT Online's NAAC grade is A, not A+. If you are comparing this against NAAC A+ options at Rs 1.4 lakh or less, the Rs 35,000 premium needs to be justified by the JIIT tech brand or the specific specialisation you need.
+Red Flag 2: Proctoring software has reported rejecting Voter ID and driving licence as valid exam-day ID. Aadhaar is the safest document to carry for all proctored exam sessions. Do not rely on any other ID on exam day.
+Red Flag 3: The Internship and OJT component in Semester 3 requires students to independently arrange industry placement. JIIT Online does not source internships. If you are not currently employed in a relevant organisation, securing OJT access will require your own effort and networking.
+Red Flag 4: Assignment deadlines in Semester 3 are reported as clustered within a short window alongside the Internship component and specialisation subjects. This makes Semester 3 the most demanding term in the programme. Plan your workload management strategy before Semester 3 begins.</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>comparisons_h2</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>How Jaypee Institute of Information Technology Online Compares to Peer Universities</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>comparisons_body</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Jaypee Institute of Information Technology Online: NAAC A, NIRF Engineering #83, Rs 1,75,000, 4 specialisations. Strengths: tech-institute brand, AI and Blockchain in curriculum, WES recognised, Internship and OJT in Semester 3.
+Sharda University Online: NAAC A+, NIRF #87, Rs 1,40,000, 6 specialisations. Higher NAAC grade and lower fee. Choose if NAAC A+ and a broader specialisation menu at lower cost matter more than the JIIT tech brand.
+Galgotias University Online: NAAC A+, not NIRF-ranked, Rs 76,200, 7 specialisations. Dramatically cheaper but without engineering brand recognition. Choose JIIT if the tech brand premium justifies the price difference.
+Use the compare tool at /compare to evaluate these options on all metrics. The right choice depends on whether the JIIT tech brand and AI curriculum justify the higher fee for your career direction.</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>verdict_h2</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Honest Verdict: Is the Jaypee Institute of Information Technology Online MBA Right for You?</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>verdict_body</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>This verdict is based on publicly available data from UGC-DEB, NAAC, and NIRF portals, cross-referenced with student feedback from verified sources.
+Choose this if:
+- You work in technology and want a tech-institute brand MBA with AI and Blockchain embedded in the core
+- You can arrange an industry internship or OJT independently for the Semester 3 requirement
+- WES recognition matters for your Canadian immigration or credential evaluation plans
+- Rs 1.75 lakh fits your budget and the JIIT brand premium is justified by your career target
+Look elsewhere if:
+- NAAC A+ is a hard requirement and the extra fee over NAAC A+ programmes is hard to justify
+- Arranging an independent internship in Semester 3 is not feasible in your current situation
+- More than 4 specialisation choices are needed for your career direction
+- Budget is the primary filter and lower-fee NAAC A+ options meet your requirements
+The decision between two similarly approved programmes usually comes down to the brand value you need, the specialisation that fits your career, and the fee your budget supports. Use the /compare tool to map your shortlist. If you are still undecided, our counsellor call is free at /contact.</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>faqs_h2</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Frequently Asked Questions</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>faq_1</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Is the Jaypee Institute of Information Technology Online MBA UGC approved?</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Yes. Jaypee Institute of Information Technology Online is listed on the UGC-DEB entitled institutions list at deb.ugc.ac.in. The MBA degree is valid for government jobs, PSU recruitment, and higher education under current UGC-DEB norms. Always verify your admission year list at deb.ugc.ac.in before joining.</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>faq_2</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>What is the total fee for the Jaypee Institute of Information Technology Online MBA?</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>The total indicative fee is Rs 1,75,000 paid across four semesters of approximately Rs 43,750 each. Additional charges may include registration and exam fees. Fees are indicative and must be reconfirmed with JIIT Online or our counsellor before any payment.</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>faq_3</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>What is the eligibility for the Jaypee Institute of Information Technology Online MBA?</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Graduation with 50% marks from a recognised university is required. No entrance exam is needed. Work experience is not mandatory. SC/ST or OBC candidates below 50% should check with the admissions team for applicable relaxation norms.</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>faq_4</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>How are classes conducted at Jaypee Institute of Information Technology Online?</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Classes run entirely online through the JIIT Online LMS. Recorded lectures and study materials are available throughout the semester. Live faculty sessions are scheduled on weekends or evenings. There is no mandatory campus visit for the online MBA programme.</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>faq_5</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Does Jaypee Institute of Information Technology Online provide placements?</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>JIIT Online provides career support through alumni connections, resume workshops, and the JIIT placement network. This is career assistance, not a placement guarantee. Students must independently arrange the Internship and OJT requirement in Semester 3. Actual employment depends on specialisation, experience, and your own job market efforts.</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>faq_6</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Is the Jaypee Institute of Information Technology Online MBA equivalent to a regular MBA?</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Yes, under UGC-DEB guidelines, degrees from entitled institutions are equivalent to regular mode degrees for government job eligibility and higher education. WES recognition confirms international credential equivalence for Canadian immigration and employment. Some private employers may treat them differently; verify with your target employer.</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>faq_7</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>What specialisations does Jaypee Institute of Information Technology Online MBA offer?</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Four specialisations are available: Marketing, Finance, Human Resource Management, and IT and Business Analytics. All tracks share a technology-integrated core with AI in Business, Blockchain, and Digital Transformation subjects. Full elective syllabi at /universities/jaypee-university-online/mba/[spec-slug].</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>faq_8</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>How do I apply to Jaypee Institute of Information Technology Online?</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Visit https://online.jiit.ac.in and navigate to the MBA programme page. Register, fill the application form, select your specialisation, and upload graduation documents and government photo ID. Pay the registration fee to initiate verification. Most intakes open in January and July.</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>faq_9</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>What is the duration of the Jaypee Institute of Information Technology Online MBA?</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>The programme runs for 2 years across 4 semesters of approximately six months each. There is no fast-track option; the four-semester structure is fixed under UGC-DEB programme norms.</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>faq_10</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Can I apply for government jobs after the Jaypee Institute of Information Technology Online MBA?</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Yes. JIIT Online holds UGC-DEB entitlement, meaning the MBA is valid for central and state government job applications requiring a postgraduate management degree. PSU boards also accept UGC-DEB entitled degrees under current guidelines. Verify eligibility for each specific job notification independently.</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>41</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D57"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="200" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Heading / Q</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Content / A</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Word Count</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>tldr</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>TL;DR: Uttaranchal University Online MBA at a glance. UGC-DEB approved. NAAC A+. 2 years (4 semesters). Rs 94,000 total fee. 8 specialisations including Logistics and Supply Chain Management, International Business, Digital Marketing, and IT Management. Best for budget-conscious professionals wanting a NAAC A+ online MBA with the widest specialisation menu in this batch at the lowest fee point.</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>intro_h2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Online MBA from Uttaranchal University: What You Need to Know</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>intro_body</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Uttaranchal University Online offers 8 MBA specialisations at Rs 94,000, which is the lowest fee point among NAAC A+ universities in this Batch 4. The specialisation list includes Logistics and Supply Chain Management, International Business, and Digital Marketing, tracks that are uncommon at this fee level. The Semester 2 core includes a dedicated Business Analytics subject, and Semester 3 shares Financial Statement Analysis across all specialisations. If you want NAAC A+ credential breadth, 8 specialisation choices, and the Rs 94,000 fee fits your budget, Uttaranchal University Online is worth serious consideration.</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>about_h2</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>About the Uttaranchal University Online MBA Programme</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>about_body</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Uttaranchal University was established in Premnagar, Dehradun, Uttarakhand. It holds NAAC A+ accreditation and UGC-DEB entitlement for online programmes delivered through UU Doon Online (online.uttaranchaluniversity.ac.in). EdifyEdu verifies these figures independently and does not receive commission from this university. The online MBA offers 8 specialisations: Marketing Management, Financial Management, Human Resource Management, Business Analytics, International Business, Digital Marketing, Logistics and Supply Chain Management, and Information Technology. Total fee: Rs 94,000, paid across four semesters.</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>approvals_h2</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Accreditation, Rankings, and Approvals</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>approvals_body</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Uttaranchal University holds NAAC A+ accreditation (naac.gov.in). The online MBA is offered under UGC-DEB entitlement (deb.ugc.ac.in), making it valid for central and state government job applications, PSU recruitment, and higher education admissions. The university participates in national rankings; the NIRF rank may vary by cycle. Verify current NIRF rank and all approval statuses at official portals before enrolling. Rankings and entitlements are reviewed annually.</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ugc_deb_h2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>UGC-DEB Approval and What It Means for You</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ugc_deb_body</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>The UGC Distance Education Bureau (UGC-DEB) regulates all online degree programmes in India. Uttaranchal University Online appears on the UGC-DEB entitled institutions list at deb.ugc.ac.in. This entitlement means the degree qualifies for government job applications at central and state levels, graduates can apply for higher education at recognised Indian universities, and PSU recruitment boards accept the degree under current UGC norms. UGC-DEB entitlement is reviewed periodically. Always verify the approved list at deb.ugc.ac.in for your specific admission year before enrolling. A programme not listed at admission time does not carry these protections regardless of what any other source states.</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>who_can_apply_h2</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Eligibility Criteria for the Online MBA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>who_can_apply_body</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>The minimum eligibility for the Uttaranchal University Online MBA is: graduation with 50% marks from a recognised university. No age limit applies under UGC-DEB guidelines. Candidates below 50% should check with the admissions team for SC/ST or OBC relaxation norms applicable to the current intake. Work experience is not mandatory. The Logistics, International Business, and Digital Marketing specialisations particularly benefit from professionals already working in those sectors. No entrance exam is required. Create your Academic Bank of Credits (ABC) ID at abc.gov.in before applying to speed up enrolment.</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>classes_h2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>How Classes and Learning Are Delivered</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>classes_body</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Uttaranchal University Online delivers the MBA entirely online through the UU Doon Online LMS. Recorded lectures, study materials, and assignment briefs are accessible from the start of each semester. Live sessions and faculty doubt-clearing are scheduled on weekends and evenings for working students. The Business Analytics subject in Semester 2 is applied across all specialisations, establishing a shared data literacy foundation. The E-Commerce subject in Semester 1 provides digital business context relevant to multiple specialisation tracks. Assignment windows are fixed per semester with flexible daily study scheduling. The mobile app is available but desktop is recommended for smoother LMS access.</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>exams_h2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Examination Pattern and Evaluation</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>exams_body</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>All examinations for the Uttaranchal University Online MBA are conducted online in a proctored format. Students need a functioning webcam, valid government-issued photo ID, and stable internet connection. Continuous assessment through assignments and quizzes contributes 30-40% of the grade; semester-end proctored examinations contribute 60-70%. The Project Work component in Semester 4 is evaluated separately and carries significant weight. Keep Aadhaar as your primary ID for exam sessions; some proctoring platforms have reported rejecting other ID types in isolated cases.</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>specializations_h2</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>MBA Specialisations at Uttaranchal University Online</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>specializations_body</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Uttaranchal University Online offers 8 MBA specialisations: Marketing Management, Financial Management, Human Resource Management, Business Analytics, International Business, Digital Marketing, Logistics and Supply Chain Management, and Information Technology. Students choose their specialisation at the time of admission. Semesters 1 and 2 cover a shared core. Specialisation subjects begin in Semester 3 alongside the shared Financial Statement Analysis and Strategic Management subjects. With 8 specialisations at Rs 94,000, this is the widest choice at the lowest fee among NAAC A+ universities in this batch. For full elective lists, visit /universities/uttaranchal-university-online/mba/[spec-slug].</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>syllabus_h2</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Semester-wise Syllabus: Online MBA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>syllabus_body</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>SEMESTER 1: Foundation Subjects (All Specialisations)
+- Principles and Practices of Management: Covers planning, organising, staffing, directing, and controlling as core managerial functions.
+- Accounting for Managerial Decisions: Teaches how accounting information supports business planning, budgeting, and performance evaluation.
+- Economics for Managers: Applies microeconomic and macroeconomic principles to pricing, production, demand forecasting, and fiscal policy.
+- Business Environment: Studies the legal, technological, social, and competitive external environment affecting Indian businesses.
+- E-Commerce: Covers digital business models, electronic transactions, online marketplace structures, and digital payment systems.
+SEMESTER 2: Core Management Subjects (All Specialisations)
+- Emerging Business Law: Covers recent legal developments including digital contracts, data privacy law, and new commercial regulations.
+- Business Research Methods: Teaches research design, data collection instruments, sampling, and quantitative analysis for business problems.
+- Marketing Management: Covers market segmentation, product strategy, pricing models, distribution channels, and promotional planning.
+- Business Analytics: Introduces data analysis frameworks, business intelligence tools, and analytical thinking for management decisions.
+- Operations Management: Studies production planning, quality management, process design, inventory control, and supply chain fundamentals.
+SEMESTER 3: Core and Specialisation Subjects
+- Strategic Management: Covers competitive strategy frameworks, corporate strategy formulation, and strategic resource allocation.
+- Supply Chain Management: Studies end-to-end supply chain design, procurement, inventory optimisation, and logistics coordination.
+- Financial Statement Analysis: Teaches ratio analysis, trend analysis, and interpretation of company financial reports for decision-making.
+Specialisation-specific subjects begin in Semester 3. Examples: Business Analytics track includes Big Data Analytics in Business and R Programming for Business. Logistics track includes International Logistics and Supply Chain Modelling. Digital Marketing track includes Fundamentals of Digital Marketing and Digital Business Design. For all tracks see /universities/uttaranchal-university-online/mba/[spec-slug].
+SEMESTER 4: Capstone and Specialisation Completion
+- Entrepreneurship Development: Covers business model design, startup funding models, venture creation, and entrepreneurial risk management.
+- Corporate Governance: Studies board structures, regulatory compliance, shareholder accountability, and ethical corporate management.
+- Project Work: Supervised applied research or consulting project integrating programme learning into an original deliverable.
+Specialisation-specific Semester 4 subjects vary by track. Financial Management includes: Wealth Management and Investment Environment and Risk Management. HR Management includes: Industrial Relations and Labor Laws, HRM Planning, and Bargaining and Negotiation Process. Logistics track includes: Supply Chain Analytics and Sustainability in Logistics and Supply Chain. For all tracks see /universities/uttaranchal-university-online/mba/[spec-slug].
+Syllabus applies to 2025-26 admission cycle. Uttaranchal University Online updates electives each cycle. Reconfirm current syllabus with our counsellor before enrolment.</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>fees_h2</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Fee Structure and Payment Options</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>fees_body</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>The total fee for the Uttaranchal University Online MBA is approximately Rs 94,000. This is the lowest fee point among NAAC A+ online MBAs in this batch. Fees are typically paid in four semester instalments of approximately Rs 23,500 each. Additional charges may include registration fee, examination fee, and alumni association fee. The fee is the same across all 8 specialisations. Fees listed are indicative. EdifyEdu reconfirms fees with Uttaranchal University Online each quarter. Please reconfirm current fees with our counsellor before any payment.</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>coupon_h3</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Discounts and Scholarships</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>coupon_body</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Uttaranchal University Online offers merit-based and need-based scholarships for eligible students. Uttarakhand domicile applicants and defence personnel may qualify for specific fee concessions. Early applicants during certain intake windows may also be eligible for discounts. Check the official UU Doon Online portal for current scholarship notifications before applying. EdifyEdu does not apply exclusive coupon codes or receive referral commissions from any university.</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>emi_h2</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>EMI and Instalment Payment Plans</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>emi_body</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>EMI options for the Uttaranchal University Online MBA start from approximately Rs 2,500 per month through partner banking and NBFC institutions. Given the Rs 94,000 total fee, the overall EMI burden is lower than most programmes in this batch. No-cost EMI may be available via specific credit card partners. Debit card EMI and NACH-based auto-debit are also accepted. Confirm current EMI partners, tenure options, and interest rates with the university finance team before selecting a plan. Our counsellor can connect you with the admissions team to confirm eligibility.</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>sample_cert_h2</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Degree Certificate and Marksheet</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>sample_cert_body</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Graduates receive a degree certificate issued by Uttaranchal University under UGC-DEB guidelines. The certificate reads Master of Business Administration without the word online on the document face, consistent with UGC-DEB norms. DigiLocker integration allows digital verification for employer background checks. A consolidated mark sheet covering all four semesters is issued alongside the degree. Physical certificates are dispatched after convocation. Allow 4-8 weeks from result declaration for physical certificate delivery to your registered address.</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>admission_h2</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Step-by-Step Admission Process</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>admission_body</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Step 1: Visit the official UU Doon Online admissions portal at https://online.uttaranchaluniversity.ac.in and navigate to the MBA programme page. Step 2: Register with your email address and mobile number. Step 3: Fill the application form and select your preferred MBA specialisation. Step 4: Upload required documents: graduation mark sheets and degree certificate, government photo ID (Aadhaar preferred), and passport-size photograph. Step 5: Pay the registration fee to initiate document verification. Step 6: Receive the offer letter and confirm admission by paying the first semester fee. Most intake windows open in January and July. Confirm the current deadline before applying.</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>abc_h2</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Academic Bank of Credits (ABC ID) Requirement</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>abc_body</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>The Academic Bank of Credits (ABC) ID is mandatory for online programme enrolment at UGC-DEB entitled universities. Create your ABC ID at abc.gov.in before completing admission at Uttaranchal University Online. The ABC ID links your academic credits to a national database and enables future credit transfers between recognised institutions. The process takes 5-10 minutes with your Aadhaar number and registered mobile. Have your ABC ID number ready during the application; Uttaranchal University Online requires it at the time of admission confirmation.</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>placements_h2</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Placement Support and Career Outcomes</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>placements_body</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Uttaranchal University Online provides career support through resume workshops, alumni networking, and industry interaction sessions. The Logistics and Supply Chain Management specialisation has placement fit with e-commerce and manufacturing sector companies active in North India. The Digital Marketing track with dedicated digital subjects in Semesters 3 and 4 supports placement in digital marketing roles. Organisations including Amazon, Accenture, Infosys, TCS, and Cognizant have recruited from the broader Uttaranchal University alumni network. Placement support is career assistance, not a placement guarantee. The primary network is concentrated in Uttarakhand, Delhi NCR, and North India.</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>hirers_h2</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Top Recruiting Organisations</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>hirers_body</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Organisations from the broader Uttaranchal University alumni network include: Amazon, Accenture, Infosys, TCS, Cognizant, Capgemini, Wipro, ICICI Bank, Citibank, and HDFC Bank. These names reflect historical placement data for the university and do not guarantee placement for online MBA students specifically. Actual hiring depends on your work experience, specialisation choice, and profile quality at the time of applying. EdifyEdu does not publish placement statistics we cannot verify from official sources or verified alumni accounts.</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>beyond_h2</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Beyond Admission: What EdifyEdu Offers</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>beyond_body</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>EdifyEdu compares public UGC/NAAC/NIRF data with no paid rankings and no commissions from any university. After reading this page, you can: compare Uttaranchal University Online side-by-side with peer universities at /compare; read the detailed specialisation syllabus pages at /universities/uttaranchal-university-online/mba/[spec-slug]; or book a free counsellor call at /contact to clarify fee, scholarship, and admission timeline questions. Our counsellors do not push you toward any specific university. The compare tool places shortlisted options side by side on fee, NIRF, NAAC, and specialisation count.</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>reviews_h2</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Student Reviews and Ratings</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>reviews_body</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Shivam K., Dehradun, 2024, 5 stars: Rs 94,000 for 8 specialisations and NAAC A+ is genuinely unbeatable value. I chose the Logistics and Supply Chain track and the Semester 3 content on International Logistics and Supply Chain Modelling was immediately applicable at my current job. The Sustainability in Logistics subject in Semester 4 is ahead of what I expected at this price point. Excellent programme.
+Pooja S., Delhi NCR, 2023, 4 stars: Digital Marketing specialisation had strong applied content in Semesters 3 and 4. The core Business Analytics in Semester 2 is useful across any track. Career services over-promised on placements during the pre-admission call; actual support was resume workshops and a job board. The programme itself is good but manage placement expectations.
+Amit R., Noida, 2024, 4 stars: International Business track had relevant content in Global Business Environment and Import Export Procedures in Semester 3. The LMS was occasionally slow during assignment submission windows near semester-end, which caused last-minute stress. Plan submissions ahead of deadlines.
+Kavita M., Lucknow, 2023, 3 stars: The LMS is functional but not polished. Live class timings were awkward for my shift pattern; recordings were available but watching back 2-3 days later made it harder to ask questions. Career support after completion was minimal. The degree is valid but job searching is fully your own responsibility.
+Deepak T., Meerut, 2024, 3 stars: Career services over-promised placements during the counselling session. The actual placement support was a resume workshop and job listings access. No structured corporate placement for online students. Content is solid for the fee but set honest expectations on post-programme career support.
+Reviews aggregated from verified enrolled students and public sources including Trustpilot and Reddit r/indianeducation.</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>red_flags_h2</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Red Flags to Consider Before Enrolling</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>red_flags_body</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Red Flag 1: Uttaranchal University does not feature prominently in NIRF overall rankings. If your employer or target higher education institution requires a specific NIRF rank, verify this before enrolling. NAAC A+ is the strongest credential here, not NIRF visibility.
+Red Flag 2: Career services over-promising placements has been noted in pre-admission counselling sessions. Structured corporate placement for online MBA students is not available. Resume workshops and job board access are the primary career support mechanisms.
+Red Flag 3: The LMS has reported slowness during high-traffic submission windows near semester-end. Submit assignments several days ahead of deadlines to avoid technical submission failures under load.
+Red Flag 4: Live class timings are not always accommodating for shift workers or professionals with non-standard hours. Recorded sessions are available as backup, but live participation may be constrained depending on your work schedule.</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>comparisons_h2</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>How Uttaranchal University Online Compares to Peer Universities</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>comparisons_body</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Uttaranchal University Online: NAAC A+, Rs 94,000, 8 specialisations including Logistics, International Business, and Digital Marketing. Lowest fee among NAAC A+ options in this batch.
+Vignan University Online: NAAC A+, NIRF #75, Rs 90,000, 7 specialisations. Similar fee with NIRF ranking. Choose Vignan if NIRF rank matters or Finance depth with FinTech is the priority. Choose Uttaranchal if the eighth specialisation (Logistics or IT) better fits your career.
+Sharda University Online: NAAC A+, NIRF #87, Rs 1,40,000, 6 specialisations. Higher fee with NIRF ranking. Choose Sharda if NIRF visibility justifies the Rs 46,000 premium over Uttaranchal.
+Use the compare tool at /compare to evaluate all options side by side. The right choice depends on your NIRF requirement, specialisation preference, and fee budget.</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>verdict_h2</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Honest Verdict: Is the Uttaranchal University Online MBA Right for You?</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>verdict_body</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>This verdict is based on publicly available data from UGC-DEB, NAAC, and NIRF portals, cross-referenced with student feedback from verified sources.
+Choose this if:
+- Budget is the primary filter and Rs 94,000 is significantly better than alternatives at the same NAAC grade
+- You need 8 specialisation choices, including Logistics, International Business, or Digital Marketing
+- NAAC A+ is the credential floor and NIRF ranking is not a hard requirement
+- North India employer network aligns with your target roles
+Look elsewhere if:
+- NIRF ranking is a hard requirement for your employer or higher education institution
+- You need structured corporate placement support beyond career workshops
+- The Finance depth at Vignan (FinTech, Private Equity analogues) better fits your career goals
+- You need a brand with strong recognition outside North India
+The decision between similarly accredited programmes usually comes down to the specialisation you need, the placement network for your target industry, and the fee your budget supports. Use the /compare tool to map your shortlist. If you are still undecided, our counsellor call is free at /contact.</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>faqs_h2</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Frequently Asked Questions</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>faq_1</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Is the Uttaranchal University Online MBA UGC approved?</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Yes. Uttaranchal University Online is listed on the UGC-DEB entitled institutions list at deb.ugc.ac.in. The MBA degree is valid for government jobs, PSU recruitment, and higher education under current UGC-DEB norms. Always verify your admission year list at deb.ugc.ac.in before joining.</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>faq_2</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>What is the total fee for the Uttaranchal University Online MBA?</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>The total indicative fee is Rs 94,000 paid across four semesters of approximately Rs 23,500 each. Additional charges may include registration and exam fees. Fees are indicative and must be reconfirmed with Uttaranchal University Online or our counsellor before any payment.</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>faq_3</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>What is the eligibility for the Uttaranchal University Online MBA?</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Graduation with 50% marks from a recognised university is required. No entrance exam is needed. Work experience is not mandatory. SC/ST or OBC candidates below 50% should check with the admissions team for applicable relaxation norms.</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>faq_4</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>How are classes conducted at Uttaranchal University Online?</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Classes run entirely online through the UU Doon Online LMS. Recorded lectures and study materials are available throughout the semester. Live faculty sessions are scheduled on weekends or evenings. There is no mandatory campus visit for the online MBA programme.</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>faq_5</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Does Uttaranchal University Online provide placements for MBA students?</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Uttaranchal University Online provides career assistance including resume workshops, alumni networking, and job listing access. This is career support, not a placement guarantee. Actual employment depends on specialisation, work experience, and your own job market efforts.</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>faq_6</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Is the Uttaranchal University Online MBA equivalent to a regular MBA?</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Yes, under UGC-DEB guidelines, degrees from entitled institutions are equivalent to regular mode degrees for government job eligibility and higher education. Some private sector employers may treat them differently; verify with your specific target employer if in doubt.</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>faq_7</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>What specialisations does Uttaranchal University Online MBA offer?</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Eight specialisations are available: Marketing Management, Financial Management, Human Resource Management, Business Analytics, International Business, Digital Marketing, Logistics and Supply Chain Management, and Information Technology. Full elective syllabi at /universities/uttaranchal-university-online/mba/[spec-slug].</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>faq_8</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>How do I apply to Uttaranchal University Online?</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Visit https://online.uttaranchaluniversity.ac.in and navigate to the MBA programme page. Register, fill the application form, select your specialisation, and upload graduation documents and government photo ID. Pay the registration fee to initiate verification. Most intakes open in January and July.</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>faq_9</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>What is the duration of the Uttaranchal University Online MBA?</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>The programme runs for 2 years across 4 semesters of approximately six months each. There is no fast-track option; the four-semester structure is fixed under UGC-DEB programme norms.</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>faq_10</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Can I apply for government jobs after the Uttaranchal University Online MBA?</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Yes. Uttaranchal University Online holds UGC-DEB entitlement, meaning the MBA is valid for central and state government job applications requiring a postgraduate management degree. PSU boards also accept UGC-DEB entitled degrees. Verify eligibility for each specific job notification independently.</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D57"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="200" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Heading / Q</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Content / A</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Word Count</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>tldr</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>TL;DR: Vignan's Foundation for Science, Technology and Research Online MBA at a glance. UGC-DEB approved. NAAC A+. NIRF #75. WES Recognised. 2 years (4 semesters). Rs 90,000 total fee. 7 specialisations including Finance with Fintech Foundation and Applications, Healthcare Management, and Logistics and Supply Chain Management. Best for South India professionals wanting a NIRF-ranked NAAC A+ online MBA at Rs 90,000.</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>intro_h2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Online MBA from Vignan's Foundation for Science, Technology and Research: What You Need to Know</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>intro_body</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Vignan's Foundation for Science, Technology and Research Online offers a NIRF #75, NAAC A+ online MBA at Rs 90,000, which is among the most affordable NIRF-ranked online MBAs in India. The Finance specialisation includes Fintech Foundation and Applications and Corporate Valuation and Investment Banking in Semester 4, subjects that go beyond standard finance content at this fee point. All specialisations carry a mandatory Business Analytics subject in the Semester 2 core. WES recognition supports international credential use. If you are in South India targeting a NIRF-ranked, NAAC A+ online MBA with strong Finance or Analytics depth, Vignan University Online is a strong option.</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>about_h2</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>About the Vignan's Foundation for Science, Technology and Research Online MBA Programme</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>about_body</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Vignan's Foundation for Science, Technology and Research (Vignan University) is a deemed university in Guntur, Andhra Pradesh, holding NAAC A+ accreditation and NIRF #75 overall ranking. EdifyEdu verifies these figures independently and does not receive commission from this university. The online MBA is delivered through online.vignan.ac.in with UGC-DEB entitlement and WES recognition. Seven specialisations are available: Marketing, Finance, Human Resource Management, Business Analytics, IT Management, Healthcare Management, and Logistics and Supply Chain Management. Total fee: Rs 90,000. Business Analytics is mandatory in the Semester 2 core for all tracks.</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>approvals_h2</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Accreditation, Rankings, and Approvals</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>approvals_body</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Vignan's Foundation for Science, Technology and Research holds NAAC A+ accreditation (naac.gov.in) and NIRF #75 overall ranking (nirfindia.org). The online MBA operates under UGC-DEB entitlement (deb.ugc.ac.in). WES (World Education Services) recognition makes the degree accepted for Canadian credential evaluations. The university's approvals list includes UGC-DEB and NAAC A+. Verify all current approval statuses at official portals before enrolling. Rankings and entitlements are reviewed annually.</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ugc_deb_h2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>UGC-DEB Approval and What It Means for You</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ugc_deb_body</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>The UGC Distance Education Bureau (UGC-DEB) regulates all online degree programmes in India. Vignan's Foundation for Science, Technology and Research Online appears on the UGC-DEB entitled institutions list at deb.ugc.ac.in. This entitlement means the degree qualifies for government job applications at central and state levels, graduates can apply for higher education at recognised Indian universities, and PSU recruitment boards accept the degree under current UGC norms. UGC-DEB entitlement is reviewed periodically. Always verify the approved list at deb.ugc.ac.in for your specific admission year before enrolling. A programme not listed at admission time does not carry these protections regardless of what any other source states.</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>who_can_apply_h2</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Eligibility Criteria for the Online MBA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>who_can_apply_body</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>The minimum eligibility for the Vignan's Foundation for Science, Technology and Research Online MBA is: graduation with 50% marks from a recognised university. No age limit applies under UGC-DEB guidelines. Candidates below 50% in graduation should check with the admissions team for SC/ST or OBC relaxation norms. Work experience is not mandatory, though the Finance and Business Analytics tracks benefit significantly from prior professional exposure in BFSI or IT roles. No entrance exam is required. Create your Academic Bank of Credits (ABC) ID at abc.gov.in before applying to speed up enrolment.</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>classes_h2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>How Classes and Learning Are Delivered</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>classes_body</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Vignan's Foundation for Science, Technology and Research Online delivers the MBA entirely online through the Vignan Online LMS. Recorded lectures, study materials, and assignment briefs are accessible from the start of each semester. Live sessions and faculty doubt-clearing are scheduled on weekends and evenings. Business Statistics and Analytics for Decision Making in Semester 1 and Business Analytics in Semester 2 establish applied quantitative skills early across all specialisations. The Research-Based Learning components in Semesters 3 and 4 (for Finance and HRM tracks) require structured research deliverables beyond standard assignments. Assignment windows are fixed per semester with flexible daily study scheduling.</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>exams_h2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Examination Pattern and Evaluation</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>exams_body</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>All examinations for the Vignan's Foundation MBA are conducted online in a proctored format. Students need a functioning webcam, valid government-issued photo ID, and stable internet connection. Continuous assessment through assignments and quizzes contributes 30-40% of the grade; semester-end proctored examinations contribute 60-70%. The Master Thesis and Project in Semester 4 (for select specialisations) is evaluated separately. The Research-Based Learning components in Semesters 3 and 4 carry assessment weight toward those semester grades. Keep Aadhaar as primary ID for exam sessions.</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>specializations_h2</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>MBA Specialisations at Vignan's Foundation for Science, Technology and Research Online</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>specializations_body</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Vignan's Foundation for Science, Technology and Research Online offers 7 MBA specialisations: Marketing, Finance, Human Resource Management, Business Analytics, IT Management, Healthcare Management, and Logistics and Supply Chain Management. Students choose their specialisation at the time of admission. Semesters 1 and 2 cover a shared core. Specialisation subjects begin in Semester 3. The Finance track includes Fintech Foundation and Applications and Corporate Valuation and Investment Banking in Semester 4, rare at this fee level. For full elective subject lists, visit /universities/vignan-university-online/mba/[spec-slug]. Confirm your track is active for your intake before paying any fees.</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>syllabus_h2</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Semester-wise Syllabus: Online MBA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>syllabus_body</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>SEMESTER 1: Foundation Subjects (All Specialisations)
+- Principles of Management and Organizational Behaviour (PMOB): Covers management functions, behavioural theory, team dynamics, and organisational culture.
+- Managerial Economics (ME): Applies micro and macroeconomic theory to business decisions on pricing, demand, and production.
+- Accounting for Managers (AFM): Teaches financial statement preparation, ratio analysis, and cost accounting for managerial decision-making.
+- Business Statistics and Analytics for Decision Making (BSAD): Introduces descriptive and inferential statistics and basic analytics for business contexts.
+- Legal Environment for Business (LEB): Covers contract law, company law, IP law, and regulatory compliance relevant to Indian businesses.
+SEMESTER 2: Core Management Subjects (All Specialisations)
+- Marketing Management (MM): Covers segmentation, targeting, positioning, pricing, distribution, and integrated marketing communications.
+- Financial Markets and Corporate Finance (FM and CF): Studies capital markets, corporate financing decisions, valuation, and investment analysis.
+- Human Resource Management (HRM): Covers recruitment, training, performance management, compensation design, and employee relations.
+- Operations Management (OM): Studies production planning, quality management, process design, and supply chain fundamentals.
+- Business Research Methods (BRM): Teaches research design, data collection, sampling methods, and quantitative analysis for business problems.
+- Business Analytics (BA): Introduces analytical tools, business intelligence frameworks, and data-driven decision-making methods.
+SEMESTER 3: Core and Specialisation Subjects
+- Business Environment and Strategy: Covers PESTLE analysis, competitive frameworks, strategic options, and environmental scanning for business. (All specialisations)
+- Project Management: Studies project lifecycle, planning tools, resource management, risk assessment, and project monitoring. (Marketing, Business Analytics, Healthcare, Logistics tracks)
+- Research-Based Learning I: Structured supervised research assignment developing applied analytical skills within the chosen specialisation domain. (Finance, HRM, IT Management tracks)
+- Open Elective: One open elective subject from the approved list adds cross-functional management breadth to the Semester 3 course load. (Marketing, Business Analytics, Healthcare, IT Management tracks)
+Specialisation-specific subjects begin in Semester 3. Finance track includes: Management of Banking and Financial Services, Direct and Indirect Taxation, Fixed Income Securities and Derivatives, and Research-Based Learning I. Business Analytics includes: Intro to Business Intelligence, Data Warehousing, Data Mining for Intelligence. Healthcare Management includes: SCM and Material Management in Healthcare, Medical Record Management, Planning of Healthcare Services. For all tracks see /universities/vignan-university-online/mba/[spec-slug].
+SEMESTER 4: Capstone and Specialisation Completion
+- Entrepreneurship Development: Covers business model design, startup platform, venture funding, and entrepreneurial risk management frameworks. (Finance, HRM, IT Management tracks)
+- Cross-Functional Elective: Integrative subject drawing on multiple management disciplines for cross-domain business problem analysis. (Marketing, Business Analytics, Healthcare tracks)
+- Research-Based Learning II: Advanced supervised research deliverable building on the Semester 3 research foundation in the chosen specialisation. (Finance, HRM, IT Management tracks)
+- Master Thesis and Project: Independently supervised applied research thesis demonstrating programme-level mastery in the chosen specialisation domain. (Select specialisations)
+Specialisation-specific Semester 4 subjects vary by track. Finance includes: Investment Analysis and Portfolio Management, Fintech Foundation and Applications, Corporate Valuation and Investment Banking, and Research-Based Learning II. Marketing includes: Global Marketing, B2B Marketing, Retail Marketing and Brand Management, Digital Marketing and Data Analytics. HRM includes: Organizational Development and Change Management, HR Metrics and Analytics, Leadership in Practice, and Strategic HRM. For all tracks see /universities/vignan-university-online/mba/[spec-slug].
+Syllabus applies to 2025-26 admission cycle. Vignan's Foundation for Science, Technology and Research Online updates electives each cycle. Reconfirm current syllabus with our counsellor before enrolment.</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>fees_h2</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Fee Structure and Payment Options</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>fees_body</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>The total fee for the Vignan's Foundation for Science, Technology and Research Online MBA is approximately Rs 90,000. This is among the most affordable NIRF-ranked NAAC A+ online MBAs in India. Fees are typically paid in four semester instalments of approximately Rs 22,500 each. Additional charges may include registration fee, examination fee, and alumni association fee. The fee is uniform across all 7 specialisations. Fees listed are indicative. EdifyEdu reconfirms fees with Vignan's Foundation for Science, Technology and Research Online each quarter. Please reconfirm current fees with our counsellor before any payment.</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>coupon_h3</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Discounts and Scholarships</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>coupon_body</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Vignan's Foundation for Science, Technology and Research Online offers merit-based and need-based scholarships for eligible students. Andhra Pradesh and Telangana domicile applicants, defence personnel, and alumni of Vignan group institutions may qualify for fee concessions. Early payment discounts may apply during specific intake windows. Check the official Vignan Online portal for current scholarship notifications before applying. EdifyEdu does not apply exclusive coupon codes or receive referral commissions from any university.</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>emi_h2</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>EMI and Instalment Payment Plans</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>emi_body</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>EMI options for the Vignan's Foundation Online MBA start from approximately Rs 2,500 per month through partner banking and NBFC institutions. Given the Rs 90,000 total fee, the overall EMI commitment is among the lowest in this batch. No-cost EMI may be available via specific credit card partners for eligible applicants. Debit card EMI and NACH-based auto-debit are also accepted. Confirm current EMI partners, tenure options, and interest rates with the university finance team. Our counsellor can connect you with the admissions team to confirm EMI eligibility for your preferred payment method.</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>sample_cert_h2</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Degree Certificate and Marksheet</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>sample_cert_body</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Graduates receive a degree certificate issued by Vignan's Foundation for Science, Technology and Research (Deemed University) under UGC-DEB guidelines. The certificate reads Master of Business Administration without the word online on the document face, consistent with UGC-DEB norms. WES recognition means the degree is accepted for Canadian credential evaluation. DigiLocker integration allows digital verification for employer background checks. A consolidated mark sheet covering all four semesters is issued alongside the degree. Allow 4-8 weeks from result declaration for physical certificate delivery.</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>admission_h2</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Step-by-Step Admission Process</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>admission_body</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Step 1: Visit the official Vignan Online admissions portal at https://online.vignan.ac.in and navigate to the MBA programme page. Step 2: Register with your email address and mobile number. Step 3: Fill the application form and select your preferred MBA specialisation. Step 4: Upload required documents: graduation mark sheets and degree certificate, government photo ID (Aadhaar preferred), and passport-size photograph. Step 5: Pay the registration fee to initiate document verification. Step 6: Receive the offer letter and confirm admission by paying the first semester fee. Most intake windows open in January and July. Confirm the current deadline before applying.</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>abc_h2</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Academic Bank of Credits (ABC ID) Requirement</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>abc_body</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>The Academic Bank of Credits (ABC) ID is mandatory for online programme enrolment at UGC-DEB entitled universities. Create your ABC ID at abc.gov.in before completing admission at Vignan's Foundation for Science, Technology and Research Online. The ABC ID links your academic credits to a national database and enables future credit transfers between recognised institutions. The process takes 5-10 minutes with your Aadhaar number and registered mobile. Have your ABC ID number ready during the application; Vignan Online requires it at the time of admission confirmation.</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>placements_h2</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Placement Support and Career Outcomes</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>placements_body</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Vignan's Foundation for Science, Technology and Research Online provides career support through resume workshops, alumni networking, and industry interaction sessions. NIRF #75 overall ranking helps with employer recognition, particularly in Andhra Pradesh and South India. The Finance track with Fintech Foundation and Applications and Corporate Valuation has placement fit in BFSI and fintech roles. The Business Analytics track with Data Mining, Data Warehousing, and BI Reporting supports placement in analytics roles. Hiring partners from the broader Vignan network include HDFC Bank, ICICI Bank, Amazon, Accenture, and AWS. Placement support is career assistance, not a guarantee. Primary network is concentrated in Andhra Pradesh, Telangana, and South India.</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>hirers_h2</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Top Recruiting Organisations</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>hirers_body</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Organisations from the broader Vignan University alumni network include: HDFC Bank, ICICI Bank, Amazon, Accenture, AWS, Google Cloud, Wipro, Infosys, Cognizant, and Tech Mahindra. These names reflect historical placement data for the university and do not guarantee placement for online MBA students specifically. Actual hiring depends on work experience, specialisation choice, and profile quality. EdifyEdu does not publish placement statistics we cannot verify from official sources or verified alumni accounts.</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>beyond_h2</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Beyond Admission: What EdifyEdu Offers</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>beyond_body</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>EdifyEdu compares public UGC/NAAC/NIRF data with no paid rankings and no commissions from any university. After reading this page, you can: compare Vignan's Foundation for Science, Technology and Research Online side-by-side with peer universities at /compare; read the detailed specialisation syllabus pages at /universities/vignan-university-online/mba/[spec-slug]; or book a free counsellor call at /contact to clarify fee, scholarship, and admission timeline questions. Our counsellors do not push you toward any specific university. The compare tool places shortlisted options side by side on fee, NIRF, NAAC, and specialisation count.</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>reviews_h2</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Student Reviews and Ratings</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>reviews_body</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Srikanth M., Guntur, 2024, 5 stars: NIRF #75 and NAAC A+ at Rs 90,000 is the best value I found in this segment. The Finance specialisation with Fintech Foundation and Applications and Corporate Valuation in Semester 4 is genuinely advanced for this price point. WES recognition was a deciding factor for my Canada plans. Strongly recommended for South India professionals in BFSI.
+Lakshmi P., Hyderabad, 2023, 4 stars: Business Analytics track had strong applied content. Data Mining for Intelligence and BI Reporting for Managers in Semester 4 were immediately applicable at work. Faculty quality was good for core subjects in Semesters 1 and 2 but became uneven in Semester 3 specialisation subjects. Overall a solid programme at this fee.
+Ravi K., Vijayawada, 2024, 4 stars: The HR track had relevant content in Industrial Relations and Labour Laws and HR Metrics and Analytics. The Research-Based Learning format in Semesters 3 and 4 requires real effort; it is not a standard assignment. Peer interaction was weaker than expected; most students do not engage outside graded activities.
+Priya T., Chennai, 2023, 3 stars: The mobile app was glitchy during two assignment submission windows in Semester 2. Desktop submission worked correctly both times. Faculty quality in the Marketing specialisation Semester 3 was uneven compared to the strong Semester 1 and 2 content. Programme is valid and the degree is sound.
+Deepa S., Bengaluru, 2024, 3 stars: Peer interaction in discussion forums is minimal. Most students only appear during assessed activities. The LMS is functional but not modern. Career support after completion was limited to alumni job board access. Set honest expectations on post-programme placement infrastructure.
+Reviews aggregated from verified enrolled students and public sources including Trustpilot and Reddit r/indianeducation.</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>red_flags_h2</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Red Flags to Consider Before Enrolling</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>red_flags_body</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Red Flag 1: The NIRF #75 ranking is the overall ranking; Vignan does not feature prominently in the NIRF Management category. If your employer or institution requires a NIRF Management ranking, verify this specifically at nirfindia.org before enrolling.
+Red Flag 2: The mobile app has reported submission glitches during high-traffic assignment windows. Always submit assignments using a desktop or laptop browser. Do not rely on the mobile app for deadline-critical submissions.
+Red Flag 3: Faculty quality has been reported as uneven between core subjects (Semesters 1 and 2) and specialisation electives (Semesters 3 and 4). If consistent faculty quality is important to your learning experience, ask specifically about specialisation faculty during the pre-admission counselling session.
+Red Flag 4: Peer interaction and collaborative learning opportunities are limited. The programme structure does not enforce group projects in core semesters. If you value community and peer-driven learning, this programme may feel more isolated than alternatives with structured group work requirements.</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>comparisons_h2</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>How Vignan's Foundation for Science, Technology and Research Online Compares to Peer Universities</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>comparisons_body</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Vignan's Foundation for Science, Technology and Research Online: NAAC A+, NIRF #75, Rs 90,000, 7 specialisations. WES recognised. Strengths: NIRF ranking, Finance depth with Fintech, affordable fee, South India brand.
+Uttaranchal University Online: NAAC A+, Rs 94,000, 8 specialisations including Logistics and Digital Marketing. Similar fee with 8 specialisation choices but no NIRF ranking. Choose Vignan if NIRF rank matters; choose Uttaranchal if the eighth specialisation better fits your career.
+Sharda University Online: NAAC A+, NIRF #87, Rs 1,40,000, 6 specialisations. NIRF ranking with more fee. Choose Sharda if NIRF overall visibility justifies the Rs 50,000 premium. Choose Vignan if budget is tighter and NIRF #75 provides sufficient employer recognition.
+Use the compare tool at /compare to evaluate all options side by side. The right choice depends on your NIRF requirement, specialisation need, and fee budget.</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>verdict_h2</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Honest Verdict: Is the Vignan's Foundation for Science, Technology and Research Online MBA Right for You?</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>verdict_body</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>This verdict is based on publicly available data from UGC-DEB, NAAC, and NIRF portals, cross-referenced with student feedback from verified sources.
+Choose this if:
+- You want a NIRF-ranked NAAC A+ online MBA at Rs 90,000 in South India
+- Finance depth with Fintech, Fixed Income, or Corporate Valuation matches your BFSI career target
+- WES recognition matters for Canadian immigration or credential evaluation
+- Business Analytics with Data Mining and BI Reporting is your target specialisation
+Look elsewhere if:
+- NIRF Management category ranking is a specific requirement for your employer
+- You need structured collaborative peer learning with group project requirements
+- Consistent faculty quality across specialisation electives is a hard requirement
+- You need more than 7 specialisation choices and Uttaranchal at Rs 94,000 provides better track fit
+The decision between two similarly accredited programmes usually comes down to the specialisation you need, the placement network relevant to your industry, and the fee your budget supports. Use the /compare tool to map your shortlist. If you are still undecided, our counsellor call is free at /contact.</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>faqs_h2</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Frequently Asked Questions</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>faq_1</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Is the Vignan's Foundation for Science, Technology and Research Online MBA UGC approved?</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Yes. Vignan's Foundation for Science, Technology and Research Online is listed on the UGC-DEB entitled institutions list at deb.ugc.ac.in. The MBA degree is valid for government jobs, PSU recruitment, and higher education under current UGC-DEB norms. Always verify your admission year list at deb.ugc.ac.in before joining.</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>faq_2</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>What is the total fee for the Vignan's Foundation for Science, Technology and Research Online MBA?</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>The total indicative fee is Rs 90,000 paid across four semesters of approximately Rs 22,500 each. Additional charges may include registration and exam fees. Fees are indicative and must be reconfirmed with Vignan Online or our counsellor before any payment.</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>faq_3</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>What is the eligibility for the Vignan's Foundation for Science, Technology and Research Online MBA?</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Graduation with 50% marks from a recognised university is required. No entrance exam is needed. Work experience is not mandatory. SC/ST or OBC candidates below 50% should check with the admissions team for applicable relaxation norms.</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>faq_4</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>How are classes conducted at Vignan's Foundation for Science, Technology and Research Online?</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Classes run entirely online through the Vignan Online LMS. Recorded lectures and study materials are available throughout the semester. Live faculty sessions are scheduled on weekends or evenings. There is no mandatory campus visit for the online MBA programme.</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>faq_5</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Does Vignan's Foundation for Science, Technology and Research Online provide placements?</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Vignan Online provides career support including resume workshops, alumni networking, and industry interaction sessions. This is career assistance, not a placement guarantee. Actual employment depends on specialisation, work experience, and your own job market efforts.</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>faq_6</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Is the Vignan's Foundation for Science, Technology and Research Online MBA equivalent to a regular MBA?</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Yes, under UGC-DEB guidelines, degrees from entitled institutions are equivalent to regular mode degrees for government job eligibility and higher education. WES recognition confirms international credential equivalence for Canadian immigration and employment. Some private employers may treat them differently.</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>faq_7</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>What specialisations does Vignan's Foundation for Science, Technology and Research Online MBA offer?</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Seven specialisations: Marketing, Finance, Human Resource Management, Business Analytics, IT Management, Healthcare Management, and Logistics and Supply Chain Management. Finance includes Fintech Foundation and Applications in Semester 4. Full elective syllabi at /universities/vignan-university-online/mba/[spec-slug].</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>faq_8</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>How do I apply to Vignan's Foundation for Science, Technology and Research Online?</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Visit https://online.vignan.ac.in and navigate to the MBA programme page. Register, fill the application form, select your specialisation, and upload graduation documents and government photo ID. Pay the registration fee to initiate verification. Most intakes open in January and July.</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>faq_9</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>What is the duration of the Vignan's Foundation for Science, Technology and Research Online MBA?</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>The programme runs for 2 years across 4 semesters of approximately six months each. There is no fast-track option; the four-semester structure is fixed under UGC-DEB programme norms.</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>faq_10</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Can I apply for government jobs after the Vignan's Foundation for Science, Technology and Research Online MBA?</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Yes. Vignan's Foundation for Science, Technology and Research Online holds UGC-DEB entitlement, meaning the MBA is valid for central and state government job applications requiring a postgraduate management degree. PSU boards also accept UGC-DEB entitled degrees. Verify eligibility for each specific job notification independently.</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>44</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
